--- a/画面設計書/画面設計書_ファイル登録・更新画面.xlsx
+++ b/画面設計書/画面設計書_ファイル登録・更新画面.xlsx
@@ -4697,16 +4697,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4718,26 +4709,26 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4751,44 +4742,11 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4800,6 +4758,69 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4820,41 +4841,20 @@
     <xf numFmtId="0" fontId="18" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -6705,545 +6705,545 @@
   <sheetData>
     <row r="1" spans="2:39" ht="14.1" customHeight="1"/>
     <row r="2" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B2" s="237" t="s">
+      <c r="B2" s="243" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="238"/>
-      <c r="D2" s="238"/>
-      <c r="E2" s="238"/>
-      <c r="F2" s="238"/>
-      <c r="G2" s="238"/>
-      <c r="H2" s="238"/>
+      <c r="C2" s="244"/>
+      <c r="D2" s="244"/>
+      <c r="E2" s="244"/>
+      <c r="F2" s="244"/>
+      <c r="G2" s="244"/>
+      <c r="H2" s="244"/>
     </row>
     <row r="3" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B3" s="238"/>
-      <c r="C3" s="238"/>
-      <c r="D3" s="238"/>
-      <c r="E3" s="238"/>
-      <c r="F3" s="238"/>
-      <c r="G3" s="238"/>
-      <c r="H3" s="238"/>
+      <c r="B3" s="244"/>
+      <c r="C3" s="244"/>
+      <c r="D3" s="244"/>
+      <c r="E3" s="244"/>
+      <c r="F3" s="244"/>
+      <c r="G3" s="244"/>
+      <c r="H3" s="244"/>
     </row>
     <row r="4" spans="2:39" ht="14.1" customHeight="1"/>
     <row r="5" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B5" s="239" t="s">
+      <c r="B5" s="242" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="239"/>
-      <c r="D5" s="239"/>
-      <c r="E5" s="239"/>
-      <c r="F5" s="239"/>
-      <c r="G5" s="239"/>
-      <c r="H5" s="239"/>
-      <c r="I5" s="239" t="s">
+      <c r="C5" s="242"/>
+      <c r="D5" s="242"/>
+      <c r="E5" s="242"/>
+      <c r="F5" s="242"/>
+      <c r="G5" s="242"/>
+      <c r="H5" s="242"/>
+      <c r="I5" s="242" t="s">
         <v>5</v>
       </c>
-      <c r="J5" s="239"/>
-      <c r="K5" s="239"/>
-      <c r="L5" s="239"/>
-      <c r="M5" s="239"/>
-      <c r="N5" s="239"/>
-      <c r="O5" s="239" t="s">
+      <c r="J5" s="242"/>
+      <c r="K5" s="242"/>
+      <c r="L5" s="242"/>
+      <c r="M5" s="242"/>
+      <c r="N5" s="242"/>
+      <c r="O5" s="242" t="s">
         <v>10</v>
       </c>
-      <c r="P5" s="239"/>
-      <c r="Q5" s="239"/>
-      <c r="R5" s="239"/>
-      <c r="S5" s="239"/>
-      <c r="T5" s="239" t="s">
+      <c r="P5" s="242"/>
+      <c r="Q5" s="242"/>
+      <c r="R5" s="242"/>
+      <c r="S5" s="242"/>
+      <c r="T5" s="242" t="s">
         <v>6</v>
       </c>
-      <c r="U5" s="239"/>
-      <c r="V5" s="239"/>
-      <c r="W5" s="239"/>
-      <c r="X5" s="239"/>
-      <c r="Y5" s="239"/>
-      <c r="Z5" s="239"/>
-      <c r="AA5" s="239"/>
-      <c r="AB5" s="239"/>
-      <c r="AC5" s="239"/>
-      <c r="AD5" s="239"/>
-      <c r="AE5" s="239"/>
-      <c r="AF5" s="239"/>
-      <c r="AG5" s="239"/>
-      <c r="AH5" s="239" t="s">
+      <c r="U5" s="242"/>
+      <c r="V5" s="242"/>
+      <c r="W5" s="242"/>
+      <c r="X5" s="242"/>
+      <c r="Y5" s="242"/>
+      <c r="Z5" s="242"/>
+      <c r="AA5" s="242"/>
+      <c r="AB5" s="242"/>
+      <c r="AC5" s="242"/>
+      <c r="AD5" s="242"/>
+      <c r="AE5" s="242"/>
+      <c r="AF5" s="242"/>
+      <c r="AG5" s="242"/>
+      <c r="AH5" s="242" t="s">
         <v>7</v>
       </c>
-      <c r="AI5" s="239"/>
-      <c r="AJ5" s="239"/>
-      <c r="AK5" s="239"/>
-      <c r="AL5" s="239"/>
-      <c r="AM5" s="239"/>
+      <c r="AI5" s="242"/>
+      <c r="AJ5" s="242"/>
+      <c r="AK5" s="242"/>
+      <c r="AL5" s="242"/>
+      <c r="AM5" s="242"/>
     </row>
     <row r="6" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B6" s="240">
+      <c r="B6" s="241">
         <v>1</v>
       </c>
-      <c r="C6" s="240"/>
-      <c r="D6" s="240"/>
-      <c r="E6" s="240"/>
-      <c r="F6" s="240"/>
-      <c r="G6" s="240"/>
-      <c r="H6" s="240"/>
-      <c r="I6" s="241">
+      <c r="C6" s="241"/>
+      <c r="D6" s="241"/>
+      <c r="E6" s="241"/>
+      <c r="F6" s="241"/>
+      <c r="G6" s="241"/>
+      <c r="H6" s="241"/>
+      <c r="I6" s="238">
         <v>45629</v>
       </c>
-      <c r="J6" s="242"/>
-      <c r="K6" s="242"/>
-      <c r="L6" s="242"/>
-      <c r="M6" s="242"/>
-      <c r="N6" s="242"/>
-      <c r="O6" s="243" t="s">
+      <c r="J6" s="239"/>
+      <c r="K6" s="239"/>
+      <c r="L6" s="239"/>
+      <c r="M6" s="239"/>
+      <c r="N6" s="239"/>
+      <c r="O6" s="240" t="s">
         <v>35</v>
       </c>
-      <c r="P6" s="243"/>
-      <c r="Q6" s="243"/>
-      <c r="R6" s="243"/>
-      <c r="S6" s="243"/>
-      <c r="T6" s="243" t="s">
+      <c r="P6" s="240"/>
+      <c r="Q6" s="240"/>
+      <c r="R6" s="240"/>
+      <c r="S6" s="240"/>
+      <c r="T6" s="240" t="s">
         <v>36</v>
       </c>
-      <c r="U6" s="243"/>
-      <c r="V6" s="243"/>
-      <c r="W6" s="243"/>
-      <c r="X6" s="243"/>
-      <c r="Y6" s="243"/>
-      <c r="Z6" s="243"/>
-      <c r="AA6" s="243"/>
-      <c r="AB6" s="243"/>
-      <c r="AC6" s="243"/>
-      <c r="AD6" s="243"/>
-      <c r="AE6" s="243"/>
-      <c r="AF6" s="243"/>
-      <c r="AG6" s="243"/>
-      <c r="AH6" s="243" t="s">
+      <c r="U6" s="240"/>
+      <c r="V6" s="240"/>
+      <c r="W6" s="240"/>
+      <c r="X6" s="240"/>
+      <c r="Y6" s="240"/>
+      <c r="Z6" s="240"/>
+      <c r="AA6" s="240"/>
+      <c r="AB6" s="240"/>
+      <c r="AC6" s="240"/>
+      <c r="AD6" s="240"/>
+      <c r="AE6" s="240"/>
+      <c r="AF6" s="240"/>
+      <c r="AG6" s="240"/>
+      <c r="AH6" s="240" t="s">
         <v>96</v>
       </c>
-      <c r="AI6" s="243"/>
-      <c r="AJ6" s="243"/>
-      <c r="AK6" s="243"/>
-      <c r="AL6" s="243"/>
-      <c r="AM6" s="243"/>
+      <c r="AI6" s="240"/>
+      <c r="AJ6" s="240"/>
+      <c r="AK6" s="240"/>
+      <c r="AL6" s="240"/>
+      <c r="AM6" s="240"/>
     </row>
     <row r="7" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B7" s="240">
+      <c r="B7" s="241">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C7" s="240"/>
-      <c r="D7" s="240"/>
-      <c r="E7" s="240"/>
-      <c r="F7" s="240"/>
-      <c r="G7" s="240"/>
-      <c r="H7" s="240"/>
-      <c r="I7" s="241">
+      <c r="C7" s="241"/>
+      <c r="D7" s="241"/>
+      <c r="E7" s="241"/>
+      <c r="F7" s="241"/>
+      <c r="G7" s="241"/>
+      <c r="H7" s="241"/>
+      <c r="I7" s="238">
         <v>46086</v>
       </c>
-      <c r="J7" s="242"/>
-      <c r="K7" s="242"/>
-      <c r="L7" s="242"/>
-      <c r="M7" s="242"/>
-      <c r="N7" s="242"/>
-      <c r="O7" s="243" t="s">
+      <c r="J7" s="239"/>
+      <c r="K7" s="239"/>
+      <c r="L7" s="239"/>
+      <c r="M7" s="239"/>
+      <c r="N7" s="239"/>
+      <c r="O7" s="240" t="s">
         <v>35</v>
       </c>
-      <c r="P7" s="243"/>
-      <c r="Q7" s="243"/>
-      <c r="R7" s="243"/>
-      <c r="S7" s="243"/>
-      <c r="T7" s="243" t="s">
+      <c r="P7" s="240"/>
+      <c r="Q7" s="240"/>
+      <c r="R7" s="240"/>
+      <c r="S7" s="240"/>
+      <c r="T7" s="240" t="s">
         <v>412</v>
       </c>
-      <c r="U7" s="243"/>
-      <c r="V7" s="243"/>
-      <c r="W7" s="243"/>
-      <c r="X7" s="243"/>
-      <c r="Y7" s="243"/>
-      <c r="Z7" s="243"/>
-      <c r="AA7" s="243"/>
-      <c r="AB7" s="243"/>
-      <c r="AC7" s="243"/>
-      <c r="AD7" s="243"/>
-      <c r="AE7" s="243"/>
-      <c r="AF7" s="243"/>
-      <c r="AG7" s="243"/>
-      <c r="AH7" s="243" t="s">
+      <c r="U7" s="240"/>
+      <c r="V7" s="240"/>
+      <c r="W7" s="240"/>
+      <c r="X7" s="240"/>
+      <c r="Y7" s="240"/>
+      <c r="Z7" s="240"/>
+      <c r="AA7" s="240"/>
+      <c r="AB7" s="240"/>
+      <c r="AC7" s="240"/>
+      <c r="AD7" s="240"/>
+      <c r="AE7" s="240"/>
+      <c r="AF7" s="240"/>
+      <c r="AG7" s="240"/>
+      <c r="AH7" s="240" t="s">
         <v>391</v>
       </c>
-      <c r="AI7" s="243"/>
-      <c r="AJ7" s="243"/>
-      <c r="AK7" s="243"/>
-      <c r="AL7" s="243"/>
-      <c r="AM7" s="243"/>
+      <c r="AI7" s="240"/>
+      <c r="AJ7" s="240"/>
+      <c r="AK7" s="240"/>
+      <c r="AL7" s="240"/>
+      <c r="AM7" s="240"/>
     </row>
     <row r="8" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B8" s="240">
+      <c r="B8" s="241">
         <v>1.2</v>
       </c>
-      <c r="C8" s="240"/>
-      <c r="D8" s="240"/>
-      <c r="E8" s="240"/>
-      <c r="F8" s="240"/>
-      <c r="G8" s="240"/>
-      <c r="H8" s="240"/>
-      <c r="I8" s="241">
+      <c r="C8" s="241"/>
+      <c r="D8" s="241"/>
+      <c r="E8" s="241"/>
+      <c r="F8" s="241"/>
+      <c r="G8" s="241"/>
+      <c r="H8" s="241"/>
+      <c r="I8" s="238">
         <v>46087</v>
       </c>
-      <c r="J8" s="242"/>
-      <c r="K8" s="242"/>
-      <c r="L8" s="242"/>
-      <c r="M8" s="242"/>
-      <c r="N8" s="242"/>
-      <c r="O8" s="243" t="s">
+      <c r="J8" s="239"/>
+      <c r="K8" s="239"/>
+      <c r="L8" s="239"/>
+      <c r="M8" s="239"/>
+      <c r="N8" s="239"/>
+      <c r="O8" s="240" t="s">
         <v>35</v>
       </c>
-      <c r="P8" s="243"/>
-      <c r="Q8" s="243"/>
-      <c r="R8" s="243"/>
-      <c r="S8" s="243"/>
-      <c r="T8" s="243" t="s">
+      <c r="P8" s="240"/>
+      <c r="Q8" s="240"/>
+      <c r="R8" s="240"/>
+      <c r="S8" s="240"/>
+      <c r="T8" s="240" t="s">
         <v>399</v>
       </c>
-      <c r="U8" s="243"/>
-      <c r="V8" s="243"/>
-      <c r="W8" s="243"/>
-      <c r="X8" s="243"/>
-      <c r="Y8" s="243"/>
-      <c r="Z8" s="243"/>
-      <c r="AA8" s="243"/>
-      <c r="AB8" s="243"/>
-      <c r="AC8" s="243"/>
-      <c r="AD8" s="243"/>
-      <c r="AE8" s="243"/>
-      <c r="AF8" s="243"/>
-      <c r="AG8" s="243"/>
-      <c r="AH8" s="243" t="s">
+      <c r="U8" s="240"/>
+      <c r="V8" s="240"/>
+      <c r="W8" s="240"/>
+      <c r="X8" s="240"/>
+      <c r="Y8" s="240"/>
+      <c r="Z8" s="240"/>
+      <c r="AA8" s="240"/>
+      <c r="AB8" s="240"/>
+      <c r="AC8" s="240"/>
+      <c r="AD8" s="240"/>
+      <c r="AE8" s="240"/>
+      <c r="AF8" s="240"/>
+      <c r="AG8" s="240"/>
+      <c r="AH8" s="240" t="s">
         <v>400</v>
       </c>
-      <c r="AI8" s="243"/>
-      <c r="AJ8" s="243"/>
-      <c r="AK8" s="243"/>
-      <c r="AL8" s="243"/>
-      <c r="AM8" s="243"/>
+      <c r="AI8" s="240"/>
+      <c r="AJ8" s="240"/>
+      <c r="AK8" s="240"/>
+      <c r="AL8" s="240"/>
+      <c r="AM8" s="240"/>
     </row>
     <row r="9" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B9" s="240"/>
-      <c r="C9" s="240"/>
-      <c r="D9" s="240"/>
-      <c r="E9" s="240"/>
-      <c r="F9" s="240"/>
-      <c r="G9" s="240"/>
-      <c r="H9" s="240"/>
-      <c r="I9" s="241"/>
-      <c r="J9" s="242"/>
-      <c r="K9" s="242"/>
-      <c r="L9" s="242"/>
-      <c r="M9" s="242"/>
-      <c r="N9" s="242"/>
-      <c r="O9" s="243"/>
-      <c r="P9" s="243"/>
-      <c r="Q9" s="243"/>
-      <c r="R9" s="243"/>
-      <c r="S9" s="243"/>
-      <c r="T9" s="243"/>
-      <c r="U9" s="243"/>
-      <c r="V9" s="243"/>
-      <c r="W9" s="243"/>
-      <c r="X9" s="243"/>
-      <c r="Y9" s="243"/>
-      <c r="Z9" s="243"/>
-      <c r="AA9" s="243"/>
-      <c r="AB9" s="243"/>
-      <c r="AC9" s="243"/>
-      <c r="AD9" s="243"/>
-      <c r="AE9" s="243"/>
-      <c r="AF9" s="243"/>
-      <c r="AG9" s="243"/>
-      <c r="AH9" s="243"/>
-      <c r="AI9" s="243"/>
-      <c r="AJ9" s="243"/>
-      <c r="AK9" s="243"/>
-      <c r="AL9" s="243"/>
-      <c r="AM9" s="243"/>
+      <c r="B9" s="241"/>
+      <c r="C9" s="241"/>
+      <c r="D9" s="241"/>
+      <c r="E9" s="241"/>
+      <c r="F9" s="241"/>
+      <c r="G9" s="241"/>
+      <c r="H9" s="241"/>
+      <c r="I9" s="238"/>
+      <c r="J9" s="239"/>
+      <c r="K9" s="239"/>
+      <c r="L9" s="239"/>
+      <c r="M9" s="239"/>
+      <c r="N9" s="239"/>
+      <c r="O9" s="240"/>
+      <c r="P9" s="240"/>
+      <c r="Q9" s="240"/>
+      <c r="R9" s="240"/>
+      <c r="S9" s="240"/>
+      <c r="T9" s="240"/>
+      <c r="U9" s="240"/>
+      <c r="V9" s="240"/>
+      <c r="W9" s="240"/>
+      <c r="X9" s="240"/>
+      <c r="Y9" s="240"/>
+      <c r="Z9" s="240"/>
+      <c r="AA9" s="240"/>
+      <c r="AB9" s="240"/>
+      <c r="AC9" s="240"/>
+      <c r="AD9" s="240"/>
+      <c r="AE9" s="240"/>
+      <c r="AF9" s="240"/>
+      <c r="AG9" s="240"/>
+      <c r="AH9" s="240"/>
+      <c r="AI9" s="240"/>
+      <c r="AJ9" s="240"/>
+      <c r="AK9" s="240"/>
+      <c r="AL9" s="240"/>
+      <c r="AM9" s="240"/>
     </row>
     <row r="10" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B10" s="240"/>
-      <c r="C10" s="240"/>
-      <c r="D10" s="240"/>
-      <c r="E10" s="240"/>
-      <c r="F10" s="240"/>
-      <c r="G10" s="240"/>
-      <c r="H10" s="240"/>
-      <c r="I10" s="241"/>
-      <c r="J10" s="242"/>
-      <c r="K10" s="242"/>
-      <c r="L10" s="242"/>
-      <c r="M10" s="242"/>
-      <c r="N10" s="242"/>
-      <c r="O10" s="243"/>
-      <c r="P10" s="243"/>
-      <c r="Q10" s="243"/>
-      <c r="R10" s="243"/>
-      <c r="S10" s="243"/>
-      <c r="T10" s="243"/>
-      <c r="U10" s="243"/>
-      <c r="V10" s="243"/>
-      <c r="W10" s="243"/>
-      <c r="X10" s="243"/>
-      <c r="Y10" s="243"/>
-      <c r="Z10" s="243"/>
-      <c r="AA10" s="243"/>
-      <c r="AB10" s="243"/>
-      <c r="AC10" s="243"/>
-      <c r="AD10" s="243"/>
-      <c r="AE10" s="243"/>
-      <c r="AF10" s="243"/>
-      <c r="AG10" s="243"/>
-      <c r="AH10" s="243"/>
-      <c r="AI10" s="243"/>
-      <c r="AJ10" s="243"/>
-      <c r="AK10" s="243"/>
-      <c r="AL10" s="243"/>
-      <c r="AM10" s="243"/>
+      <c r="B10" s="241"/>
+      <c r="C10" s="241"/>
+      <c r="D10" s="241"/>
+      <c r="E10" s="241"/>
+      <c r="F10" s="241"/>
+      <c r="G10" s="241"/>
+      <c r="H10" s="241"/>
+      <c r="I10" s="238"/>
+      <c r="J10" s="239"/>
+      <c r="K10" s="239"/>
+      <c r="L10" s="239"/>
+      <c r="M10" s="239"/>
+      <c r="N10" s="239"/>
+      <c r="O10" s="240"/>
+      <c r="P10" s="240"/>
+      <c r="Q10" s="240"/>
+      <c r="R10" s="240"/>
+      <c r="S10" s="240"/>
+      <c r="T10" s="240"/>
+      <c r="U10" s="240"/>
+      <c r="V10" s="240"/>
+      <c r="W10" s="240"/>
+      <c r="X10" s="240"/>
+      <c r="Y10" s="240"/>
+      <c r="Z10" s="240"/>
+      <c r="AA10" s="240"/>
+      <c r="AB10" s="240"/>
+      <c r="AC10" s="240"/>
+      <c r="AD10" s="240"/>
+      <c r="AE10" s="240"/>
+      <c r="AF10" s="240"/>
+      <c r="AG10" s="240"/>
+      <c r="AH10" s="240"/>
+      <c r="AI10" s="240"/>
+      <c r="AJ10" s="240"/>
+      <c r="AK10" s="240"/>
+      <c r="AL10" s="240"/>
+      <c r="AM10" s="240"/>
     </row>
     <row r="11" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B11" s="240"/>
-      <c r="C11" s="240"/>
-      <c r="D11" s="240"/>
-      <c r="E11" s="240"/>
-      <c r="F11" s="240"/>
-      <c r="G11" s="240"/>
-      <c r="H11" s="240"/>
-      <c r="I11" s="241"/>
-      <c r="J11" s="242"/>
-      <c r="K11" s="242"/>
-      <c r="L11" s="242"/>
-      <c r="M11" s="242"/>
-      <c r="N11" s="242"/>
-      <c r="O11" s="243"/>
-      <c r="P11" s="243"/>
-      <c r="Q11" s="243"/>
-      <c r="R11" s="243"/>
-      <c r="S11" s="243"/>
-      <c r="T11" s="243"/>
-      <c r="U11" s="243"/>
-      <c r="V11" s="243"/>
-      <c r="W11" s="243"/>
-      <c r="X11" s="243"/>
-      <c r="Y11" s="243"/>
-      <c r="Z11" s="243"/>
-      <c r="AA11" s="243"/>
-      <c r="AB11" s="243"/>
-      <c r="AC11" s="243"/>
-      <c r="AD11" s="243"/>
-      <c r="AE11" s="243"/>
-      <c r="AF11" s="243"/>
-      <c r="AG11" s="243"/>
-      <c r="AH11" s="243"/>
-      <c r="AI11" s="243"/>
-      <c r="AJ11" s="243"/>
-      <c r="AK11" s="243"/>
-      <c r="AL11" s="243"/>
-      <c r="AM11" s="243"/>
+      <c r="B11" s="241"/>
+      <c r="C11" s="241"/>
+      <c r="D11" s="241"/>
+      <c r="E11" s="241"/>
+      <c r="F11" s="241"/>
+      <c r="G11" s="241"/>
+      <c r="H11" s="241"/>
+      <c r="I11" s="238"/>
+      <c r="J11" s="239"/>
+      <c r="K11" s="239"/>
+      <c r="L11" s="239"/>
+      <c r="M11" s="239"/>
+      <c r="N11" s="239"/>
+      <c r="O11" s="240"/>
+      <c r="P11" s="240"/>
+      <c r="Q11" s="240"/>
+      <c r="R11" s="240"/>
+      <c r="S11" s="240"/>
+      <c r="T11" s="240"/>
+      <c r="U11" s="240"/>
+      <c r="V11" s="240"/>
+      <c r="W11" s="240"/>
+      <c r="X11" s="240"/>
+      <c r="Y11" s="240"/>
+      <c r="Z11" s="240"/>
+      <c r="AA11" s="240"/>
+      <c r="AB11" s="240"/>
+      <c r="AC11" s="240"/>
+      <c r="AD11" s="240"/>
+      <c r="AE11" s="240"/>
+      <c r="AF11" s="240"/>
+      <c r="AG11" s="240"/>
+      <c r="AH11" s="240"/>
+      <c r="AI11" s="240"/>
+      <c r="AJ11" s="240"/>
+      <c r="AK11" s="240"/>
+      <c r="AL11" s="240"/>
+      <c r="AM11" s="240"/>
     </row>
     <row r="12" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B12" s="240"/>
-      <c r="C12" s="240"/>
-      <c r="D12" s="240"/>
-      <c r="E12" s="240"/>
-      <c r="F12" s="240"/>
-      <c r="G12" s="240"/>
-      <c r="H12" s="240"/>
-      <c r="I12" s="241"/>
-      <c r="J12" s="242"/>
-      <c r="K12" s="242"/>
-      <c r="L12" s="242"/>
-      <c r="M12" s="242"/>
-      <c r="N12" s="242"/>
-      <c r="O12" s="243"/>
-      <c r="P12" s="243"/>
-      <c r="Q12" s="243"/>
-      <c r="R12" s="243"/>
-      <c r="S12" s="243"/>
-      <c r="T12" s="243"/>
-      <c r="U12" s="243"/>
-      <c r="V12" s="243"/>
-      <c r="W12" s="243"/>
-      <c r="X12" s="243"/>
-      <c r="Y12" s="243"/>
-      <c r="Z12" s="243"/>
-      <c r="AA12" s="243"/>
-      <c r="AB12" s="243"/>
-      <c r="AC12" s="243"/>
-      <c r="AD12" s="243"/>
-      <c r="AE12" s="243"/>
-      <c r="AF12" s="243"/>
-      <c r="AG12" s="243"/>
-      <c r="AH12" s="243"/>
-      <c r="AI12" s="243"/>
-      <c r="AJ12" s="243"/>
-      <c r="AK12" s="243"/>
-      <c r="AL12" s="243"/>
-      <c r="AM12" s="243"/>
+      <c r="B12" s="241"/>
+      <c r="C12" s="241"/>
+      <c r="D12" s="241"/>
+      <c r="E12" s="241"/>
+      <c r="F12" s="241"/>
+      <c r="G12" s="241"/>
+      <c r="H12" s="241"/>
+      <c r="I12" s="238"/>
+      <c r="J12" s="239"/>
+      <c r="K12" s="239"/>
+      <c r="L12" s="239"/>
+      <c r="M12" s="239"/>
+      <c r="N12" s="239"/>
+      <c r="O12" s="240"/>
+      <c r="P12" s="240"/>
+      <c r="Q12" s="240"/>
+      <c r="R12" s="240"/>
+      <c r="S12" s="240"/>
+      <c r="T12" s="240"/>
+      <c r="U12" s="240"/>
+      <c r="V12" s="240"/>
+      <c r="W12" s="240"/>
+      <c r="X12" s="240"/>
+      <c r="Y12" s="240"/>
+      <c r="Z12" s="240"/>
+      <c r="AA12" s="240"/>
+      <c r="AB12" s="240"/>
+      <c r="AC12" s="240"/>
+      <c r="AD12" s="240"/>
+      <c r="AE12" s="240"/>
+      <c r="AF12" s="240"/>
+      <c r="AG12" s="240"/>
+      <c r="AH12" s="240"/>
+      <c r="AI12" s="240"/>
+      <c r="AJ12" s="240"/>
+      <c r="AK12" s="240"/>
+      <c r="AL12" s="240"/>
+      <c r="AM12" s="240"/>
     </row>
     <row r="13" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B13" s="244"/>
-      <c r="C13" s="244"/>
-      <c r="D13" s="244"/>
-      <c r="E13" s="244"/>
-      <c r="F13" s="244"/>
-      <c r="G13" s="244"/>
-      <c r="H13" s="244"/>
-      <c r="I13" s="241"/>
-      <c r="J13" s="242"/>
-      <c r="K13" s="242"/>
-      <c r="L13" s="242"/>
-      <c r="M13" s="242"/>
-      <c r="N13" s="242"/>
-      <c r="O13" s="243"/>
-      <c r="P13" s="243"/>
-      <c r="Q13" s="243"/>
-      <c r="R13" s="243"/>
-      <c r="S13" s="243"/>
-      <c r="T13" s="243"/>
-      <c r="U13" s="243"/>
-      <c r="V13" s="243"/>
-      <c r="W13" s="243"/>
-      <c r="X13" s="243"/>
-      <c r="Y13" s="243"/>
-      <c r="Z13" s="243"/>
-      <c r="AA13" s="243"/>
-      <c r="AB13" s="243"/>
-      <c r="AC13" s="243"/>
-      <c r="AD13" s="243"/>
-      <c r="AE13" s="243"/>
-      <c r="AF13" s="243"/>
-      <c r="AG13" s="243"/>
-      <c r="AH13" s="243"/>
-      <c r="AI13" s="243"/>
-      <c r="AJ13" s="243"/>
-      <c r="AK13" s="243"/>
-      <c r="AL13" s="243"/>
-      <c r="AM13" s="243"/>
+      <c r="B13" s="237"/>
+      <c r="C13" s="237"/>
+      <c r="D13" s="237"/>
+      <c r="E13" s="237"/>
+      <c r="F13" s="237"/>
+      <c r="G13" s="237"/>
+      <c r="H13" s="237"/>
+      <c r="I13" s="238"/>
+      <c r="J13" s="239"/>
+      <c r="K13" s="239"/>
+      <c r="L13" s="239"/>
+      <c r="M13" s="239"/>
+      <c r="N13" s="239"/>
+      <c r="O13" s="240"/>
+      <c r="P13" s="240"/>
+      <c r="Q13" s="240"/>
+      <c r="R13" s="240"/>
+      <c r="S13" s="240"/>
+      <c r="T13" s="240"/>
+      <c r="U13" s="240"/>
+      <c r="V13" s="240"/>
+      <c r="W13" s="240"/>
+      <c r="X13" s="240"/>
+      <c r="Y13" s="240"/>
+      <c r="Z13" s="240"/>
+      <c r="AA13" s="240"/>
+      <c r="AB13" s="240"/>
+      <c r="AC13" s="240"/>
+      <c r="AD13" s="240"/>
+      <c r="AE13" s="240"/>
+      <c r="AF13" s="240"/>
+      <c r="AG13" s="240"/>
+      <c r="AH13" s="240"/>
+      <c r="AI13" s="240"/>
+      <c r="AJ13" s="240"/>
+      <c r="AK13" s="240"/>
+      <c r="AL13" s="240"/>
+      <c r="AM13" s="240"/>
     </row>
     <row r="14" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B14" s="244"/>
-      <c r="C14" s="244"/>
-      <c r="D14" s="244"/>
-      <c r="E14" s="244"/>
-      <c r="F14" s="244"/>
-      <c r="G14" s="244"/>
-      <c r="H14" s="244"/>
-      <c r="I14" s="241"/>
-      <c r="J14" s="242"/>
-      <c r="K14" s="242"/>
-      <c r="L14" s="242"/>
-      <c r="M14" s="242"/>
-      <c r="N14" s="242"/>
-      <c r="O14" s="243"/>
-      <c r="P14" s="243"/>
-      <c r="Q14" s="243"/>
-      <c r="R14" s="243"/>
-      <c r="S14" s="243"/>
-      <c r="T14" s="243"/>
-      <c r="U14" s="243"/>
-      <c r="V14" s="243"/>
-      <c r="W14" s="243"/>
-      <c r="X14" s="243"/>
-      <c r="Y14" s="243"/>
-      <c r="Z14" s="243"/>
-      <c r="AA14" s="243"/>
-      <c r="AB14" s="243"/>
-      <c r="AC14" s="243"/>
-      <c r="AD14" s="243"/>
-      <c r="AE14" s="243"/>
-      <c r="AF14" s="243"/>
-      <c r="AG14" s="243"/>
-      <c r="AH14" s="243"/>
-      <c r="AI14" s="243"/>
-      <c r="AJ14" s="243"/>
-      <c r="AK14" s="243"/>
-      <c r="AL14" s="243"/>
-      <c r="AM14" s="243"/>
+      <c r="B14" s="237"/>
+      <c r="C14" s="237"/>
+      <c r="D14" s="237"/>
+      <c r="E14" s="237"/>
+      <c r="F14" s="237"/>
+      <c r="G14" s="237"/>
+      <c r="H14" s="237"/>
+      <c r="I14" s="238"/>
+      <c r="J14" s="239"/>
+      <c r="K14" s="239"/>
+      <c r="L14" s="239"/>
+      <c r="M14" s="239"/>
+      <c r="N14" s="239"/>
+      <c r="O14" s="240"/>
+      <c r="P14" s="240"/>
+      <c r="Q14" s="240"/>
+      <c r="R14" s="240"/>
+      <c r="S14" s="240"/>
+      <c r="T14" s="240"/>
+      <c r="U14" s="240"/>
+      <c r="V14" s="240"/>
+      <c r="W14" s="240"/>
+      <c r="X14" s="240"/>
+      <c r="Y14" s="240"/>
+      <c r="Z14" s="240"/>
+      <c r="AA14" s="240"/>
+      <c r="AB14" s="240"/>
+      <c r="AC14" s="240"/>
+      <c r="AD14" s="240"/>
+      <c r="AE14" s="240"/>
+      <c r="AF14" s="240"/>
+      <c r="AG14" s="240"/>
+      <c r="AH14" s="240"/>
+      <c r="AI14" s="240"/>
+      <c r="AJ14" s="240"/>
+      <c r="AK14" s="240"/>
+      <c r="AL14" s="240"/>
+      <c r="AM14" s="240"/>
     </row>
     <row r="15" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B15" s="244"/>
-      <c r="C15" s="244"/>
-      <c r="D15" s="244"/>
-      <c r="E15" s="244"/>
-      <c r="F15" s="244"/>
-      <c r="G15" s="244"/>
-      <c r="H15" s="244"/>
-      <c r="I15" s="241"/>
-      <c r="J15" s="242"/>
-      <c r="K15" s="242"/>
-      <c r="L15" s="242"/>
-      <c r="M15" s="242"/>
-      <c r="N15" s="242"/>
-      <c r="O15" s="243"/>
-      <c r="P15" s="243"/>
-      <c r="Q15" s="243"/>
-      <c r="R15" s="243"/>
-      <c r="S15" s="243"/>
-      <c r="T15" s="243"/>
-      <c r="U15" s="243"/>
-      <c r="V15" s="243"/>
-      <c r="W15" s="243"/>
-      <c r="X15" s="243"/>
-      <c r="Y15" s="243"/>
-      <c r="Z15" s="243"/>
-      <c r="AA15" s="243"/>
-      <c r="AB15" s="243"/>
-      <c r="AC15" s="243"/>
-      <c r="AD15" s="243"/>
-      <c r="AE15" s="243"/>
-      <c r="AF15" s="243"/>
-      <c r="AG15" s="243"/>
-      <c r="AH15" s="243"/>
-      <c r="AI15" s="243"/>
-      <c r="AJ15" s="243"/>
-      <c r="AK15" s="243"/>
-      <c r="AL15" s="243"/>
-      <c r="AM15" s="243"/>
+      <c r="B15" s="237"/>
+      <c r="C15" s="237"/>
+      <c r="D15" s="237"/>
+      <c r="E15" s="237"/>
+      <c r="F15" s="237"/>
+      <c r="G15" s="237"/>
+      <c r="H15" s="237"/>
+      <c r="I15" s="238"/>
+      <c r="J15" s="239"/>
+      <c r="K15" s="239"/>
+      <c r="L15" s="239"/>
+      <c r="M15" s="239"/>
+      <c r="N15" s="239"/>
+      <c r="O15" s="240"/>
+      <c r="P15" s="240"/>
+      <c r="Q15" s="240"/>
+      <c r="R15" s="240"/>
+      <c r="S15" s="240"/>
+      <c r="T15" s="240"/>
+      <c r="U15" s="240"/>
+      <c r="V15" s="240"/>
+      <c r="W15" s="240"/>
+      <c r="X15" s="240"/>
+      <c r="Y15" s="240"/>
+      <c r="Z15" s="240"/>
+      <c r="AA15" s="240"/>
+      <c r="AB15" s="240"/>
+      <c r="AC15" s="240"/>
+      <c r="AD15" s="240"/>
+      <c r="AE15" s="240"/>
+      <c r="AF15" s="240"/>
+      <c r="AG15" s="240"/>
+      <c r="AH15" s="240"/>
+      <c r="AI15" s="240"/>
+      <c r="AJ15" s="240"/>
+      <c r="AK15" s="240"/>
+      <c r="AL15" s="240"/>
+      <c r="AM15" s="240"/>
     </row>
     <row r="16" spans="2:39" ht="14.1" customHeight="1">
-      <c r="B16" s="244"/>
-      <c r="C16" s="244"/>
-      <c r="D16" s="244"/>
-      <c r="E16" s="244"/>
-      <c r="F16" s="244"/>
-      <c r="G16" s="244"/>
-      <c r="H16" s="244"/>
-      <c r="I16" s="241"/>
-      <c r="J16" s="242"/>
-      <c r="K16" s="242"/>
-      <c r="L16" s="242"/>
-      <c r="M16" s="242"/>
-      <c r="N16" s="242"/>
-      <c r="O16" s="243"/>
-      <c r="P16" s="243"/>
-      <c r="Q16" s="243"/>
-      <c r="R16" s="243"/>
-      <c r="S16" s="243"/>
-      <c r="T16" s="243"/>
-      <c r="U16" s="243"/>
-      <c r="V16" s="243"/>
-      <c r="W16" s="243"/>
-      <c r="X16" s="243"/>
-      <c r="Y16" s="243"/>
-      <c r="Z16" s="243"/>
-      <c r="AA16" s="243"/>
-      <c r="AB16" s="243"/>
-      <c r="AC16" s="243"/>
-      <c r="AD16" s="243"/>
-      <c r="AE16" s="243"/>
-      <c r="AF16" s="243"/>
-      <c r="AG16" s="243"/>
-      <c r="AH16" s="243"/>
-      <c r="AI16" s="243"/>
-      <c r="AJ16" s="243"/>
-      <c r="AK16" s="243"/>
-      <c r="AL16" s="243"/>
-      <c r="AM16" s="243"/>
+      <c r="B16" s="237"/>
+      <c r="C16" s="237"/>
+      <c r="D16" s="237"/>
+      <c r="E16" s="237"/>
+      <c r="F16" s="237"/>
+      <c r="G16" s="237"/>
+      <c r="H16" s="237"/>
+      <c r="I16" s="238"/>
+      <c r="J16" s="239"/>
+      <c r="K16" s="239"/>
+      <c r="L16" s="239"/>
+      <c r="M16" s="239"/>
+      <c r="N16" s="239"/>
+      <c r="O16" s="240"/>
+      <c r="P16" s="240"/>
+      <c r="Q16" s="240"/>
+      <c r="R16" s="240"/>
+      <c r="S16" s="240"/>
+      <c r="T16" s="240"/>
+      <c r="U16" s="240"/>
+      <c r="V16" s="240"/>
+      <c r="W16" s="240"/>
+      <c r="X16" s="240"/>
+      <c r="Y16" s="240"/>
+      <c r="Z16" s="240"/>
+      <c r="AA16" s="240"/>
+      <c r="AB16" s="240"/>
+      <c r="AC16" s="240"/>
+      <c r="AD16" s="240"/>
+      <c r="AE16" s="240"/>
+      <c r="AF16" s="240"/>
+      <c r="AG16" s="240"/>
+      <c r="AH16" s="240"/>
+      <c r="AI16" s="240"/>
+      <c r="AJ16" s="240"/>
+      <c r="AK16" s="240"/>
+      <c r="AL16" s="240"/>
+      <c r="AM16" s="240"/>
     </row>
     <row r="17" spans="2:31" ht="14.1" customHeight="1">
       <c r="J17" s="16"/>
@@ -7429,26 +7429,37 @@
     <row r="33" ht="14.1" customHeight="1"/>
   </sheetData>
   <mergeCells count="61">
-    <mergeCell ref="B16:H16"/>
-    <mergeCell ref="I16:N16"/>
-    <mergeCell ref="O16:S16"/>
-    <mergeCell ref="T16:AG16"/>
-    <mergeCell ref="AH16:AM16"/>
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="I15:N15"/>
-    <mergeCell ref="O15:S15"/>
-    <mergeCell ref="T15:AG15"/>
-    <mergeCell ref="AH15:AM15"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="I14:N14"/>
-    <mergeCell ref="O14:S14"/>
-    <mergeCell ref="T14:AG14"/>
-    <mergeCell ref="AH14:AM14"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="I13:N13"/>
-    <mergeCell ref="O13:S13"/>
-    <mergeCell ref="T13:AG13"/>
-    <mergeCell ref="AH13:AM13"/>
+    <mergeCell ref="B2:H3"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="I5:N5"/>
+    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="T5:AG5"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="I7:N7"/>
+    <mergeCell ref="O7:S7"/>
+    <mergeCell ref="T7:AG7"/>
+    <mergeCell ref="AH7:AM7"/>
+    <mergeCell ref="AH5:AM5"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="I6:N6"/>
+    <mergeCell ref="O6:S6"/>
+    <mergeCell ref="T6:AG6"/>
+    <mergeCell ref="AH6:AM6"/>
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="I9:N9"/>
+    <mergeCell ref="T8:AG8"/>
+    <mergeCell ref="T9:AG9"/>
+    <mergeCell ref="AH9:AM9"/>
+    <mergeCell ref="O9:S9"/>
+    <mergeCell ref="AH8:AM8"/>
+    <mergeCell ref="O8:S8"/>
+    <mergeCell ref="B8:H8"/>
+    <mergeCell ref="I8:N8"/>
+    <mergeCell ref="T10:AG10"/>
+    <mergeCell ref="AH10:AM10"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="O10:S10"/>
+    <mergeCell ref="I10:N10"/>
     <mergeCell ref="B12:H12"/>
     <mergeCell ref="I12:N12"/>
     <mergeCell ref="T12:AG12"/>
@@ -7459,37 +7470,26 @@
     <mergeCell ref="I11:N11"/>
     <mergeCell ref="T11:AG11"/>
     <mergeCell ref="AH11:AM11"/>
-    <mergeCell ref="T10:AG10"/>
-    <mergeCell ref="AH10:AM10"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="O10:S10"/>
-    <mergeCell ref="I10:N10"/>
-    <mergeCell ref="B9:H9"/>
-    <mergeCell ref="I9:N9"/>
-    <mergeCell ref="T8:AG8"/>
-    <mergeCell ref="T9:AG9"/>
-    <mergeCell ref="AH9:AM9"/>
-    <mergeCell ref="O9:S9"/>
-    <mergeCell ref="AH8:AM8"/>
-    <mergeCell ref="O8:S8"/>
-    <mergeCell ref="B8:H8"/>
-    <mergeCell ref="I8:N8"/>
-    <mergeCell ref="AH5:AM5"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="I6:N6"/>
-    <mergeCell ref="O6:S6"/>
-    <mergeCell ref="T6:AG6"/>
-    <mergeCell ref="AH6:AM6"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="I7:N7"/>
-    <mergeCell ref="O7:S7"/>
-    <mergeCell ref="T7:AG7"/>
-    <mergeCell ref="AH7:AM7"/>
-    <mergeCell ref="B2:H3"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="I5:N5"/>
-    <mergeCell ref="O5:S5"/>
-    <mergeCell ref="T5:AG5"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="I13:N13"/>
+    <mergeCell ref="O13:S13"/>
+    <mergeCell ref="T13:AG13"/>
+    <mergeCell ref="AH13:AM13"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="I14:N14"/>
+    <mergeCell ref="O14:S14"/>
+    <mergeCell ref="T14:AG14"/>
+    <mergeCell ref="AH14:AM14"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="I15:N15"/>
+    <mergeCell ref="O15:S15"/>
+    <mergeCell ref="T15:AG15"/>
+    <mergeCell ref="AH15:AM15"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="I16:N16"/>
+    <mergeCell ref="O16:S16"/>
+    <mergeCell ref="T16:AG16"/>
+    <mergeCell ref="AH16:AM16"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7511,36 +7511,36 @@
       <c r="A1" s="18"/>
     </row>
     <row r="2" spans="1:40" ht="14.1" customHeight="1">
-      <c r="B2" s="237" t="s">
+      <c r="B2" s="243" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="237"/>
-      <c r="D2" s="237"/>
-      <c r="E2" s="237"/>
-      <c r="F2" s="237"/>
-      <c r="G2" s="237"/>
-      <c r="H2" s="237"/>
-      <c r="I2" s="237"/>
-      <c r="J2" s="237"/>
-      <c r="K2" s="237"/>
-      <c r="L2" s="237"/>
-      <c r="M2" s="237"/>
-      <c r="N2" s="237"/>
+      <c r="C2" s="243"/>
+      <c r="D2" s="243"/>
+      <c r="E2" s="243"/>
+      <c r="F2" s="243"/>
+      <c r="G2" s="243"/>
+      <c r="H2" s="243"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
+      <c r="M2" s="243"/>
+      <c r="N2" s="243"/>
     </row>
     <row r="3" spans="1:40" ht="14.1" customHeight="1">
-      <c r="B3" s="237"/>
-      <c r="C3" s="237"/>
-      <c r="D3" s="237"/>
-      <c r="E3" s="237"/>
-      <c r="F3" s="237"/>
-      <c r="G3" s="237"/>
-      <c r="H3" s="237"/>
-      <c r="I3" s="237"/>
-      <c r="J3" s="237"/>
-      <c r="K3" s="237"/>
-      <c r="L3" s="237"/>
-      <c r="M3" s="237"/>
-      <c r="N3" s="237"/>
+      <c r="B3" s="243"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="243"/>
+      <c r="F3" s="243"/>
+      <c r="G3" s="243"/>
+      <c r="H3" s="243"/>
+      <c r="I3" s="243"/>
+      <c r="J3" s="243"/>
+      <c r="K3" s="243"/>
+      <c r="L3" s="243"/>
+      <c r="M3" s="243"/>
+      <c r="N3" s="243"/>
     </row>
     <row r="4" spans="1:40" ht="14.1" customHeight="1">
       <c r="B4" s="19" t="s">
@@ -7713,164 +7713,164 @@
       </c>
     </row>
     <row r="49" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B49" s="258" t="s">
+      <c r="B49" s="264" t="s">
         <v>0</v>
       </c>
-      <c r="C49" s="259"/>
-      <c r="D49" s="258" t="s">
+      <c r="C49" s="266"/>
+      <c r="D49" s="264" t="s">
         <v>12</v>
       </c>
-      <c r="E49" s="262"/>
-      <c r="F49" s="262"/>
-      <c r="G49" s="262"/>
-      <c r="H49" s="262"/>
-      <c r="I49" s="259"/>
-      <c r="J49" s="255" t="s">
+      <c r="E49" s="265"/>
+      <c r="F49" s="265"/>
+      <c r="G49" s="265"/>
+      <c r="H49" s="265"/>
+      <c r="I49" s="266"/>
+      <c r="J49" s="285" t="s">
         <v>13</v>
       </c>
-      <c r="K49" s="256"/>
-      <c r="L49" s="256"/>
-      <c r="M49" s="256"/>
-      <c r="N49" s="256"/>
-      <c r="O49" s="256"/>
-      <c r="P49" s="256"/>
-      <c r="Q49" s="256"/>
-      <c r="R49" s="256"/>
-      <c r="S49" s="256"/>
-      <c r="T49" s="256"/>
-      <c r="U49" s="257"/>
-      <c r="V49" s="266" t="s">
+      <c r="K49" s="286"/>
+      <c r="L49" s="286"/>
+      <c r="M49" s="286"/>
+      <c r="N49" s="286"/>
+      <c r="O49" s="286"/>
+      <c r="P49" s="286"/>
+      <c r="Q49" s="286"/>
+      <c r="R49" s="286"/>
+      <c r="S49" s="286"/>
+      <c r="T49" s="286"/>
+      <c r="U49" s="287"/>
+      <c r="V49" s="288" t="s">
         <v>48</v>
       </c>
-      <c r="W49" s="255" t="s">
+      <c r="W49" s="285" t="s">
         <v>16</v>
       </c>
-      <c r="X49" s="257"/>
-      <c r="Y49" s="258" t="s">
+      <c r="X49" s="287"/>
+      <c r="Y49" s="264" t="s">
         <v>49</v>
       </c>
-      <c r="Z49" s="262"/>
-      <c r="AA49" s="262"/>
-      <c r="AB49" s="262"/>
-      <c r="AC49" s="259"/>
-      <c r="AD49" s="258" t="s">
+      <c r="Z49" s="265"/>
+      <c r="AA49" s="265"/>
+      <c r="AB49" s="265"/>
+      <c r="AC49" s="266"/>
+      <c r="AD49" s="264" t="s">
         <v>50</v>
       </c>
-      <c r="AE49" s="259"/>
-      <c r="AF49" s="258" t="s">
+      <c r="AE49" s="266"/>
+      <c r="AF49" s="264" t="s">
         <v>51</v>
       </c>
-      <c r="AG49" s="259"/>
-      <c r="AH49" s="272" t="s">
+      <c r="AG49" s="266"/>
+      <c r="AH49" s="279" t="s">
         <v>52</v>
       </c>
-      <c r="AI49" s="273"/>
-      <c r="AJ49" s="274"/>
-      <c r="AK49" s="272" t="s">
+      <c r="AI49" s="280"/>
+      <c r="AJ49" s="281"/>
+      <c r="AK49" s="279" t="s">
         <v>53</v>
       </c>
-      <c r="AL49" s="274"/>
-      <c r="AM49" s="272" t="s">
+      <c r="AL49" s="281"/>
+      <c r="AM49" s="279" t="s">
         <v>54</v>
       </c>
-      <c r="AN49" s="273"/>
-      <c r="AO49" s="273"/>
-      <c r="AP49" s="274"/>
-      <c r="AQ49" s="258" t="s">
+      <c r="AN49" s="280"/>
+      <c r="AO49" s="280"/>
+      <c r="AP49" s="281"/>
+      <c r="AQ49" s="264" t="s">
         <v>15</v>
       </c>
-      <c r="AR49" s="262"/>
-      <c r="AS49" s="262"/>
-      <c r="AT49" s="262"/>
-      <c r="AU49" s="262"/>
-      <c r="AV49" s="262"/>
-      <c r="AW49" s="262"/>
-      <c r="AX49" s="262"/>
-      <c r="AY49" s="262"/>
-      <c r="AZ49" s="262"/>
-      <c r="BA49" s="262"/>
-      <c r="BB49" s="262"/>
-      <c r="BC49" s="262"/>
-      <c r="BD49" s="262"/>
-      <c r="BE49" s="259"/>
+      <c r="AR49" s="265"/>
+      <c r="AS49" s="265"/>
+      <c r="AT49" s="265"/>
+      <c r="AU49" s="265"/>
+      <c r="AV49" s="265"/>
+      <c r="AW49" s="265"/>
+      <c r="AX49" s="265"/>
+      <c r="AY49" s="265"/>
+      <c r="AZ49" s="265"/>
+      <c r="BA49" s="265"/>
+      <c r="BB49" s="265"/>
+      <c r="BC49" s="265"/>
+      <c r="BD49" s="265"/>
+      <c r="BE49" s="266"/>
       <c r="BG49" s="21" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="50" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B50" s="260"/>
-      <c r="C50" s="261"/>
-      <c r="D50" s="260"/>
-      <c r="E50" s="263"/>
-      <c r="F50" s="263"/>
-      <c r="G50" s="263"/>
-      <c r="H50" s="263"/>
-      <c r="I50" s="261"/>
-      <c r="J50" s="255" t="s">
+      <c r="B50" s="267"/>
+      <c r="C50" s="269"/>
+      <c r="D50" s="267"/>
+      <c r="E50" s="268"/>
+      <c r="F50" s="268"/>
+      <c r="G50" s="268"/>
+      <c r="H50" s="268"/>
+      <c r="I50" s="269"/>
+      <c r="J50" s="285" t="s">
         <v>14</v>
       </c>
-      <c r="K50" s="256"/>
-      <c r="L50" s="256"/>
-      <c r="M50" s="256"/>
-      <c r="N50" s="256"/>
-      <c r="O50" s="257"/>
-      <c r="P50" s="255" t="s">
+      <c r="K50" s="286"/>
+      <c r="L50" s="286"/>
+      <c r="M50" s="286"/>
+      <c r="N50" s="286"/>
+      <c r="O50" s="287"/>
+      <c r="P50" s="285" t="s">
         <v>24</v>
       </c>
-      <c r="Q50" s="256"/>
-      <c r="R50" s="256"/>
-      <c r="S50" s="256"/>
-      <c r="T50" s="256"/>
-      <c r="U50" s="257"/>
-      <c r="V50" s="267"/>
+      <c r="Q50" s="286"/>
+      <c r="R50" s="286"/>
+      <c r="S50" s="286"/>
+      <c r="T50" s="286"/>
+      <c r="U50" s="287"/>
+      <c r="V50" s="289"/>
       <c r="W50" s="114" t="s">
         <v>18</v>
       </c>
       <c r="X50" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="Y50" s="260"/>
-      <c r="Z50" s="263"/>
-      <c r="AA50" s="263"/>
-      <c r="AB50" s="263"/>
-      <c r="AC50" s="261"/>
-      <c r="AD50" s="260"/>
-      <c r="AE50" s="261"/>
-      <c r="AF50" s="260"/>
-      <c r="AG50" s="261"/>
-      <c r="AH50" s="275"/>
-      <c r="AI50" s="276"/>
-      <c r="AJ50" s="277"/>
-      <c r="AK50" s="275"/>
-      <c r="AL50" s="277"/>
-      <c r="AM50" s="275"/>
-      <c r="AN50" s="276"/>
-      <c r="AO50" s="276"/>
-      <c r="AP50" s="277"/>
-      <c r="AQ50" s="260"/>
-      <c r="AR50" s="263"/>
-      <c r="AS50" s="263"/>
-      <c r="AT50" s="263"/>
-      <c r="AU50" s="263"/>
-      <c r="AV50" s="263"/>
-      <c r="AW50" s="263"/>
-      <c r="AX50" s="263"/>
-      <c r="AY50" s="263"/>
-      <c r="AZ50" s="263"/>
-      <c r="BA50" s="263"/>
-      <c r="BB50" s="263"/>
-      <c r="BC50" s="263"/>
-      <c r="BD50" s="263"/>
-      <c r="BE50" s="261"/>
+      <c r="Y50" s="267"/>
+      <c r="Z50" s="268"/>
+      <c r="AA50" s="268"/>
+      <c r="AB50" s="268"/>
+      <c r="AC50" s="269"/>
+      <c r="AD50" s="267"/>
+      <c r="AE50" s="269"/>
+      <c r="AF50" s="267"/>
+      <c r="AG50" s="269"/>
+      <c r="AH50" s="282"/>
+      <c r="AI50" s="283"/>
+      <c r="AJ50" s="284"/>
+      <c r="AK50" s="282"/>
+      <c r="AL50" s="284"/>
+      <c r="AM50" s="282"/>
+      <c r="AN50" s="283"/>
+      <c r="AO50" s="283"/>
+      <c r="AP50" s="284"/>
+      <c r="AQ50" s="267"/>
+      <c r="AR50" s="268"/>
+      <c r="AS50" s="268"/>
+      <c r="AT50" s="268"/>
+      <c r="AU50" s="268"/>
+      <c r="AV50" s="268"/>
+      <c r="AW50" s="268"/>
+      <c r="AX50" s="268"/>
+      <c r="AY50" s="268"/>
+      <c r="AZ50" s="268"/>
+      <c r="BA50" s="268"/>
+      <c r="BB50" s="268"/>
+      <c r="BC50" s="268"/>
+      <c r="BD50" s="268"/>
+      <c r="BE50" s="269"/>
       <c r="BG50" s="21" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="51" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B51" s="268">
+      <c r="B51" s="254">
         <v>1</v>
       </c>
-      <c r="C51" s="269"/>
+      <c r="C51" s="255"/>
       <c r="D51" s="112" t="s">
         <v>106</v>
       </c>
@@ -7918,95 +7918,95 @@
       <c r="AN51" s="110"/>
       <c r="AO51" s="110"/>
       <c r="AP51" s="111"/>
-      <c r="AQ51" s="248" t="s">
+      <c r="AQ51" s="273" t="s">
         <v>153</v>
       </c>
-      <c r="AR51" s="249"/>
-      <c r="AS51" s="249"/>
-      <c r="AT51" s="249"/>
-      <c r="AU51" s="249"/>
-      <c r="AV51" s="249"/>
-      <c r="AW51" s="249"/>
-      <c r="AX51" s="249"/>
-      <c r="AY51" s="249"/>
-      <c r="AZ51" s="249"/>
-      <c r="BA51" s="249"/>
-      <c r="BB51" s="249"/>
-      <c r="BC51" s="249"/>
-      <c r="BD51" s="249"/>
-      <c r="BE51" s="250"/>
+      <c r="AR51" s="274"/>
+      <c r="AS51" s="274"/>
+      <c r="AT51" s="274"/>
+      <c r="AU51" s="274"/>
+      <c r="AV51" s="274"/>
+      <c r="AW51" s="274"/>
+      <c r="AX51" s="274"/>
+      <c r="AY51" s="274"/>
+      <c r="AZ51" s="274"/>
+      <c r="BA51" s="274"/>
+      <c r="BB51" s="274"/>
+      <c r="BC51" s="274"/>
+      <c r="BD51" s="274"/>
+      <c r="BE51" s="275"/>
       <c r="BG51" s="21" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="52" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B52" s="270" t="s">
+      <c r="B52" s="256" t="s">
         <v>30</v>
       </c>
-      <c r="C52" s="270"/>
-      <c r="D52" s="270"/>
-      <c r="E52" s="270"/>
-      <c r="F52" s="270"/>
-      <c r="G52" s="270"/>
-      <c r="H52" s="270"/>
-      <c r="I52" s="270"/>
-      <c r="J52" s="270"/>
-      <c r="K52" s="270"/>
-      <c r="L52" s="270"/>
-      <c r="M52" s="270"/>
-      <c r="N52" s="270"/>
-      <c r="O52" s="270"/>
-      <c r="P52" s="270"/>
-      <c r="Q52" s="270"/>
-      <c r="R52" s="270"/>
-      <c r="S52" s="270"/>
-      <c r="T52" s="270"/>
-      <c r="U52" s="270"/>
-      <c r="V52" s="270"/>
-      <c r="W52" s="270"/>
-      <c r="X52" s="270"/>
-      <c r="Y52" s="271"/>
-      <c r="Z52" s="271"/>
-      <c r="AA52" s="271"/>
-      <c r="AB52" s="271"/>
-      <c r="AC52" s="271"/>
-      <c r="AD52" s="271"/>
-      <c r="AE52" s="271"/>
-      <c r="AF52" s="270"/>
-      <c r="AG52" s="270"/>
-      <c r="AH52" s="271"/>
-      <c r="AI52" s="271"/>
-      <c r="AJ52" s="271"/>
-      <c r="AK52" s="271"/>
-      <c r="AL52" s="271"/>
-      <c r="AM52" s="271"/>
-      <c r="AN52" s="271"/>
-      <c r="AO52" s="271"/>
-      <c r="AP52" s="271"/>
-      <c r="AQ52" s="270"/>
-      <c r="AR52" s="270"/>
-      <c r="AS52" s="270"/>
-      <c r="AT52" s="270"/>
-      <c r="AU52" s="270"/>
-      <c r="AV52" s="270"/>
-      <c r="AW52" s="270"/>
-      <c r="AX52" s="270"/>
-      <c r="AY52" s="270"/>
-      <c r="AZ52" s="270"/>
-      <c r="BA52" s="270"/>
-      <c r="BB52" s="270"/>
-      <c r="BC52" s="270"/>
-      <c r="BD52" s="270"/>
-      <c r="BE52" s="270"/>
+      <c r="C52" s="256"/>
+      <c r="D52" s="256"/>
+      <c r="E52" s="256"/>
+      <c r="F52" s="256"/>
+      <c r="G52" s="256"/>
+      <c r="H52" s="256"/>
+      <c r="I52" s="256"/>
+      <c r="J52" s="256"/>
+      <c r="K52" s="256"/>
+      <c r="L52" s="256"/>
+      <c r="M52" s="256"/>
+      <c r="N52" s="256"/>
+      <c r="O52" s="256"/>
+      <c r="P52" s="256"/>
+      <c r="Q52" s="256"/>
+      <c r="R52" s="256"/>
+      <c r="S52" s="256"/>
+      <c r="T52" s="256"/>
+      <c r="U52" s="256"/>
+      <c r="V52" s="256"/>
+      <c r="W52" s="256"/>
+      <c r="X52" s="256"/>
+      <c r="Y52" s="257"/>
+      <c r="Z52" s="257"/>
+      <c r="AA52" s="257"/>
+      <c r="AB52" s="257"/>
+      <c r="AC52" s="257"/>
+      <c r="AD52" s="257"/>
+      <c r="AE52" s="257"/>
+      <c r="AF52" s="256"/>
+      <c r="AG52" s="256"/>
+      <c r="AH52" s="257"/>
+      <c r="AI52" s="257"/>
+      <c r="AJ52" s="257"/>
+      <c r="AK52" s="257"/>
+      <c r="AL52" s="257"/>
+      <c r="AM52" s="257"/>
+      <c r="AN52" s="257"/>
+      <c r="AO52" s="257"/>
+      <c r="AP52" s="257"/>
+      <c r="AQ52" s="256"/>
+      <c r="AR52" s="256"/>
+      <c r="AS52" s="256"/>
+      <c r="AT52" s="256"/>
+      <c r="AU52" s="256"/>
+      <c r="AV52" s="256"/>
+      <c r="AW52" s="256"/>
+      <c r="AX52" s="256"/>
+      <c r="AY52" s="256"/>
+      <c r="AZ52" s="256"/>
+      <c r="BA52" s="256"/>
+      <c r="BB52" s="256"/>
+      <c r="BC52" s="256"/>
+      <c r="BD52" s="256"/>
+      <c r="BE52" s="256"/>
       <c r="BG52" s="21" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="53" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B53" s="264">
+      <c r="B53" s="246">
         <v>2</v>
       </c>
-      <c r="C53" s="265"/>
+      <c r="C53" s="247"/>
       <c r="D53" s="22" t="s">
         <v>107</v>
       </c>
@@ -8056,21 +8056,21 @@
       <c r="AN53" s="42"/>
       <c r="AO53" s="42"/>
       <c r="AP53" s="43"/>
-      <c r="AQ53" s="245"/>
-      <c r="AR53" s="246"/>
-      <c r="AS53" s="246"/>
-      <c r="AT53" s="246"/>
-      <c r="AU53" s="246"/>
-      <c r="AV53" s="246"/>
-      <c r="AW53" s="246"/>
-      <c r="AX53" s="246"/>
-      <c r="AY53" s="246"/>
-      <c r="AZ53" s="246"/>
-      <c r="BA53" s="246"/>
-      <c r="BB53" s="246"/>
-      <c r="BC53" s="246"/>
-      <c r="BD53" s="246"/>
-      <c r="BE53" s="247"/>
+      <c r="AQ53" s="261"/>
+      <c r="AR53" s="262"/>
+      <c r="AS53" s="262"/>
+      <c r="AT53" s="262"/>
+      <c r="AU53" s="262"/>
+      <c r="AV53" s="262"/>
+      <c r="AW53" s="262"/>
+      <c r="AX53" s="262"/>
+      <c r="AY53" s="262"/>
+      <c r="AZ53" s="262"/>
+      <c r="BA53" s="262"/>
+      <c r="BB53" s="262"/>
+      <c r="BC53" s="262"/>
+      <c r="BD53" s="262"/>
+      <c r="BE53" s="263"/>
       <c r="BI53" s="21" t="s">
         <v>66</v>
       </c>
@@ -8079,10 +8079,10 @@
       </c>
     </row>
     <row r="54" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B54" s="264">
+      <c r="B54" s="246">
         <v>3</v>
       </c>
-      <c r="C54" s="265"/>
+      <c r="C54" s="247"/>
       <c r="D54" s="22" t="s">
         <v>108</v>
       </c>
@@ -8132,31 +8132,31 @@
       <c r="AN54" s="42"/>
       <c r="AO54" s="42"/>
       <c r="AP54" s="43"/>
-      <c r="AQ54" s="245"/>
-      <c r="AR54" s="246"/>
-      <c r="AS54" s="246"/>
-      <c r="AT54" s="246"/>
-      <c r="AU54" s="246"/>
-      <c r="AV54" s="246"/>
-      <c r="AW54" s="246"/>
-      <c r="AX54" s="246"/>
-      <c r="AY54" s="246"/>
-      <c r="AZ54" s="246"/>
-      <c r="BA54" s="246"/>
-      <c r="BB54" s="246"/>
-      <c r="BC54" s="246"/>
-      <c r="BD54" s="246"/>
-      <c r="BE54" s="247"/>
+      <c r="AQ54" s="261"/>
+      <c r="AR54" s="262"/>
+      <c r="AS54" s="262"/>
+      <c r="AT54" s="262"/>
+      <c r="AU54" s="262"/>
+      <c r="AV54" s="262"/>
+      <c r="AW54" s="262"/>
+      <c r="AX54" s="262"/>
+      <c r="AY54" s="262"/>
+      <c r="AZ54" s="262"/>
+      <c r="BA54" s="262"/>
+      <c r="BB54" s="262"/>
+      <c r="BC54" s="262"/>
+      <c r="BD54" s="262"/>
+      <c r="BE54" s="263"/>
       <c r="BJ54" s="21" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="55" spans="1:62" s="176" customFormat="1" ht="14.1" customHeight="1">
       <c r="A55" s="175"/>
-      <c r="B55" s="264">
+      <c r="B55" s="246">
         <v>4</v>
       </c>
-      <c r="C55" s="265"/>
+      <c r="C55" s="247"/>
       <c r="D55" s="22" t="s">
         <v>284</v>
       </c>
@@ -8206,28 +8206,28 @@
       <c r="AN55" s="42"/>
       <c r="AO55" s="42"/>
       <c r="AP55" s="43"/>
-      <c r="AQ55" s="245"/>
-      <c r="AR55" s="246"/>
-      <c r="AS55" s="246"/>
-      <c r="AT55" s="246"/>
-      <c r="AU55" s="246"/>
-      <c r="AV55" s="246"/>
-      <c r="AW55" s="246"/>
-      <c r="AX55" s="246"/>
-      <c r="AY55" s="246"/>
-      <c r="AZ55" s="246"/>
-      <c r="BA55" s="246"/>
-      <c r="BB55" s="246"/>
-      <c r="BC55" s="246"/>
-      <c r="BD55" s="246"/>
-      <c r="BE55" s="247"/>
+      <c r="AQ55" s="261"/>
+      <c r="AR55" s="262"/>
+      <c r="AS55" s="262"/>
+      <c r="AT55" s="262"/>
+      <c r="AU55" s="262"/>
+      <c r="AV55" s="262"/>
+      <c r="AW55" s="262"/>
+      <c r="AX55" s="262"/>
+      <c r="AY55" s="262"/>
+      <c r="AZ55" s="262"/>
+      <c r="BA55" s="262"/>
+      <c r="BB55" s="262"/>
+      <c r="BC55" s="262"/>
+      <c r="BD55" s="262"/>
+      <c r="BE55" s="263"/>
     </row>
     <row r="56" spans="1:62" s="176" customFormat="1" ht="14.1" customHeight="1">
       <c r="A56" s="175"/>
-      <c r="B56" s="264">
+      <c r="B56" s="246">
         <v>5</v>
       </c>
-      <c r="C56" s="265"/>
+      <c r="C56" s="247"/>
       <c r="D56" s="22" t="s">
         <v>56</v>
       </c>
@@ -8264,10 +8264,10 @@
       <c r="AA56" s="42"/>
       <c r="AB56" s="42"/>
       <c r="AC56" s="43"/>
-      <c r="AD56" s="245">
+      <c r="AD56" s="261">
         <v>100</v>
       </c>
-      <c r="AE56" s="247"/>
+      <c r="AE56" s="263"/>
       <c r="AF56" s="22">
         <v>20</v>
       </c>
@@ -8285,27 +8285,27 @@
       <c r="AN56" s="42"/>
       <c r="AO56" s="42"/>
       <c r="AP56" s="43"/>
-      <c r="AQ56" s="245"/>
-      <c r="AR56" s="246"/>
-      <c r="AS56" s="246"/>
-      <c r="AT56" s="246"/>
-      <c r="AU56" s="246"/>
-      <c r="AV56" s="246"/>
-      <c r="AW56" s="246"/>
-      <c r="AX56" s="246"/>
-      <c r="AY56" s="246"/>
-      <c r="AZ56" s="246"/>
-      <c r="BA56" s="246"/>
-      <c r="BB56" s="246"/>
-      <c r="BC56" s="246"/>
-      <c r="BD56" s="246"/>
-      <c r="BE56" s="247"/>
+      <c r="AQ56" s="261"/>
+      <c r="AR56" s="262"/>
+      <c r="AS56" s="262"/>
+      <c r="AT56" s="262"/>
+      <c r="AU56" s="262"/>
+      <c r="AV56" s="262"/>
+      <c r="AW56" s="262"/>
+      <c r="AX56" s="262"/>
+      <c r="AY56" s="262"/>
+      <c r="AZ56" s="262"/>
+      <c r="BA56" s="262"/>
+      <c r="BB56" s="262"/>
+      <c r="BC56" s="262"/>
+      <c r="BD56" s="262"/>
+      <c r="BE56" s="263"/>
     </row>
     <row r="57" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B57" s="264">
+      <c r="B57" s="246">
         <v>6</v>
       </c>
-      <c r="C57" s="265"/>
+      <c r="C57" s="247"/>
       <c r="D57" s="22" t="s">
         <v>5</v>
       </c>
@@ -8355,27 +8355,27 @@
       <c r="AN57" s="42"/>
       <c r="AO57" s="42"/>
       <c r="AP57" s="43"/>
-      <c r="AQ57" s="245"/>
-      <c r="AR57" s="246"/>
-      <c r="AS57" s="246"/>
-      <c r="AT57" s="246"/>
-      <c r="AU57" s="246"/>
-      <c r="AV57" s="246"/>
-      <c r="AW57" s="246"/>
-      <c r="AX57" s="246"/>
-      <c r="AY57" s="246"/>
-      <c r="AZ57" s="246"/>
-      <c r="BA57" s="246"/>
-      <c r="BB57" s="246"/>
-      <c r="BC57" s="246"/>
-      <c r="BD57" s="246"/>
-      <c r="BE57" s="247"/>
+      <c r="AQ57" s="261"/>
+      <c r="AR57" s="262"/>
+      <c r="AS57" s="262"/>
+      <c r="AT57" s="262"/>
+      <c r="AU57" s="262"/>
+      <c r="AV57" s="262"/>
+      <c r="AW57" s="262"/>
+      <c r="AX57" s="262"/>
+      <c r="AY57" s="262"/>
+      <c r="AZ57" s="262"/>
+      <c r="BA57" s="262"/>
+      <c r="BB57" s="262"/>
+      <c r="BC57" s="262"/>
+      <c r="BD57" s="262"/>
+      <c r="BE57" s="263"/>
     </row>
     <row r="58" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B58" s="264">
+      <c r="B58" s="246">
         <v>7</v>
       </c>
-      <c r="C58" s="265"/>
+      <c r="C58" s="247"/>
       <c r="D58" s="22" t="s">
         <v>56</v>
       </c>
@@ -8434,29 +8434,29 @@
       <c r="AN58" s="42"/>
       <c r="AO58" s="42"/>
       <c r="AP58" s="43"/>
-      <c r="AQ58" s="245" t="s">
+      <c r="AQ58" s="261" t="s">
         <v>221</v>
       </c>
-      <c r="AR58" s="246"/>
-      <c r="AS58" s="246"/>
-      <c r="AT58" s="246"/>
-      <c r="AU58" s="246"/>
-      <c r="AV58" s="246"/>
-      <c r="AW58" s="246"/>
-      <c r="AX58" s="246"/>
-      <c r="AY58" s="246"/>
-      <c r="AZ58" s="246"/>
-      <c r="BA58" s="246"/>
-      <c r="BB58" s="246"/>
-      <c r="BC58" s="246"/>
-      <c r="BD58" s="246"/>
-      <c r="BE58" s="247"/>
+      <c r="AR58" s="262"/>
+      <c r="AS58" s="262"/>
+      <c r="AT58" s="262"/>
+      <c r="AU58" s="262"/>
+      <c r="AV58" s="262"/>
+      <c r="AW58" s="262"/>
+      <c r="AX58" s="262"/>
+      <c r="AY58" s="262"/>
+      <c r="AZ58" s="262"/>
+      <c r="BA58" s="262"/>
+      <c r="BB58" s="262"/>
+      <c r="BC58" s="262"/>
+      <c r="BD58" s="262"/>
+      <c r="BE58" s="263"/>
     </row>
     <row r="59" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B59" s="264">
+      <c r="B59" s="246">
         <v>8</v>
       </c>
-      <c r="C59" s="265"/>
+      <c r="C59" s="247"/>
       <c r="D59" s="22" t="s">
         <v>382</v>
       </c>
@@ -8506,27 +8506,27 @@
       <c r="AN59" s="42"/>
       <c r="AO59" s="42"/>
       <c r="AP59" s="43"/>
-      <c r="AQ59" s="245"/>
-      <c r="AR59" s="246"/>
-      <c r="AS59" s="246"/>
-      <c r="AT59" s="246"/>
-      <c r="AU59" s="246"/>
-      <c r="AV59" s="246"/>
-      <c r="AW59" s="246"/>
-      <c r="AX59" s="246"/>
-      <c r="AY59" s="246"/>
-      <c r="AZ59" s="246"/>
-      <c r="BA59" s="246"/>
-      <c r="BB59" s="246"/>
-      <c r="BC59" s="246"/>
-      <c r="BD59" s="246"/>
-      <c r="BE59" s="247"/>
+      <c r="AQ59" s="261"/>
+      <c r="AR59" s="262"/>
+      <c r="AS59" s="262"/>
+      <c r="AT59" s="262"/>
+      <c r="AU59" s="262"/>
+      <c r="AV59" s="262"/>
+      <c r="AW59" s="262"/>
+      <c r="AX59" s="262"/>
+      <c r="AY59" s="262"/>
+      <c r="AZ59" s="262"/>
+      <c r="BA59" s="262"/>
+      <c r="BB59" s="262"/>
+      <c r="BC59" s="262"/>
+      <c r="BD59" s="262"/>
+      <c r="BE59" s="263"/>
     </row>
     <row r="60" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B60" s="264">
+      <c r="B60" s="246">
         <v>9</v>
       </c>
-      <c r="C60" s="265"/>
+      <c r="C60" s="247"/>
       <c r="D60" s="22" t="s">
         <v>56</v>
       </c>
@@ -8586,27 +8586,27 @@
       <c r="AN60" s="42"/>
       <c r="AO60" s="42"/>
       <c r="AP60" s="43"/>
-      <c r="AQ60" s="245"/>
-      <c r="AR60" s="246"/>
-      <c r="AS60" s="246"/>
-      <c r="AT60" s="246"/>
-      <c r="AU60" s="246"/>
-      <c r="AV60" s="246"/>
-      <c r="AW60" s="246"/>
-      <c r="AX60" s="246"/>
-      <c r="AY60" s="246"/>
-      <c r="AZ60" s="246"/>
-      <c r="BA60" s="246"/>
-      <c r="BB60" s="246"/>
-      <c r="BC60" s="246"/>
-      <c r="BD60" s="246"/>
-      <c r="BE60" s="247"/>
+      <c r="AQ60" s="261"/>
+      <c r="AR60" s="262"/>
+      <c r="AS60" s="262"/>
+      <c r="AT60" s="262"/>
+      <c r="AU60" s="262"/>
+      <c r="AV60" s="262"/>
+      <c r="AW60" s="262"/>
+      <c r="AX60" s="262"/>
+      <c r="AY60" s="262"/>
+      <c r="AZ60" s="262"/>
+      <c r="BA60" s="262"/>
+      <c r="BB60" s="262"/>
+      <c r="BC60" s="262"/>
+      <c r="BD60" s="262"/>
+      <c r="BE60" s="263"/>
     </row>
     <row r="61" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B61" s="264">
+      <c r="B61" s="246">
         <v>10</v>
       </c>
-      <c r="C61" s="265"/>
+      <c r="C61" s="247"/>
       <c r="D61" s="22" t="s">
         <v>56</v>
       </c>
@@ -8666,27 +8666,27 @@
       <c r="AN61" s="42"/>
       <c r="AO61" s="42"/>
       <c r="AP61" s="43"/>
-      <c r="AQ61" s="245"/>
-      <c r="AR61" s="246"/>
-      <c r="AS61" s="246"/>
-      <c r="AT61" s="246"/>
-      <c r="AU61" s="246"/>
-      <c r="AV61" s="246"/>
-      <c r="AW61" s="246"/>
-      <c r="AX61" s="246"/>
-      <c r="AY61" s="246"/>
-      <c r="AZ61" s="246"/>
-      <c r="BA61" s="246"/>
-      <c r="BB61" s="246"/>
-      <c r="BC61" s="246"/>
-      <c r="BD61" s="246"/>
-      <c r="BE61" s="247"/>
+      <c r="AQ61" s="261"/>
+      <c r="AR61" s="262"/>
+      <c r="AS61" s="262"/>
+      <c r="AT61" s="262"/>
+      <c r="AU61" s="262"/>
+      <c r="AV61" s="262"/>
+      <c r="AW61" s="262"/>
+      <c r="AX61" s="262"/>
+      <c r="AY61" s="262"/>
+      <c r="AZ61" s="262"/>
+      <c r="BA61" s="262"/>
+      <c r="BB61" s="262"/>
+      <c r="BC61" s="262"/>
+      <c r="BD61" s="262"/>
+      <c r="BE61" s="263"/>
     </row>
     <row r="62" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B62" s="264">
+      <c r="B62" s="246">
         <v>11</v>
       </c>
-      <c r="C62" s="265"/>
+      <c r="C62" s="247"/>
       <c r="D62" s="22" t="s">
         <v>112</v>
       </c>
@@ -8736,27 +8736,27 @@
       <c r="AN62" s="42"/>
       <c r="AO62" s="42"/>
       <c r="AP62" s="43"/>
-      <c r="AQ62" s="245"/>
-      <c r="AR62" s="246"/>
-      <c r="AS62" s="246"/>
-      <c r="AT62" s="246"/>
-      <c r="AU62" s="246"/>
-      <c r="AV62" s="246"/>
-      <c r="AW62" s="246"/>
-      <c r="AX62" s="246"/>
-      <c r="AY62" s="246"/>
-      <c r="AZ62" s="246"/>
-      <c r="BA62" s="246"/>
-      <c r="BB62" s="246"/>
-      <c r="BC62" s="246"/>
-      <c r="BD62" s="246"/>
-      <c r="BE62" s="247"/>
+      <c r="AQ62" s="261"/>
+      <c r="AR62" s="262"/>
+      <c r="AS62" s="262"/>
+      <c r="AT62" s="262"/>
+      <c r="AU62" s="262"/>
+      <c r="AV62" s="262"/>
+      <c r="AW62" s="262"/>
+      <c r="AX62" s="262"/>
+      <c r="AY62" s="262"/>
+      <c r="AZ62" s="262"/>
+      <c r="BA62" s="262"/>
+      <c r="BB62" s="262"/>
+      <c r="BC62" s="262"/>
+      <c r="BD62" s="262"/>
+      <c r="BE62" s="263"/>
     </row>
     <row r="63" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B63" s="264">
+      <c r="B63" s="246">
         <v>12</v>
       </c>
-      <c r="C63" s="265"/>
+      <c r="C63" s="247"/>
       <c r="D63" s="22" t="s">
         <v>113</v>
       </c>
@@ -8808,29 +8808,29 @@
       <c r="AN63" s="42"/>
       <c r="AO63" s="42"/>
       <c r="AP63" s="43"/>
-      <c r="AQ63" s="245" t="s">
+      <c r="AQ63" s="261" t="s">
         <v>297</v>
       </c>
-      <c r="AR63" s="246"/>
-      <c r="AS63" s="246"/>
-      <c r="AT63" s="246"/>
-      <c r="AU63" s="246"/>
-      <c r="AV63" s="246"/>
-      <c r="AW63" s="246"/>
-      <c r="AX63" s="246"/>
-      <c r="AY63" s="246"/>
-      <c r="AZ63" s="246"/>
-      <c r="BA63" s="246"/>
-      <c r="BB63" s="246"/>
-      <c r="BC63" s="246"/>
-      <c r="BD63" s="246"/>
-      <c r="BE63" s="247"/>
+      <c r="AR63" s="262"/>
+      <c r="AS63" s="262"/>
+      <c r="AT63" s="262"/>
+      <c r="AU63" s="262"/>
+      <c r="AV63" s="262"/>
+      <c r="AW63" s="262"/>
+      <c r="AX63" s="262"/>
+      <c r="AY63" s="262"/>
+      <c r="AZ63" s="262"/>
+      <c r="BA63" s="262"/>
+      <c r="BB63" s="262"/>
+      <c r="BC63" s="262"/>
+      <c r="BD63" s="262"/>
+      <c r="BE63" s="263"/>
     </row>
     <row r="64" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B64" s="264">
+      <c r="B64" s="246">
         <v>13</v>
       </c>
-      <c r="C64" s="265"/>
+      <c r="C64" s="247"/>
       <c r="D64" s="22" t="s">
         <v>114</v>
       </c>
@@ -8880,27 +8880,27 @@
       <c r="AN64" s="42"/>
       <c r="AO64" s="42"/>
       <c r="AP64" s="43"/>
-      <c r="AQ64" s="245"/>
-      <c r="AR64" s="246"/>
-      <c r="AS64" s="246"/>
-      <c r="AT64" s="246"/>
-      <c r="AU64" s="246"/>
-      <c r="AV64" s="246"/>
-      <c r="AW64" s="246"/>
-      <c r="AX64" s="246"/>
-      <c r="AY64" s="246"/>
-      <c r="AZ64" s="246"/>
-      <c r="BA64" s="246"/>
-      <c r="BB64" s="246"/>
-      <c r="BC64" s="246"/>
-      <c r="BD64" s="246"/>
-      <c r="BE64" s="247"/>
+      <c r="AQ64" s="261"/>
+      <c r="AR64" s="262"/>
+      <c r="AS64" s="262"/>
+      <c r="AT64" s="262"/>
+      <c r="AU64" s="262"/>
+      <c r="AV64" s="262"/>
+      <c r="AW64" s="262"/>
+      <c r="AX64" s="262"/>
+      <c r="AY64" s="262"/>
+      <c r="AZ64" s="262"/>
+      <c r="BA64" s="262"/>
+      <c r="BB64" s="262"/>
+      <c r="BC64" s="262"/>
+      <c r="BD64" s="262"/>
+      <c r="BE64" s="263"/>
     </row>
     <row r="65" spans="1:58" ht="14.1" customHeight="1">
-      <c r="B65" s="264">
+      <c r="B65" s="246">
         <v>14</v>
       </c>
-      <c r="C65" s="265"/>
+      <c r="C65" s="247"/>
       <c r="D65" s="22" t="s">
         <v>113</v>
       </c>
@@ -8952,29 +8952,29 @@
       <c r="AN65" s="42"/>
       <c r="AO65" s="42"/>
       <c r="AP65" s="43"/>
-      <c r="AQ65" s="245" t="s">
+      <c r="AQ65" s="261" t="s">
         <v>297</v>
       </c>
-      <c r="AR65" s="246"/>
-      <c r="AS65" s="246"/>
-      <c r="AT65" s="246"/>
-      <c r="AU65" s="246"/>
-      <c r="AV65" s="246"/>
-      <c r="AW65" s="246"/>
-      <c r="AX65" s="246"/>
-      <c r="AY65" s="246"/>
-      <c r="AZ65" s="246"/>
-      <c r="BA65" s="246"/>
-      <c r="BB65" s="246"/>
-      <c r="BC65" s="246"/>
-      <c r="BD65" s="246"/>
-      <c r="BE65" s="247"/>
+      <c r="AR65" s="262"/>
+      <c r="AS65" s="262"/>
+      <c r="AT65" s="262"/>
+      <c r="AU65" s="262"/>
+      <c r="AV65" s="262"/>
+      <c r="AW65" s="262"/>
+      <c r="AX65" s="262"/>
+      <c r="AY65" s="262"/>
+      <c r="AZ65" s="262"/>
+      <c r="BA65" s="262"/>
+      <c r="BB65" s="262"/>
+      <c r="BC65" s="262"/>
+      <c r="BD65" s="262"/>
+      <c r="BE65" s="263"/>
     </row>
     <row r="66" spans="1:58" ht="14.1" customHeight="1">
-      <c r="B66" s="264">
+      <c r="B66" s="246">
         <v>15</v>
       </c>
-      <c r="C66" s="265"/>
+      <c r="C66" s="247"/>
       <c r="D66" s="22" t="s">
         <v>115</v>
       </c>
@@ -9024,27 +9024,27 @@
       <c r="AN66" s="42"/>
       <c r="AO66" s="42"/>
       <c r="AP66" s="43"/>
-      <c r="AQ66" s="245"/>
-      <c r="AR66" s="246"/>
-      <c r="AS66" s="246"/>
-      <c r="AT66" s="246"/>
-      <c r="AU66" s="246"/>
-      <c r="AV66" s="246"/>
-      <c r="AW66" s="246"/>
-      <c r="AX66" s="246"/>
-      <c r="AY66" s="246"/>
-      <c r="AZ66" s="246"/>
-      <c r="BA66" s="246"/>
-      <c r="BB66" s="246"/>
-      <c r="BC66" s="246"/>
-      <c r="BD66" s="246"/>
-      <c r="BE66" s="247"/>
+      <c r="AQ66" s="261"/>
+      <c r="AR66" s="262"/>
+      <c r="AS66" s="262"/>
+      <c r="AT66" s="262"/>
+      <c r="AU66" s="262"/>
+      <c r="AV66" s="262"/>
+      <c r="AW66" s="262"/>
+      <c r="AX66" s="262"/>
+      <c r="AY66" s="262"/>
+      <c r="AZ66" s="262"/>
+      <c r="BA66" s="262"/>
+      <c r="BB66" s="262"/>
+      <c r="BC66" s="262"/>
+      <c r="BD66" s="262"/>
+      <c r="BE66" s="263"/>
     </row>
     <row r="67" spans="1:58" ht="14.1" customHeight="1">
-      <c r="B67" s="264">
+      <c r="B67" s="246">
         <v>16</v>
       </c>
-      <c r="C67" s="265"/>
+      <c r="C67" s="247"/>
       <c r="D67" s="22" t="s">
         <v>113</v>
       </c>
@@ -9096,30 +9096,30 @@
       <c r="AN67" s="42"/>
       <c r="AO67" s="42"/>
       <c r="AP67" s="43"/>
-      <c r="AQ67" s="245" t="s">
+      <c r="AQ67" s="261" t="s">
         <v>297</v>
       </c>
-      <c r="AR67" s="246"/>
-      <c r="AS67" s="246"/>
-      <c r="AT67" s="246"/>
-      <c r="AU67" s="246"/>
-      <c r="AV67" s="246"/>
-      <c r="AW67" s="246"/>
-      <c r="AX67" s="246"/>
-      <c r="AY67" s="246"/>
-      <c r="AZ67" s="246"/>
-      <c r="BA67" s="246"/>
-      <c r="BB67" s="246"/>
-      <c r="BC67" s="246"/>
-      <c r="BD67" s="246"/>
-      <c r="BE67" s="247"/>
+      <c r="AR67" s="262"/>
+      <c r="AS67" s="262"/>
+      <c r="AT67" s="262"/>
+      <c r="AU67" s="262"/>
+      <c r="AV67" s="262"/>
+      <c r="AW67" s="262"/>
+      <c r="AX67" s="262"/>
+      <c r="AY67" s="262"/>
+      <c r="AZ67" s="262"/>
+      <c r="BA67" s="262"/>
+      <c r="BB67" s="262"/>
+      <c r="BC67" s="262"/>
+      <c r="BD67" s="262"/>
+      <c r="BE67" s="263"/>
     </row>
     <row r="68" spans="1:58" s="21" customFormat="1" ht="14.4" customHeight="1">
       <c r="A68" s="6"/>
-      <c r="B68" s="264">
+      <c r="B68" s="246">
         <v>17</v>
       </c>
-      <c r="C68" s="265"/>
+      <c r="C68" s="247"/>
       <c r="D68" s="22" t="s">
         <v>147</v>
       </c>
@@ -9169,31 +9169,31 @@
       <c r="AN68" s="100"/>
       <c r="AO68" s="100"/>
       <c r="AP68" s="101"/>
-      <c r="AQ68" s="245" t="s">
+      <c r="AQ68" s="261" t="s">
         <v>154</v>
       </c>
-      <c r="AR68" s="246"/>
-      <c r="AS68" s="246"/>
-      <c r="AT68" s="246"/>
-      <c r="AU68" s="246"/>
-      <c r="AV68" s="246"/>
-      <c r="AW68" s="246"/>
-      <c r="AX68" s="246"/>
-      <c r="AY68" s="246"/>
-      <c r="AZ68" s="246"/>
-      <c r="BA68" s="246"/>
-      <c r="BB68" s="246"/>
-      <c r="BC68" s="246"/>
-      <c r="BD68" s="246"/>
-      <c r="BE68" s="247"/>
+      <c r="AR68" s="262"/>
+      <c r="AS68" s="262"/>
+      <c r="AT68" s="262"/>
+      <c r="AU68" s="262"/>
+      <c r="AV68" s="262"/>
+      <c r="AW68" s="262"/>
+      <c r="AX68" s="262"/>
+      <c r="AY68" s="262"/>
+      <c r="AZ68" s="262"/>
+      <c r="BA68" s="262"/>
+      <c r="BB68" s="262"/>
+      <c r="BC68" s="262"/>
+      <c r="BD68" s="262"/>
+      <c r="BE68" s="263"/>
       <c r="BF68" s="11"/>
     </row>
     <row r="69" spans="1:58" s="21" customFormat="1" ht="14.4" customHeight="1">
       <c r="A69" s="6"/>
-      <c r="B69" s="264">
+      <c r="B69" s="246">
         <v>18</v>
       </c>
-      <c r="C69" s="265"/>
+      <c r="C69" s="247"/>
       <c r="D69" s="22" t="s">
         <v>109</v>
       </c>
@@ -9243,29 +9243,29 @@
       <c r="AN69" s="42"/>
       <c r="AO69" s="42"/>
       <c r="AP69" s="43"/>
-      <c r="AQ69" s="245"/>
-      <c r="AR69" s="246"/>
-      <c r="AS69" s="246"/>
-      <c r="AT69" s="246"/>
-      <c r="AU69" s="246"/>
-      <c r="AV69" s="246"/>
-      <c r="AW69" s="246"/>
-      <c r="AX69" s="246"/>
-      <c r="AY69" s="246"/>
-      <c r="AZ69" s="246"/>
-      <c r="BA69" s="246"/>
-      <c r="BB69" s="246"/>
-      <c r="BC69" s="246"/>
-      <c r="BD69" s="246"/>
-      <c r="BE69" s="247"/>
+      <c r="AQ69" s="261"/>
+      <c r="AR69" s="262"/>
+      <c r="AS69" s="262"/>
+      <c r="AT69" s="262"/>
+      <c r="AU69" s="262"/>
+      <c r="AV69" s="262"/>
+      <c r="AW69" s="262"/>
+      <c r="AX69" s="262"/>
+      <c r="AY69" s="262"/>
+      <c r="AZ69" s="262"/>
+      <c r="BA69" s="262"/>
+      <c r="BB69" s="262"/>
+      <c r="BC69" s="262"/>
+      <c r="BD69" s="262"/>
+      <c r="BE69" s="263"/>
       <c r="BF69" s="11"/>
     </row>
     <row r="70" spans="1:58" s="21" customFormat="1" ht="28.8" customHeight="1">
       <c r="A70" s="6"/>
-      <c r="B70" s="264">
+      <c r="B70" s="246">
         <v>19</v>
       </c>
-      <c r="C70" s="265"/>
+      <c r="C70" s="247"/>
       <c r="D70" s="22" t="s">
         <v>116</v>
       </c>
@@ -9315,92 +9315,92 @@
       <c r="AN70" s="42"/>
       <c r="AO70" s="42"/>
       <c r="AP70" s="43"/>
-      <c r="AQ70" s="284" t="s">
+      <c r="AQ70" s="258" t="s">
         <v>392</v>
       </c>
-      <c r="AR70" s="285"/>
-      <c r="AS70" s="285"/>
-      <c r="AT70" s="285"/>
-      <c r="AU70" s="285"/>
-      <c r="AV70" s="285"/>
-      <c r="AW70" s="285"/>
-      <c r="AX70" s="285"/>
-      <c r="AY70" s="285"/>
-      <c r="AZ70" s="285"/>
-      <c r="BA70" s="285"/>
-      <c r="BB70" s="285"/>
-      <c r="BC70" s="285"/>
-      <c r="BD70" s="285"/>
-      <c r="BE70" s="286"/>
+      <c r="AR70" s="259"/>
+      <c r="AS70" s="259"/>
+      <c r="AT70" s="259"/>
+      <c r="AU70" s="259"/>
+      <c r="AV70" s="259"/>
+      <c r="AW70" s="259"/>
+      <c r="AX70" s="259"/>
+      <c r="AY70" s="259"/>
+      <c r="AZ70" s="259"/>
+      <c r="BA70" s="259"/>
+      <c r="BB70" s="259"/>
+      <c r="BC70" s="259"/>
+      <c r="BD70" s="259"/>
+      <c r="BE70" s="260"/>
       <c r="BF70" s="11"/>
     </row>
     <row r="71" spans="1:58" s="21" customFormat="1" ht="14.4" customHeight="1">
       <c r="A71" s="23"/>
-      <c r="B71" s="251" t="s">
+      <c r="B71" s="248" t="s">
         <v>98</v>
       </c>
-      <c r="C71" s="252"/>
-      <c r="D71" s="252"/>
-      <c r="E71" s="252"/>
-      <c r="F71" s="252"/>
-      <c r="G71" s="252"/>
-      <c r="H71" s="252"/>
-      <c r="I71" s="252"/>
-      <c r="J71" s="252"/>
-      <c r="K71" s="252"/>
-      <c r="L71" s="252"/>
-      <c r="M71" s="252"/>
-      <c r="N71" s="252"/>
-      <c r="O71" s="252"/>
-      <c r="P71" s="252"/>
-      <c r="Q71" s="252"/>
-      <c r="R71" s="252"/>
-      <c r="S71" s="252"/>
-      <c r="T71" s="252"/>
-      <c r="U71" s="252"/>
-      <c r="V71" s="252"/>
-      <c r="W71" s="252"/>
-      <c r="X71" s="252"/>
-      <c r="Y71" s="252"/>
-      <c r="Z71" s="252"/>
-      <c r="AA71" s="252"/>
-      <c r="AB71" s="252"/>
-      <c r="AC71" s="252"/>
-      <c r="AD71" s="252"/>
-      <c r="AE71" s="252"/>
-      <c r="AF71" s="252"/>
-      <c r="AG71" s="252"/>
-      <c r="AH71" s="252"/>
-      <c r="AI71" s="252"/>
-      <c r="AJ71" s="252"/>
-      <c r="AK71" s="252"/>
-      <c r="AL71" s="252"/>
-      <c r="AM71" s="252"/>
-      <c r="AN71" s="252"/>
-      <c r="AO71" s="252"/>
-      <c r="AP71" s="252"/>
-      <c r="AQ71" s="252"/>
-      <c r="AR71" s="252"/>
-      <c r="AS71" s="252"/>
-      <c r="AT71" s="252"/>
-      <c r="AU71" s="252"/>
-      <c r="AV71" s="252"/>
-      <c r="AW71" s="252"/>
-      <c r="AX71" s="252"/>
-      <c r="AY71" s="252"/>
-      <c r="AZ71" s="252"/>
-      <c r="BA71" s="252"/>
-      <c r="BB71" s="252"/>
-      <c r="BC71" s="252"/>
-      <c r="BD71" s="252"/>
-      <c r="BE71" s="252"/>
+      <c r="C71" s="249"/>
+      <c r="D71" s="249"/>
+      <c r="E71" s="249"/>
+      <c r="F71" s="249"/>
+      <c r="G71" s="249"/>
+      <c r="H71" s="249"/>
+      <c r="I71" s="249"/>
+      <c r="J71" s="249"/>
+      <c r="K71" s="249"/>
+      <c r="L71" s="249"/>
+      <c r="M71" s="249"/>
+      <c r="N71" s="249"/>
+      <c r="O71" s="249"/>
+      <c r="P71" s="249"/>
+      <c r="Q71" s="249"/>
+      <c r="R71" s="249"/>
+      <c r="S71" s="249"/>
+      <c r="T71" s="249"/>
+      <c r="U71" s="249"/>
+      <c r="V71" s="249"/>
+      <c r="W71" s="249"/>
+      <c r="X71" s="249"/>
+      <c r="Y71" s="249"/>
+      <c r="Z71" s="249"/>
+      <c r="AA71" s="249"/>
+      <c r="AB71" s="249"/>
+      <c r="AC71" s="249"/>
+      <c r="AD71" s="249"/>
+      <c r="AE71" s="249"/>
+      <c r="AF71" s="249"/>
+      <c r="AG71" s="249"/>
+      <c r="AH71" s="249"/>
+      <c r="AI71" s="249"/>
+      <c r="AJ71" s="249"/>
+      <c r="AK71" s="249"/>
+      <c r="AL71" s="249"/>
+      <c r="AM71" s="249"/>
+      <c r="AN71" s="249"/>
+      <c r="AO71" s="249"/>
+      <c r="AP71" s="249"/>
+      <c r="AQ71" s="249"/>
+      <c r="AR71" s="249"/>
+      <c r="AS71" s="249"/>
+      <c r="AT71" s="249"/>
+      <c r="AU71" s="249"/>
+      <c r="AV71" s="249"/>
+      <c r="AW71" s="249"/>
+      <c r="AX71" s="249"/>
+      <c r="AY71" s="249"/>
+      <c r="AZ71" s="249"/>
+      <c r="BA71" s="249"/>
+      <c r="BB71" s="249"/>
+      <c r="BC71" s="249"/>
+      <c r="BD71" s="249"/>
+      <c r="BE71" s="249"/>
     </row>
     <row r="72" spans="1:58" s="21" customFormat="1" ht="14.4" customHeight="1">
       <c r="A72" s="23"/>
-      <c r="B72" s="264">
+      <c r="B72" s="246">
         <v>16</v>
       </c>
-      <c r="C72" s="265"/>
+      <c r="C72" s="247"/>
       <c r="D72" s="22" t="s">
         <v>132</v>
       </c>
@@ -9450,28 +9450,28 @@
       <c r="AN72" s="100"/>
       <c r="AO72" s="100"/>
       <c r="AP72" s="101"/>
-      <c r="AQ72" s="245"/>
-      <c r="AR72" s="246"/>
-      <c r="AS72" s="246"/>
-      <c r="AT72" s="246"/>
-      <c r="AU72" s="246"/>
-      <c r="AV72" s="246"/>
-      <c r="AW72" s="246"/>
-      <c r="AX72" s="246"/>
-      <c r="AY72" s="246"/>
-      <c r="AZ72" s="246"/>
-      <c r="BA72" s="246"/>
-      <c r="BB72" s="246"/>
-      <c r="BC72" s="246"/>
-      <c r="BD72" s="246"/>
-      <c r="BE72" s="247"/>
+      <c r="AQ72" s="261"/>
+      <c r="AR72" s="262"/>
+      <c r="AS72" s="262"/>
+      <c r="AT72" s="262"/>
+      <c r="AU72" s="262"/>
+      <c r="AV72" s="262"/>
+      <c r="AW72" s="262"/>
+      <c r="AX72" s="262"/>
+      <c r="AY72" s="262"/>
+      <c r="AZ72" s="262"/>
+      <c r="BA72" s="262"/>
+      <c r="BB72" s="262"/>
+      <c r="BC72" s="262"/>
+      <c r="BD72" s="262"/>
+      <c r="BE72" s="263"/>
     </row>
     <row r="73" spans="1:58" s="21" customFormat="1" ht="14.4" customHeight="1">
       <c r="A73" s="23"/>
-      <c r="B73" s="264">
+      <c r="B73" s="246">
         <v>17</v>
       </c>
-      <c r="C73" s="265"/>
+      <c r="C73" s="247"/>
       <c r="D73" s="22" t="s">
         <v>134</v>
       </c>
@@ -9521,28 +9521,28 @@
       <c r="AN73" s="100"/>
       <c r="AO73" s="100"/>
       <c r="AP73" s="101"/>
-      <c r="AQ73" s="245"/>
-      <c r="AR73" s="246"/>
-      <c r="AS73" s="246"/>
-      <c r="AT73" s="246"/>
-      <c r="AU73" s="246"/>
-      <c r="AV73" s="246"/>
-      <c r="AW73" s="246"/>
-      <c r="AX73" s="246"/>
-      <c r="AY73" s="246"/>
-      <c r="AZ73" s="246"/>
-      <c r="BA73" s="246"/>
-      <c r="BB73" s="246"/>
-      <c r="BC73" s="246"/>
-      <c r="BD73" s="246"/>
-      <c r="BE73" s="247"/>
+      <c r="AQ73" s="261"/>
+      <c r="AR73" s="262"/>
+      <c r="AS73" s="262"/>
+      <c r="AT73" s="262"/>
+      <c r="AU73" s="262"/>
+      <c r="AV73" s="262"/>
+      <c r="AW73" s="262"/>
+      <c r="AX73" s="262"/>
+      <c r="AY73" s="262"/>
+      <c r="AZ73" s="262"/>
+      <c r="BA73" s="262"/>
+      <c r="BB73" s="262"/>
+      <c r="BC73" s="262"/>
+      <c r="BD73" s="262"/>
+      <c r="BE73" s="263"/>
     </row>
     <row r="74" spans="1:58" s="21" customFormat="1" ht="14.4" customHeight="1">
       <c r="A74" s="23"/>
-      <c r="B74" s="264">
+      <c r="B74" s="246">
         <v>18</v>
       </c>
-      <c r="C74" s="265"/>
+      <c r="C74" s="247"/>
       <c r="D74" s="22" t="s">
         <v>135</v>
       </c>
@@ -9594,28 +9594,28 @@
       <c r="AN74" s="100"/>
       <c r="AO74" s="100"/>
       <c r="AP74" s="101"/>
-      <c r="AQ74" s="245"/>
-      <c r="AR74" s="246"/>
-      <c r="AS74" s="246"/>
-      <c r="AT74" s="246"/>
-      <c r="AU74" s="246"/>
-      <c r="AV74" s="246"/>
-      <c r="AW74" s="246"/>
-      <c r="AX74" s="246"/>
-      <c r="AY74" s="246"/>
-      <c r="AZ74" s="246"/>
-      <c r="BA74" s="246"/>
-      <c r="BB74" s="246"/>
-      <c r="BC74" s="246"/>
-      <c r="BD74" s="246"/>
-      <c r="BE74" s="247"/>
+      <c r="AQ74" s="261"/>
+      <c r="AR74" s="262"/>
+      <c r="AS74" s="262"/>
+      <c r="AT74" s="262"/>
+      <c r="AU74" s="262"/>
+      <c r="AV74" s="262"/>
+      <c r="AW74" s="262"/>
+      <c r="AX74" s="262"/>
+      <c r="AY74" s="262"/>
+      <c r="AZ74" s="262"/>
+      <c r="BA74" s="262"/>
+      <c r="BB74" s="262"/>
+      <c r="BC74" s="262"/>
+      <c r="BD74" s="262"/>
+      <c r="BE74" s="263"/>
     </row>
     <row r="75" spans="1:58" s="21" customFormat="1" ht="14.4" customHeight="1">
       <c r="A75" s="23"/>
-      <c r="B75" s="264">
+      <c r="B75" s="246">
         <v>19</v>
       </c>
-      <c r="C75" s="265"/>
+      <c r="C75" s="247"/>
       <c r="D75" s="22" t="s">
         <v>138</v>
       </c>
@@ -9667,28 +9667,28 @@
       <c r="AN75" s="100"/>
       <c r="AO75" s="100"/>
       <c r="AP75" s="101"/>
-      <c r="AQ75" s="245"/>
-      <c r="AR75" s="246"/>
-      <c r="AS75" s="246"/>
-      <c r="AT75" s="246"/>
-      <c r="AU75" s="246"/>
-      <c r="AV75" s="246"/>
-      <c r="AW75" s="246"/>
-      <c r="AX75" s="246"/>
-      <c r="AY75" s="246"/>
-      <c r="AZ75" s="246"/>
-      <c r="BA75" s="246"/>
-      <c r="BB75" s="246"/>
-      <c r="BC75" s="246"/>
-      <c r="BD75" s="246"/>
-      <c r="BE75" s="247"/>
+      <c r="AQ75" s="261"/>
+      <c r="AR75" s="262"/>
+      <c r="AS75" s="262"/>
+      <c r="AT75" s="262"/>
+      <c r="AU75" s="262"/>
+      <c r="AV75" s="262"/>
+      <c r="AW75" s="262"/>
+      <c r="AX75" s="262"/>
+      <c r="AY75" s="262"/>
+      <c r="AZ75" s="262"/>
+      <c r="BA75" s="262"/>
+      <c r="BB75" s="262"/>
+      <c r="BC75" s="262"/>
+      <c r="BD75" s="262"/>
+      <c r="BE75" s="263"/>
     </row>
     <row r="76" spans="1:58" s="21" customFormat="1" ht="14.4" customHeight="1">
       <c r="A76" s="23"/>
-      <c r="B76" s="264">
+      <c r="B76" s="246">
         <v>20</v>
       </c>
-      <c r="C76" s="265"/>
+      <c r="C76" s="247"/>
       <c r="D76" s="22" t="s">
         <v>141</v>
       </c>
@@ -9740,28 +9740,28 @@
       <c r="AN76" s="100"/>
       <c r="AO76" s="100"/>
       <c r="AP76" s="101"/>
-      <c r="AQ76" s="245"/>
-      <c r="AR76" s="246"/>
-      <c r="AS76" s="246"/>
-      <c r="AT76" s="246"/>
-      <c r="AU76" s="246"/>
-      <c r="AV76" s="246"/>
-      <c r="AW76" s="246"/>
-      <c r="AX76" s="246"/>
-      <c r="AY76" s="246"/>
-      <c r="AZ76" s="246"/>
-      <c r="BA76" s="246"/>
-      <c r="BB76" s="246"/>
-      <c r="BC76" s="246"/>
-      <c r="BD76" s="246"/>
-      <c r="BE76" s="247"/>
+      <c r="AQ76" s="261"/>
+      <c r="AR76" s="262"/>
+      <c r="AS76" s="262"/>
+      <c r="AT76" s="262"/>
+      <c r="AU76" s="262"/>
+      <c r="AV76" s="262"/>
+      <c r="AW76" s="262"/>
+      <c r="AX76" s="262"/>
+      <c r="AY76" s="262"/>
+      <c r="AZ76" s="262"/>
+      <c r="BA76" s="262"/>
+      <c r="BB76" s="262"/>
+      <c r="BC76" s="262"/>
+      <c r="BD76" s="262"/>
+      <c r="BE76" s="263"/>
     </row>
     <row r="77" spans="1:58" s="21" customFormat="1" ht="14.1" customHeight="1">
       <c r="A77" s="23"/>
-      <c r="B77" s="264">
+      <c r="B77" s="246">
         <v>21</v>
       </c>
-      <c r="C77" s="265"/>
+      <c r="C77" s="247"/>
       <c r="D77" s="22" t="s">
         <v>144</v>
       </c>
@@ -9813,28 +9813,28 @@
       <c r="AN77" s="100"/>
       <c r="AO77" s="100"/>
       <c r="AP77" s="101"/>
-      <c r="AQ77" s="245"/>
-      <c r="AR77" s="246"/>
-      <c r="AS77" s="246"/>
-      <c r="AT77" s="246"/>
-      <c r="AU77" s="246"/>
-      <c r="AV77" s="246"/>
-      <c r="AW77" s="246"/>
-      <c r="AX77" s="246"/>
-      <c r="AY77" s="246"/>
-      <c r="AZ77" s="246"/>
-      <c r="BA77" s="246"/>
-      <c r="BB77" s="246"/>
-      <c r="BC77" s="246"/>
-      <c r="BD77" s="246"/>
-      <c r="BE77" s="247"/>
+      <c r="AQ77" s="261"/>
+      <c r="AR77" s="262"/>
+      <c r="AS77" s="262"/>
+      <c r="AT77" s="262"/>
+      <c r="AU77" s="262"/>
+      <c r="AV77" s="262"/>
+      <c r="AW77" s="262"/>
+      <c r="AX77" s="262"/>
+      <c r="AY77" s="262"/>
+      <c r="AZ77" s="262"/>
+      <c r="BA77" s="262"/>
+      <c r="BB77" s="262"/>
+      <c r="BC77" s="262"/>
+      <c r="BD77" s="262"/>
+      <c r="BE77" s="263"/>
     </row>
     <row r="78" spans="1:58" s="21" customFormat="1" ht="13.95" customHeight="1">
       <c r="A78" s="23"/>
-      <c r="B78" s="264">
+      <c r="B78" s="246">
         <v>22</v>
       </c>
-      <c r="C78" s="265"/>
+      <c r="C78" s="247"/>
       <c r="D78" s="22" t="s">
         <v>145</v>
       </c>
@@ -9886,28 +9886,28 @@
       <c r="AN78" s="100"/>
       <c r="AO78" s="100"/>
       <c r="AP78" s="101"/>
-      <c r="AQ78" s="245"/>
-      <c r="AR78" s="246"/>
-      <c r="AS78" s="246"/>
-      <c r="AT78" s="246"/>
-      <c r="AU78" s="246"/>
-      <c r="AV78" s="246"/>
-      <c r="AW78" s="246"/>
-      <c r="AX78" s="246"/>
-      <c r="AY78" s="246"/>
-      <c r="AZ78" s="246"/>
-      <c r="BA78" s="246"/>
-      <c r="BB78" s="246"/>
-      <c r="BC78" s="246"/>
-      <c r="BD78" s="246"/>
-      <c r="BE78" s="247"/>
+      <c r="AQ78" s="261"/>
+      <c r="AR78" s="262"/>
+      <c r="AS78" s="262"/>
+      <c r="AT78" s="262"/>
+      <c r="AU78" s="262"/>
+      <c r="AV78" s="262"/>
+      <c r="AW78" s="262"/>
+      <c r="AX78" s="262"/>
+      <c r="AY78" s="262"/>
+      <c r="AZ78" s="262"/>
+      <c r="BA78" s="262"/>
+      <c r="BB78" s="262"/>
+      <c r="BC78" s="262"/>
+      <c r="BD78" s="262"/>
+      <c r="BE78" s="263"/>
     </row>
     <row r="79" spans="1:58" s="21" customFormat="1" ht="14.1" customHeight="1">
       <c r="A79" s="23"/>
-      <c r="B79" s="264">
+      <c r="B79" s="246">
         <v>23</v>
       </c>
-      <c r="C79" s="265"/>
+      <c r="C79" s="247"/>
       <c r="D79" s="22" t="s">
         <v>146</v>
       </c>
@@ -9955,28 +9955,28 @@
       <c r="AN79" s="100"/>
       <c r="AO79" s="100"/>
       <c r="AP79" s="101"/>
-      <c r="AQ79" s="245"/>
-      <c r="AR79" s="246"/>
-      <c r="AS79" s="246"/>
-      <c r="AT79" s="246"/>
-      <c r="AU79" s="246"/>
-      <c r="AV79" s="246"/>
-      <c r="AW79" s="246"/>
-      <c r="AX79" s="246"/>
-      <c r="AY79" s="246"/>
-      <c r="AZ79" s="246"/>
-      <c r="BA79" s="246"/>
-      <c r="BB79" s="246"/>
-      <c r="BC79" s="246"/>
-      <c r="BD79" s="246"/>
-      <c r="BE79" s="247"/>
+      <c r="AQ79" s="261"/>
+      <c r="AR79" s="262"/>
+      <c r="AS79" s="262"/>
+      <c r="AT79" s="262"/>
+      <c r="AU79" s="262"/>
+      <c r="AV79" s="262"/>
+      <c r="AW79" s="262"/>
+      <c r="AX79" s="262"/>
+      <c r="AY79" s="262"/>
+      <c r="AZ79" s="262"/>
+      <c r="BA79" s="262"/>
+      <c r="BB79" s="262"/>
+      <c r="BC79" s="262"/>
+      <c r="BD79" s="262"/>
+      <c r="BE79" s="263"/>
     </row>
     <row r="80" spans="1:58" s="21" customFormat="1" ht="14.1" customHeight="1">
       <c r="A80" s="23"/>
-      <c r="B80" s="264">
+      <c r="B80" s="246">
         <v>24</v>
       </c>
-      <c r="C80" s="265"/>
+      <c r="C80" s="247"/>
       <c r="D80" s="22" t="s">
         <v>141</v>
       </c>
@@ -10028,28 +10028,28 @@
       <c r="AN80" s="100"/>
       <c r="AO80" s="100"/>
       <c r="AP80" s="101"/>
-      <c r="AQ80" s="245"/>
-      <c r="AR80" s="246"/>
-      <c r="AS80" s="246"/>
-      <c r="AT80" s="246"/>
-      <c r="AU80" s="246"/>
-      <c r="AV80" s="246"/>
-      <c r="AW80" s="246"/>
-      <c r="AX80" s="246"/>
-      <c r="AY80" s="246"/>
-      <c r="AZ80" s="246"/>
-      <c r="BA80" s="246"/>
-      <c r="BB80" s="246"/>
-      <c r="BC80" s="246"/>
-      <c r="BD80" s="246"/>
-      <c r="BE80" s="247"/>
+      <c r="AQ80" s="261"/>
+      <c r="AR80" s="262"/>
+      <c r="AS80" s="262"/>
+      <c r="AT80" s="262"/>
+      <c r="AU80" s="262"/>
+      <c r="AV80" s="262"/>
+      <c r="AW80" s="262"/>
+      <c r="AX80" s="262"/>
+      <c r="AY80" s="262"/>
+      <c r="AZ80" s="262"/>
+      <c r="BA80" s="262"/>
+      <c r="BB80" s="262"/>
+      <c r="BC80" s="262"/>
+      <c r="BD80" s="262"/>
+      <c r="BE80" s="263"/>
     </row>
     <row r="81" spans="1:59" s="21" customFormat="1" ht="14.1" customHeight="1">
       <c r="A81" s="23"/>
-      <c r="B81" s="264">
+      <c r="B81" s="246">
         <v>25</v>
       </c>
-      <c r="C81" s="265"/>
+      <c r="C81" s="247"/>
       <c r="D81" s="22" t="s">
         <v>144</v>
       </c>
@@ -10101,28 +10101,28 @@
       <c r="AN81" s="100"/>
       <c r="AO81" s="100"/>
       <c r="AP81" s="101"/>
-      <c r="AQ81" s="245"/>
-      <c r="AR81" s="246"/>
-      <c r="AS81" s="246"/>
-      <c r="AT81" s="246"/>
-      <c r="AU81" s="246"/>
-      <c r="AV81" s="246"/>
-      <c r="AW81" s="246"/>
-      <c r="AX81" s="246"/>
-      <c r="AY81" s="246"/>
-      <c r="AZ81" s="246"/>
-      <c r="BA81" s="246"/>
-      <c r="BB81" s="246"/>
-      <c r="BC81" s="246"/>
-      <c r="BD81" s="246"/>
-      <c r="BE81" s="247"/>
+      <c r="AQ81" s="261"/>
+      <c r="AR81" s="262"/>
+      <c r="AS81" s="262"/>
+      <c r="AT81" s="262"/>
+      <c r="AU81" s="262"/>
+      <c r="AV81" s="262"/>
+      <c r="AW81" s="262"/>
+      <c r="AX81" s="262"/>
+      <c r="AY81" s="262"/>
+      <c r="AZ81" s="262"/>
+      <c r="BA81" s="262"/>
+      <c r="BB81" s="262"/>
+      <c r="BC81" s="262"/>
+      <c r="BD81" s="262"/>
+      <c r="BE81" s="263"/>
     </row>
     <row r="82" spans="1:59" s="21" customFormat="1" ht="14.1" customHeight="1">
       <c r="A82" s="23"/>
-      <c r="B82" s="264">
+      <c r="B82" s="246">
         <v>26</v>
       </c>
-      <c r="C82" s="265"/>
+      <c r="C82" s="247"/>
       <c r="D82" s="22" t="s">
         <v>145</v>
       </c>
@@ -10174,28 +10174,28 @@
       <c r="AN82" s="100"/>
       <c r="AO82" s="100"/>
       <c r="AP82" s="101"/>
-      <c r="AQ82" s="245"/>
-      <c r="AR82" s="246"/>
-      <c r="AS82" s="246"/>
-      <c r="AT82" s="246"/>
-      <c r="AU82" s="246"/>
-      <c r="AV82" s="246"/>
-      <c r="AW82" s="246"/>
-      <c r="AX82" s="246"/>
-      <c r="AY82" s="246"/>
-      <c r="AZ82" s="246"/>
-      <c r="BA82" s="246"/>
-      <c r="BB82" s="246"/>
-      <c r="BC82" s="246"/>
-      <c r="BD82" s="246"/>
-      <c r="BE82" s="247"/>
+      <c r="AQ82" s="261"/>
+      <c r="AR82" s="262"/>
+      <c r="AS82" s="262"/>
+      <c r="AT82" s="262"/>
+      <c r="AU82" s="262"/>
+      <c r="AV82" s="262"/>
+      <c r="AW82" s="262"/>
+      <c r="AX82" s="262"/>
+      <c r="AY82" s="262"/>
+      <c r="AZ82" s="262"/>
+      <c r="BA82" s="262"/>
+      <c r="BB82" s="262"/>
+      <c r="BC82" s="262"/>
+      <c r="BD82" s="262"/>
+      <c r="BE82" s="263"/>
     </row>
     <row r="83" spans="1:59" s="21" customFormat="1" ht="14.1" customHeight="1">
       <c r="A83" s="23"/>
-      <c r="B83" s="264">
+      <c r="B83" s="246">
         <v>27</v>
       </c>
-      <c r="C83" s="265"/>
+      <c r="C83" s="247"/>
       <c r="D83" s="22" t="s">
         <v>148</v>
       </c>
@@ -10245,91 +10245,91 @@
       <c r="AN83" s="100"/>
       <c r="AO83" s="100"/>
       <c r="AP83" s="101"/>
-      <c r="AQ83" s="245"/>
-      <c r="AR83" s="246"/>
-      <c r="AS83" s="246"/>
-      <c r="AT83" s="246"/>
-      <c r="AU83" s="246"/>
-      <c r="AV83" s="246"/>
-      <c r="AW83" s="246"/>
-      <c r="AX83" s="246"/>
-      <c r="AY83" s="246"/>
-      <c r="AZ83" s="246"/>
-      <c r="BA83" s="246"/>
-      <c r="BB83" s="246"/>
-      <c r="BC83" s="246"/>
-      <c r="BD83" s="246"/>
-      <c r="BE83" s="247"/>
+      <c r="AQ83" s="261"/>
+      <c r="AR83" s="262"/>
+      <c r="AS83" s="262"/>
+      <c r="AT83" s="262"/>
+      <c r="AU83" s="262"/>
+      <c r="AV83" s="262"/>
+      <c r="AW83" s="262"/>
+      <c r="AX83" s="262"/>
+      <c r="AY83" s="262"/>
+      <c r="AZ83" s="262"/>
+      <c r="BA83" s="262"/>
+      <c r="BB83" s="262"/>
+      <c r="BC83" s="262"/>
+      <c r="BD83" s="262"/>
+      <c r="BE83" s="263"/>
     </row>
     <row r="84" spans="1:59" s="106" customFormat="1" ht="14.1" customHeight="1">
       <c r="A84" s="23"/>
-      <c r="B84" s="251" t="s">
+      <c r="B84" s="248" t="s">
         <v>151</v>
       </c>
-      <c r="C84" s="252"/>
-      <c r="D84" s="252"/>
-      <c r="E84" s="252"/>
-      <c r="F84" s="252"/>
-      <c r="G84" s="252"/>
-      <c r="H84" s="252"/>
-      <c r="I84" s="252"/>
-      <c r="J84" s="252"/>
-      <c r="K84" s="252"/>
-      <c r="L84" s="252"/>
-      <c r="M84" s="252"/>
-      <c r="N84" s="252"/>
-      <c r="O84" s="252"/>
-      <c r="P84" s="252"/>
-      <c r="Q84" s="252"/>
-      <c r="R84" s="252"/>
-      <c r="S84" s="252"/>
-      <c r="T84" s="252"/>
-      <c r="U84" s="252"/>
-      <c r="V84" s="252"/>
-      <c r="W84" s="252"/>
-      <c r="X84" s="252"/>
-      <c r="Y84" s="252"/>
-      <c r="Z84" s="252"/>
-      <c r="AA84" s="252"/>
-      <c r="AB84" s="252"/>
-      <c r="AC84" s="252"/>
-      <c r="AD84" s="252"/>
-      <c r="AE84" s="252"/>
-      <c r="AF84" s="252"/>
-      <c r="AG84" s="252"/>
-      <c r="AH84" s="252"/>
-      <c r="AI84" s="252"/>
-      <c r="AJ84" s="252"/>
-      <c r="AK84" s="252"/>
-      <c r="AL84" s="252"/>
-      <c r="AM84" s="252"/>
-      <c r="AN84" s="252"/>
-      <c r="AO84" s="252"/>
-      <c r="AP84" s="252"/>
-      <c r="AQ84" s="252"/>
-      <c r="AR84" s="252"/>
-      <c r="AS84" s="252"/>
-      <c r="AT84" s="252"/>
-      <c r="AU84" s="252"/>
-      <c r="AV84" s="252"/>
-      <c r="AW84" s="252"/>
-      <c r="AX84" s="252"/>
-      <c r="AY84" s="252"/>
-      <c r="AZ84" s="252"/>
-      <c r="BA84" s="252"/>
-      <c r="BB84" s="252"/>
-      <c r="BC84" s="252"/>
-      <c r="BD84" s="252"/>
-      <c r="BE84" s="252"/>
+      <c r="C84" s="249"/>
+      <c r="D84" s="249"/>
+      <c r="E84" s="249"/>
+      <c r="F84" s="249"/>
+      <c r="G84" s="249"/>
+      <c r="H84" s="249"/>
+      <c r="I84" s="249"/>
+      <c r="J84" s="249"/>
+      <c r="K84" s="249"/>
+      <c r="L84" s="249"/>
+      <c r="M84" s="249"/>
+      <c r="N84" s="249"/>
+      <c r="O84" s="249"/>
+      <c r="P84" s="249"/>
+      <c r="Q84" s="249"/>
+      <c r="R84" s="249"/>
+      <c r="S84" s="249"/>
+      <c r="T84" s="249"/>
+      <c r="U84" s="249"/>
+      <c r="V84" s="249"/>
+      <c r="W84" s="249"/>
+      <c r="X84" s="249"/>
+      <c r="Y84" s="249"/>
+      <c r="Z84" s="249"/>
+      <c r="AA84" s="249"/>
+      <c r="AB84" s="249"/>
+      <c r="AC84" s="249"/>
+      <c r="AD84" s="249"/>
+      <c r="AE84" s="249"/>
+      <c r="AF84" s="249"/>
+      <c r="AG84" s="249"/>
+      <c r="AH84" s="249"/>
+      <c r="AI84" s="249"/>
+      <c r="AJ84" s="249"/>
+      <c r="AK84" s="249"/>
+      <c r="AL84" s="249"/>
+      <c r="AM84" s="249"/>
+      <c r="AN84" s="249"/>
+      <c r="AO84" s="249"/>
+      <c r="AP84" s="249"/>
+      <c r="AQ84" s="249"/>
+      <c r="AR84" s="249"/>
+      <c r="AS84" s="249"/>
+      <c r="AT84" s="249"/>
+      <c r="AU84" s="249"/>
+      <c r="AV84" s="249"/>
+      <c r="AW84" s="249"/>
+      <c r="AX84" s="249"/>
+      <c r="AY84" s="249"/>
+      <c r="AZ84" s="249"/>
+      <c r="BA84" s="249"/>
+      <c r="BB84" s="249"/>
+      <c r="BC84" s="249"/>
+      <c r="BD84" s="249"/>
+      <c r="BE84" s="249"/>
       <c r="BF84" s="21"/>
       <c r="BG84" s="80"/>
     </row>
     <row r="85" spans="1:59" s="106" customFormat="1" ht="14.1" customHeight="1">
       <c r="A85" s="23"/>
-      <c r="B85" s="264">
+      <c r="B85" s="246">
         <v>28</v>
       </c>
-      <c r="C85" s="265"/>
+      <c r="C85" s="247"/>
       <c r="D85" s="22" t="s">
         <v>149</v>
       </c>
@@ -10377,32 +10377,32 @@
       <c r="AN85" s="100"/>
       <c r="AO85" s="100"/>
       <c r="AP85" s="101"/>
-      <c r="AQ85" s="245" t="s">
+      <c r="AQ85" s="261" t="s">
         <v>150</v>
       </c>
-      <c r="AR85" s="246"/>
-      <c r="AS85" s="246"/>
-      <c r="AT85" s="246"/>
-      <c r="AU85" s="246"/>
-      <c r="AV85" s="246"/>
-      <c r="AW85" s="246"/>
-      <c r="AX85" s="246"/>
-      <c r="AY85" s="246"/>
-      <c r="AZ85" s="246"/>
-      <c r="BA85" s="246"/>
-      <c r="BB85" s="246"/>
-      <c r="BC85" s="246"/>
-      <c r="BD85" s="246"/>
-      <c r="BE85" s="247"/>
+      <c r="AR85" s="262"/>
+      <c r="AS85" s="262"/>
+      <c r="AT85" s="262"/>
+      <c r="AU85" s="262"/>
+      <c r="AV85" s="262"/>
+      <c r="AW85" s="262"/>
+      <c r="AX85" s="262"/>
+      <c r="AY85" s="262"/>
+      <c r="AZ85" s="262"/>
+      <c r="BA85" s="262"/>
+      <c r="BB85" s="262"/>
+      <c r="BC85" s="262"/>
+      <c r="BD85" s="262"/>
+      <c r="BE85" s="263"/>
       <c r="BF85" s="21"/>
       <c r="BG85" s="80"/>
     </row>
     <row r="86" spans="1:59" s="106" customFormat="1" ht="14.1" customHeight="1">
       <c r="A86" s="23"/>
-      <c r="B86" s="264">
+      <c r="B86" s="246">
         <v>29</v>
       </c>
-      <c r="C86" s="265"/>
+      <c r="C86" s="247"/>
       <c r="D86" s="22" t="s">
         <v>74</v>
       </c>
@@ -10450,94 +10450,94 @@
       <c r="AN86" s="100"/>
       <c r="AO86" s="100"/>
       <c r="AP86" s="101"/>
-      <c r="AQ86" s="245" t="s">
+      <c r="AQ86" s="261" t="s">
         <v>156</v>
       </c>
-      <c r="AR86" s="246"/>
-      <c r="AS86" s="246"/>
-      <c r="AT86" s="246"/>
-      <c r="AU86" s="246"/>
-      <c r="AV86" s="246"/>
-      <c r="AW86" s="246"/>
-      <c r="AX86" s="246"/>
-      <c r="AY86" s="246"/>
-      <c r="AZ86" s="246"/>
-      <c r="BA86" s="246"/>
-      <c r="BB86" s="246"/>
-      <c r="BC86" s="246"/>
-      <c r="BD86" s="246"/>
-      <c r="BE86" s="247"/>
+      <c r="AR86" s="262"/>
+      <c r="AS86" s="262"/>
+      <c r="AT86" s="262"/>
+      <c r="AU86" s="262"/>
+      <c r="AV86" s="262"/>
+      <c r="AW86" s="262"/>
+      <c r="AX86" s="262"/>
+      <c r="AY86" s="262"/>
+      <c r="AZ86" s="262"/>
+      <c r="BA86" s="262"/>
+      <c r="BB86" s="262"/>
+      <c r="BC86" s="262"/>
+      <c r="BD86" s="262"/>
+      <c r="BE86" s="263"/>
       <c r="BF86" s="21"/>
       <c r="BG86" s="80"/>
     </row>
     <row r="87" spans="1:59" s="106" customFormat="1" ht="14.1" customHeight="1">
       <c r="A87" s="105"/>
-      <c r="B87" s="270" t="s">
+      <c r="B87" s="256" t="s">
         <v>121</v>
       </c>
-      <c r="C87" s="270"/>
-      <c r="D87" s="270"/>
-      <c r="E87" s="270"/>
-      <c r="F87" s="270"/>
-      <c r="G87" s="270"/>
-      <c r="H87" s="270"/>
-      <c r="I87" s="270"/>
-      <c r="J87" s="270"/>
-      <c r="K87" s="270"/>
-      <c r="L87" s="270"/>
-      <c r="M87" s="270"/>
-      <c r="N87" s="270"/>
-      <c r="O87" s="270"/>
-      <c r="P87" s="270"/>
-      <c r="Q87" s="270"/>
-      <c r="R87" s="270"/>
-      <c r="S87" s="270"/>
-      <c r="T87" s="270"/>
-      <c r="U87" s="270"/>
-      <c r="V87" s="270"/>
-      <c r="W87" s="270"/>
-      <c r="X87" s="270"/>
-      <c r="Y87" s="271"/>
-      <c r="Z87" s="271"/>
-      <c r="AA87" s="271"/>
-      <c r="AB87" s="271"/>
-      <c r="AC87" s="271"/>
-      <c r="AD87" s="271"/>
-      <c r="AE87" s="271"/>
-      <c r="AF87" s="270"/>
-      <c r="AG87" s="270"/>
-      <c r="AH87" s="271"/>
-      <c r="AI87" s="271"/>
-      <c r="AJ87" s="271"/>
-      <c r="AK87" s="271"/>
-      <c r="AL87" s="271"/>
-      <c r="AM87" s="271"/>
-      <c r="AN87" s="271"/>
-      <c r="AO87" s="271"/>
-      <c r="AP87" s="271"/>
-      <c r="AQ87" s="270"/>
-      <c r="AR87" s="270"/>
-      <c r="AS87" s="270"/>
-      <c r="AT87" s="270"/>
-      <c r="AU87" s="270"/>
-      <c r="AV87" s="270"/>
-      <c r="AW87" s="270"/>
-      <c r="AX87" s="270"/>
-      <c r="AY87" s="270"/>
-      <c r="AZ87" s="270"/>
-      <c r="BA87" s="270"/>
-      <c r="BB87" s="270"/>
-      <c r="BC87" s="270"/>
-      <c r="BD87" s="270"/>
-      <c r="BE87" s="270"/>
+      <c r="C87" s="256"/>
+      <c r="D87" s="256"/>
+      <c r="E87" s="256"/>
+      <c r="F87" s="256"/>
+      <c r="G87" s="256"/>
+      <c r="H87" s="256"/>
+      <c r="I87" s="256"/>
+      <c r="J87" s="256"/>
+      <c r="K87" s="256"/>
+      <c r="L87" s="256"/>
+      <c r="M87" s="256"/>
+      <c r="N87" s="256"/>
+      <c r="O87" s="256"/>
+      <c r="P87" s="256"/>
+      <c r="Q87" s="256"/>
+      <c r="R87" s="256"/>
+      <c r="S87" s="256"/>
+      <c r="T87" s="256"/>
+      <c r="U87" s="256"/>
+      <c r="V87" s="256"/>
+      <c r="W87" s="256"/>
+      <c r="X87" s="256"/>
+      <c r="Y87" s="257"/>
+      <c r="Z87" s="257"/>
+      <c r="AA87" s="257"/>
+      <c r="AB87" s="257"/>
+      <c r="AC87" s="257"/>
+      <c r="AD87" s="257"/>
+      <c r="AE87" s="257"/>
+      <c r="AF87" s="256"/>
+      <c r="AG87" s="256"/>
+      <c r="AH87" s="257"/>
+      <c r="AI87" s="257"/>
+      <c r="AJ87" s="257"/>
+      <c r="AK87" s="257"/>
+      <c r="AL87" s="257"/>
+      <c r="AM87" s="257"/>
+      <c r="AN87" s="257"/>
+      <c r="AO87" s="257"/>
+      <c r="AP87" s="257"/>
+      <c r="AQ87" s="256"/>
+      <c r="AR87" s="256"/>
+      <c r="AS87" s="256"/>
+      <c r="AT87" s="256"/>
+      <c r="AU87" s="256"/>
+      <c r="AV87" s="256"/>
+      <c r="AW87" s="256"/>
+      <c r="AX87" s="256"/>
+      <c r="AY87" s="256"/>
+      <c r="AZ87" s="256"/>
+      <c r="BA87" s="256"/>
+      <c r="BB87" s="256"/>
+      <c r="BC87" s="256"/>
+      <c r="BD87" s="256"/>
+      <c r="BE87" s="256"/>
       <c r="BG87" s="80"/>
     </row>
     <row r="88" spans="1:59" s="106" customFormat="1" ht="14.1" customHeight="1">
       <c r="A88" s="105"/>
-      <c r="B88" s="268">
+      <c r="B88" s="254">
         <v>30</v>
       </c>
-      <c r="C88" s="269"/>
+      <c r="C88" s="255"/>
       <c r="D88" s="99" t="s">
         <v>122</v>
       </c>
@@ -10585,31 +10585,31 @@
       <c r="AN88" s="110"/>
       <c r="AO88" s="110"/>
       <c r="AP88" s="111"/>
-      <c r="AQ88" s="245" t="s">
+      <c r="AQ88" s="261" t="s">
         <v>123</v>
       </c>
-      <c r="AR88" s="246"/>
-      <c r="AS88" s="246"/>
-      <c r="AT88" s="246"/>
-      <c r="AU88" s="246"/>
-      <c r="AV88" s="246"/>
-      <c r="AW88" s="246"/>
-      <c r="AX88" s="246"/>
-      <c r="AY88" s="246"/>
-      <c r="AZ88" s="246"/>
-      <c r="BA88" s="246"/>
-      <c r="BB88" s="246"/>
-      <c r="BC88" s="246"/>
-      <c r="BD88" s="246"/>
-      <c r="BE88" s="247"/>
+      <c r="AR88" s="262"/>
+      <c r="AS88" s="262"/>
+      <c r="AT88" s="262"/>
+      <c r="AU88" s="262"/>
+      <c r="AV88" s="262"/>
+      <c r="AW88" s="262"/>
+      <c r="AX88" s="262"/>
+      <c r="AY88" s="262"/>
+      <c r="AZ88" s="262"/>
+      <c r="BA88" s="262"/>
+      <c r="BB88" s="262"/>
+      <c r="BC88" s="262"/>
+      <c r="BD88" s="262"/>
+      <c r="BE88" s="263"/>
       <c r="BG88" s="80"/>
     </row>
     <row r="89" spans="1:59" s="106" customFormat="1" ht="27.6" customHeight="1">
       <c r="A89" s="105"/>
-      <c r="B89" s="268">
+      <c r="B89" s="254">
         <v>31</v>
       </c>
-      <c r="C89" s="269"/>
+      <c r="C89" s="255"/>
       <c r="D89" s="99" t="s">
         <v>124</v>
       </c>
@@ -10659,29 +10659,29 @@
       <c r="AN89" s="110"/>
       <c r="AO89" s="110"/>
       <c r="AP89" s="111"/>
-      <c r="AQ89" s="245"/>
-      <c r="AR89" s="246"/>
-      <c r="AS89" s="246"/>
-      <c r="AT89" s="246"/>
-      <c r="AU89" s="246"/>
-      <c r="AV89" s="246"/>
-      <c r="AW89" s="246"/>
-      <c r="AX89" s="246"/>
-      <c r="AY89" s="246"/>
-      <c r="AZ89" s="246"/>
-      <c r="BA89" s="246"/>
-      <c r="BB89" s="246"/>
-      <c r="BC89" s="246"/>
-      <c r="BD89" s="246"/>
-      <c r="BE89" s="247"/>
+      <c r="AQ89" s="261"/>
+      <c r="AR89" s="262"/>
+      <c r="AS89" s="262"/>
+      <c r="AT89" s="262"/>
+      <c r="AU89" s="262"/>
+      <c r="AV89" s="262"/>
+      <c r="AW89" s="262"/>
+      <c r="AX89" s="262"/>
+      <c r="AY89" s="262"/>
+      <c r="AZ89" s="262"/>
+      <c r="BA89" s="262"/>
+      <c r="BB89" s="262"/>
+      <c r="BC89" s="262"/>
+      <c r="BD89" s="262"/>
+      <c r="BE89" s="263"/>
       <c r="BG89" s="80"/>
     </row>
     <row r="90" spans="1:59" s="106" customFormat="1" ht="14.1" customHeight="1">
       <c r="A90" s="105"/>
-      <c r="B90" s="268">
+      <c r="B90" s="254">
         <v>32</v>
       </c>
-      <c r="C90" s="269"/>
+      <c r="C90" s="255"/>
       <c r="D90" s="99" t="s">
         <v>125</v>
       </c>
@@ -10731,91 +10731,91 @@
       <c r="AN90" s="110"/>
       <c r="AO90" s="110"/>
       <c r="AP90" s="111"/>
-      <c r="AQ90" s="245"/>
-      <c r="AR90" s="246"/>
-      <c r="AS90" s="246"/>
-      <c r="AT90" s="246"/>
-      <c r="AU90" s="246"/>
-      <c r="AV90" s="246"/>
-      <c r="AW90" s="246"/>
-      <c r="AX90" s="246"/>
-      <c r="AY90" s="246"/>
-      <c r="AZ90" s="246"/>
-      <c r="BA90" s="246"/>
-      <c r="BB90" s="246"/>
-      <c r="BC90" s="246"/>
-      <c r="BD90" s="246"/>
-      <c r="BE90" s="247"/>
+      <c r="AQ90" s="261"/>
+      <c r="AR90" s="262"/>
+      <c r="AS90" s="262"/>
+      <c r="AT90" s="262"/>
+      <c r="AU90" s="262"/>
+      <c r="AV90" s="262"/>
+      <c r="AW90" s="262"/>
+      <c r="AX90" s="262"/>
+      <c r="AY90" s="262"/>
+      <c r="AZ90" s="262"/>
+      <c r="BA90" s="262"/>
+      <c r="BB90" s="262"/>
+      <c r="BC90" s="262"/>
+      <c r="BD90" s="262"/>
+      <c r="BE90" s="263"/>
       <c r="BG90" s="80"/>
     </row>
     <row r="91" spans="1:59" s="106" customFormat="1" ht="14.1" customHeight="1">
       <c r="A91" s="105"/>
-      <c r="B91" s="270" t="s">
+      <c r="B91" s="256" t="s">
         <v>128</v>
       </c>
-      <c r="C91" s="270"/>
-      <c r="D91" s="270"/>
-      <c r="E91" s="270"/>
-      <c r="F91" s="270"/>
-      <c r="G91" s="270"/>
-      <c r="H91" s="270"/>
-      <c r="I91" s="270"/>
-      <c r="J91" s="270"/>
-      <c r="K91" s="270"/>
-      <c r="L91" s="270"/>
-      <c r="M91" s="270"/>
-      <c r="N91" s="270"/>
-      <c r="O91" s="270"/>
-      <c r="P91" s="270"/>
-      <c r="Q91" s="270"/>
-      <c r="R91" s="270"/>
-      <c r="S91" s="270"/>
-      <c r="T91" s="270"/>
-      <c r="U91" s="270"/>
-      <c r="V91" s="270"/>
-      <c r="W91" s="270"/>
-      <c r="X91" s="270"/>
-      <c r="Y91" s="271"/>
-      <c r="Z91" s="271"/>
-      <c r="AA91" s="271"/>
-      <c r="AB91" s="271"/>
-      <c r="AC91" s="271"/>
-      <c r="AD91" s="271"/>
-      <c r="AE91" s="271"/>
-      <c r="AF91" s="270"/>
-      <c r="AG91" s="270"/>
-      <c r="AH91" s="271"/>
-      <c r="AI91" s="271"/>
-      <c r="AJ91" s="271"/>
-      <c r="AK91" s="271"/>
-      <c r="AL91" s="271"/>
-      <c r="AM91" s="271"/>
-      <c r="AN91" s="271"/>
-      <c r="AO91" s="271"/>
-      <c r="AP91" s="271"/>
-      <c r="AQ91" s="270"/>
-      <c r="AR91" s="270"/>
-      <c r="AS91" s="270"/>
-      <c r="AT91" s="270"/>
-      <c r="AU91" s="270"/>
-      <c r="AV91" s="270"/>
-      <c r="AW91" s="270"/>
-      <c r="AX91" s="270"/>
-      <c r="AY91" s="270"/>
-      <c r="AZ91" s="270"/>
-      <c r="BA91" s="270"/>
-      <c r="BB91" s="270"/>
-      <c r="BC91" s="270"/>
-      <c r="BD91" s="270"/>
-      <c r="BE91" s="270"/>
+      <c r="C91" s="256"/>
+      <c r="D91" s="256"/>
+      <c r="E91" s="256"/>
+      <c r="F91" s="256"/>
+      <c r="G91" s="256"/>
+      <c r="H91" s="256"/>
+      <c r="I91" s="256"/>
+      <c r="J91" s="256"/>
+      <c r="K91" s="256"/>
+      <c r="L91" s="256"/>
+      <c r="M91" s="256"/>
+      <c r="N91" s="256"/>
+      <c r="O91" s="256"/>
+      <c r="P91" s="256"/>
+      <c r="Q91" s="256"/>
+      <c r="R91" s="256"/>
+      <c r="S91" s="256"/>
+      <c r="T91" s="256"/>
+      <c r="U91" s="256"/>
+      <c r="V91" s="256"/>
+      <c r="W91" s="256"/>
+      <c r="X91" s="256"/>
+      <c r="Y91" s="257"/>
+      <c r="Z91" s="257"/>
+      <c r="AA91" s="257"/>
+      <c r="AB91" s="257"/>
+      <c r="AC91" s="257"/>
+      <c r="AD91" s="257"/>
+      <c r="AE91" s="257"/>
+      <c r="AF91" s="256"/>
+      <c r="AG91" s="256"/>
+      <c r="AH91" s="257"/>
+      <c r="AI91" s="257"/>
+      <c r="AJ91" s="257"/>
+      <c r="AK91" s="257"/>
+      <c r="AL91" s="257"/>
+      <c r="AM91" s="257"/>
+      <c r="AN91" s="257"/>
+      <c r="AO91" s="257"/>
+      <c r="AP91" s="257"/>
+      <c r="AQ91" s="256"/>
+      <c r="AR91" s="256"/>
+      <c r="AS91" s="256"/>
+      <c r="AT91" s="256"/>
+      <c r="AU91" s="256"/>
+      <c r="AV91" s="256"/>
+      <c r="AW91" s="256"/>
+      <c r="AX91" s="256"/>
+      <c r="AY91" s="256"/>
+      <c r="AZ91" s="256"/>
+      <c r="BA91" s="256"/>
+      <c r="BB91" s="256"/>
+      <c r="BC91" s="256"/>
+      <c r="BD91" s="256"/>
+      <c r="BE91" s="256"/>
       <c r="BG91" s="80"/>
     </row>
     <row r="92" spans="1:59" s="106" customFormat="1" ht="14.1" customHeight="1">
       <c r="A92" s="105"/>
-      <c r="B92" s="268">
+      <c r="B92" s="254">
         <v>33</v>
       </c>
-      <c r="C92" s="269"/>
+      <c r="C92" s="255"/>
       <c r="D92" s="99" t="s">
         <v>122</v>
       </c>
@@ -10863,31 +10863,31 @@
       <c r="AN92" s="110"/>
       <c r="AO92" s="110"/>
       <c r="AP92" s="111"/>
-      <c r="AQ92" s="278" t="s">
+      <c r="AQ92" s="270" t="s">
         <v>129</v>
       </c>
-      <c r="AR92" s="279"/>
-      <c r="AS92" s="279"/>
-      <c r="AT92" s="279"/>
-      <c r="AU92" s="279"/>
-      <c r="AV92" s="279"/>
-      <c r="AW92" s="279"/>
-      <c r="AX92" s="279"/>
-      <c r="AY92" s="279"/>
-      <c r="AZ92" s="279"/>
-      <c r="BA92" s="279"/>
-      <c r="BB92" s="279"/>
-      <c r="BC92" s="279"/>
-      <c r="BD92" s="279"/>
-      <c r="BE92" s="280"/>
+      <c r="AR92" s="271"/>
+      <c r="AS92" s="271"/>
+      <c r="AT92" s="271"/>
+      <c r="AU92" s="271"/>
+      <c r="AV92" s="271"/>
+      <c r="AW92" s="271"/>
+      <c r="AX92" s="271"/>
+      <c r="AY92" s="271"/>
+      <c r="AZ92" s="271"/>
+      <c r="BA92" s="271"/>
+      <c r="BB92" s="271"/>
+      <c r="BC92" s="271"/>
+      <c r="BD92" s="271"/>
+      <c r="BE92" s="272"/>
       <c r="BG92" s="80"/>
     </row>
     <row r="93" spans="1:59" s="106" customFormat="1" ht="14.1" customHeight="1">
       <c r="A93" s="105"/>
-      <c r="B93" s="268">
+      <c r="B93" s="254">
         <v>34</v>
       </c>
-      <c r="C93" s="269"/>
+      <c r="C93" s="255"/>
       <c r="D93" s="99" t="s">
         <v>124</v>
       </c>
@@ -10937,28 +10937,28 @@
       <c r="AN93" s="110"/>
       <c r="AO93" s="110"/>
       <c r="AP93" s="111"/>
-      <c r="AQ93" s="278"/>
-      <c r="AR93" s="279"/>
-      <c r="AS93" s="279"/>
-      <c r="AT93" s="279"/>
-      <c r="AU93" s="279"/>
-      <c r="AV93" s="279"/>
-      <c r="AW93" s="279"/>
-      <c r="AX93" s="279"/>
-      <c r="AY93" s="279"/>
-      <c r="AZ93" s="279"/>
-      <c r="BA93" s="279"/>
-      <c r="BB93" s="279"/>
-      <c r="BC93" s="279"/>
-      <c r="BD93" s="279"/>
-      <c r="BE93" s="280"/>
+      <c r="AQ93" s="270"/>
+      <c r="AR93" s="271"/>
+      <c r="AS93" s="271"/>
+      <c r="AT93" s="271"/>
+      <c r="AU93" s="271"/>
+      <c r="AV93" s="271"/>
+      <c r="AW93" s="271"/>
+      <c r="AX93" s="271"/>
+      <c r="AY93" s="271"/>
+      <c r="AZ93" s="271"/>
+      <c r="BA93" s="271"/>
+      <c r="BB93" s="271"/>
+      <c r="BC93" s="271"/>
+      <c r="BD93" s="271"/>
+      <c r="BE93" s="272"/>
     </row>
     <row r="94" spans="1:59" ht="14.1" customHeight="1">
       <c r="A94" s="105"/>
-      <c r="B94" s="268">
+      <c r="B94" s="254">
         <v>35</v>
       </c>
-      <c r="C94" s="269"/>
+      <c r="C94" s="255"/>
       <c r="D94" s="99" t="s">
         <v>125</v>
       </c>
@@ -11008,91 +11008,91 @@
       <c r="AN94" s="110"/>
       <c r="AO94" s="110"/>
       <c r="AP94" s="111"/>
-      <c r="AQ94" s="278"/>
-      <c r="AR94" s="279"/>
-      <c r="AS94" s="279"/>
-      <c r="AT94" s="279"/>
-      <c r="AU94" s="279"/>
-      <c r="AV94" s="279"/>
-      <c r="AW94" s="279"/>
-      <c r="AX94" s="279"/>
-      <c r="AY94" s="279"/>
-      <c r="AZ94" s="279"/>
-      <c r="BA94" s="279"/>
-      <c r="BB94" s="279"/>
-      <c r="BC94" s="279"/>
-      <c r="BD94" s="279"/>
-      <c r="BE94" s="280"/>
+      <c r="AQ94" s="270"/>
+      <c r="AR94" s="271"/>
+      <c r="AS94" s="271"/>
+      <c r="AT94" s="271"/>
+      <c r="AU94" s="271"/>
+      <c r="AV94" s="271"/>
+      <c r="AW94" s="271"/>
+      <c r="AX94" s="271"/>
+      <c r="AY94" s="271"/>
+      <c r="AZ94" s="271"/>
+      <c r="BA94" s="271"/>
+      <c r="BB94" s="271"/>
+      <c r="BC94" s="271"/>
+      <c r="BD94" s="271"/>
+      <c r="BE94" s="272"/>
       <c r="BF94" s="106"/>
     </row>
     <row r="95" spans="1:59" ht="14.1" customHeight="1">
       <c r="A95" s="105"/>
-      <c r="B95" s="281" t="s">
+      <c r="B95" s="276" t="s">
         <v>324</v>
       </c>
-      <c r="C95" s="282"/>
-      <c r="D95" s="282"/>
-      <c r="E95" s="282"/>
-      <c r="F95" s="282"/>
-      <c r="G95" s="282"/>
-      <c r="H95" s="282"/>
-      <c r="I95" s="282"/>
-      <c r="J95" s="282"/>
-      <c r="K95" s="282"/>
-      <c r="L95" s="282"/>
-      <c r="M95" s="282"/>
-      <c r="N95" s="282"/>
-      <c r="O95" s="282"/>
-      <c r="P95" s="282"/>
-      <c r="Q95" s="282"/>
-      <c r="R95" s="282"/>
-      <c r="S95" s="282"/>
-      <c r="T95" s="282"/>
-      <c r="U95" s="282"/>
-      <c r="V95" s="282"/>
-      <c r="W95" s="282"/>
-      <c r="X95" s="282"/>
-      <c r="Y95" s="282"/>
-      <c r="Z95" s="282"/>
-      <c r="AA95" s="282"/>
-      <c r="AB95" s="282"/>
-      <c r="AC95" s="282"/>
-      <c r="AD95" s="282"/>
-      <c r="AE95" s="282"/>
-      <c r="AF95" s="282"/>
-      <c r="AG95" s="282"/>
-      <c r="AH95" s="282"/>
-      <c r="AI95" s="282"/>
-      <c r="AJ95" s="282"/>
-      <c r="AK95" s="282"/>
-      <c r="AL95" s="282"/>
-      <c r="AM95" s="282"/>
-      <c r="AN95" s="282"/>
-      <c r="AO95" s="282"/>
-      <c r="AP95" s="282"/>
-      <c r="AQ95" s="282"/>
-      <c r="AR95" s="282"/>
-      <c r="AS95" s="282"/>
-      <c r="AT95" s="282"/>
-      <c r="AU95" s="282"/>
-      <c r="AV95" s="282"/>
-      <c r="AW95" s="282"/>
-      <c r="AX95" s="282"/>
-      <c r="AY95" s="282"/>
-      <c r="AZ95" s="282"/>
-      <c r="BA95" s="282"/>
-      <c r="BB95" s="282"/>
-      <c r="BC95" s="282"/>
-      <c r="BD95" s="282"/>
-      <c r="BE95" s="283"/>
+      <c r="C95" s="277"/>
+      <c r="D95" s="277"/>
+      <c r="E95" s="277"/>
+      <c r="F95" s="277"/>
+      <c r="G95" s="277"/>
+      <c r="H95" s="277"/>
+      <c r="I95" s="277"/>
+      <c r="J95" s="277"/>
+      <c r="K95" s="277"/>
+      <c r="L95" s="277"/>
+      <c r="M95" s="277"/>
+      <c r="N95" s="277"/>
+      <c r="O95" s="277"/>
+      <c r="P95" s="277"/>
+      <c r="Q95" s="277"/>
+      <c r="R95" s="277"/>
+      <c r="S95" s="277"/>
+      <c r="T95" s="277"/>
+      <c r="U95" s="277"/>
+      <c r="V95" s="277"/>
+      <c r="W95" s="277"/>
+      <c r="X95" s="277"/>
+      <c r="Y95" s="277"/>
+      <c r="Z95" s="277"/>
+      <c r="AA95" s="277"/>
+      <c r="AB95" s="277"/>
+      <c r="AC95" s="277"/>
+      <c r="AD95" s="277"/>
+      <c r="AE95" s="277"/>
+      <c r="AF95" s="277"/>
+      <c r="AG95" s="277"/>
+      <c r="AH95" s="277"/>
+      <c r="AI95" s="277"/>
+      <c r="AJ95" s="277"/>
+      <c r="AK95" s="277"/>
+      <c r="AL95" s="277"/>
+      <c r="AM95" s="277"/>
+      <c r="AN95" s="277"/>
+      <c r="AO95" s="277"/>
+      <c r="AP95" s="277"/>
+      <c r="AQ95" s="277"/>
+      <c r="AR95" s="277"/>
+      <c r="AS95" s="277"/>
+      <c r="AT95" s="277"/>
+      <c r="AU95" s="277"/>
+      <c r="AV95" s="277"/>
+      <c r="AW95" s="277"/>
+      <c r="AX95" s="277"/>
+      <c r="AY95" s="277"/>
+      <c r="AZ95" s="277"/>
+      <c r="BA95" s="277"/>
+      <c r="BB95" s="277"/>
+      <c r="BC95" s="277"/>
+      <c r="BD95" s="277"/>
+      <c r="BE95" s="278"/>
       <c r="BF95" s="106"/>
     </row>
     <row r="96" spans="1:59" ht="14.1" customHeight="1">
       <c r="A96" s="105"/>
-      <c r="B96" s="268">
+      <c r="B96" s="254">
         <v>36</v>
       </c>
-      <c r="C96" s="269"/>
+      <c r="C96" s="255"/>
       <c r="D96" s="99" t="s">
         <v>130</v>
       </c>
@@ -11140,21 +11140,21 @@
       <c r="AN96" s="110"/>
       <c r="AO96" s="110"/>
       <c r="AP96" s="111"/>
-      <c r="AQ96" s="248"/>
-      <c r="AR96" s="249"/>
-      <c r="AS96" s="249"/>
-      <c r="AT96" s="249"/>
-      <c r="AU96" s="249"/>
-      <c r="AV96" s="249"/>
-      <c r="AW96" s="249"/>
-      <c r="AX96" s="249"/>
-      <c r="AY96" s="249"/>
-      <c r="AZ96" s="249"/>
-      <c r="BA96" s="249"/>
-      <c r="BB96" s="249"/>
-      <c r="BC96" s="249"/>
-      <c r="BD96" s="249"/>
-      <c r="BE96" s="250"/>
+      <c r="AQ96" s="273"/>
+      <c r="AR96" s="274"/>
+      <c r="AS96" s="274"/>
+      <c r="AT96" s="274"/>
+      <c r="AU96" s="274"/>
+      <c r="AV96" s="274"/>
+      <c r="AW96" s="274"/>
+      <c r="AX96" s="274"/>
+      <c r="AY96" s="274"/>
+      <c r="AZ96" s="274"/>
+      <c r="BA96" s="274"/>
+      <c r="BB96" s="274"/>
+      <c r="BC96" s="274"/>
+      <c r="BD96" s="274"/>
+      <c r="BE96" s="275"/>
       <c r="BF96" s="106"/>
     </row>
     <row r="97" spans="2:57" ht="14.1" customHeight="1">
@@ -11205,198 +11205,198 @@
       <c r="O98" s="14"/>
     </row>
     <row r="99" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B99" s="258" t="s">
+      <c r="B99" s="264" t="s">
         <v>0</v>
       </c>
-      <c r="C99" s="259"/>
-      <c r="D99" s="258" t="s">
+      <c r="C99" s="266"/>
+      <c r="D99" s="264" t="s">
         <v>12</v>
       </c>
-      <c r="E99" s="262"/>
-      <c r="F99" s="262"/>
-      <c r="G99" s="262"/>
-      <c r="H99" s="262"/>
-      <c r="I99" s="259"/>
-      <c r="J99" s="258" t="s">
+      <c r="E99" s="265"/>
+      <c r="F99" s="265"/>
+      <c r="G99" s="265"/>
+      <c r="H99" s="265"/>
+      <c r="I99" s="266"/>
+      <c r="J99" s="264" t="s">
         <v>1</v>
       </c>
-      <c r="K99" s="262"/>
-      <c r="L99" s="262"/>
-      <c r="M99" s="262"/>
-      <c r="N99" s="262"/>
-      <c r="O99" s="262"/>
-      <c r="P99" s="259"/>
-      <c r="Q99" s="258" t="s">
+      <c r="K99" s="265"/>
+      <c r="L99" s="265"/>
+      <c r="M99" s="265"/>
+      <c r="N99" s="265"/>
+      <c r="O99" s="265"/>
+      <c r="P99" s="266"/>
+      <c r="Q99" s="264" t="s">
         <v>21</v>
       </c>
-      <c r="R99" s="262"/>
-      <c r="S99" s="262"/>
-      <c r="T99" s="259"/>
-      <c r="U99" s="258" t="s">
+      <c r="R99" s="265"/>
+      <c r="S99" s="265"/>
+      <c r="T99" s="266"/>
+      <c r="U99" s="264" t="s">
         <v>22</v>
       </c>
-      <c r="V99" s="262"/>
-      <c r="W99" s="259"/>
-      <c r="X99" s="258" t="s">
+      <c r="V99" s="265"/>
+      <c r="W99" s="266"/>
+      <c r="X99" s="264" t="s">
         <v>15</v>
       </c>
-      <c r="Y99" s="262"/>
-      <c r="Z99" s="262"/>
-      <c r="AA99" s="262"/>
-      <c r="AB99" s="262"/>
-      <c r="AC99" s="262"/>
-      <c r="AD99" s="262"/>
-      <c r="AE99" s="262"/>
-      <c r="AF99" s="262"/>
-      <c r="AG99" s="262"/>
-      <c r="AH99" s="262"/>
-      <c r="AI99" s="262"/>
-      <c r="AJ99" s="262"/>
-      <c r="AK99" s="262"/>
-      <c r="AL99" s="262"/>
-      <c r="AM99" s="262"/>
-      <c r="AN99" s="262"/>
-      <c r="AO99" s="262"/>
-      <c r="AP99" s="262"/>
-      <c r="AQ99" s="262"/>
-      <c r="AR99" s="262"/>
-      <c r="AS99" s="262"/>
-      <c r="AT99" s="262"/>
-      <c r="AU99" s="262"/>
-      <c r="AV99" s="262"/>
-      <c r="AW99" s="262"/>
-      <c r="AX99" s="262"/>
-      <c r="AY99" s="262"/>
-      <c r="AZ99" s="262"/>
-      <c r="BA99" s="262"/>
-      <c r="BB99" s="262"/>
-      <c r="BC99" s="262"/>
-      <c r="BD99" s="262"/>
-      <c r="BE99" s="259"/>
+      <c r="Y99" s="265"/>
+      <c r="Z99" s="265"/>
+      <c r="AA99" s="265"/>
+      <c r="AB99" s="265"/>
+      <c r="AC99" s="265"/>
+      <c r="AD99" s="265"/>
+      <c r="AE99" s="265"/>
+      <c r="AF99" s="265"/>
+      <c r="AG99" s="265"/>
+      <c r="AH99" s="265"/>
+      <c r="AI99" s="265"/>
+      <c r="AJ99" s="265"/>
+      <c r="AK99" s="265"/>
+      <c r="AL99" s="265"/>
+      <c r="AM99" s="265"/>
+      <c r="AN99" s="265"/>
+      <c r="AO99" s="265"/>
+      <c r="AP99" s="265"/>
+      <c r="AQ99" s="265"/>
+      <c r="AR99" s="265"/>
+      <c r="AS99" s="265"/>
+      <c r="AT99" s="265"/>
+      <c r="AU99" s="265"/>
+      <c r="AV99" s="265"/>
+      <c r="AW99" s="265"/>
+      <c r="AX99" s="265"/>
+      <c r="AY99" s="265"/>
+      <c r="AZ99" s="265"/>
+      <c r="BA99" s="265"/>
+      <c r="BB99" s="265"/>
+      <c r="BC99" s="265"/>
+      <c r="BD99" s="265"/>
+      <c r="BE99" s="266"/>
     </row>
     <row r="100" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B100" s="260"/>
-      <c r="C100" s="261"/>
-      <c r="D100" s="260"/>
-      <c r="E100" s="263"/>
-      <c r="F100" s="263"/>
-      <c r="G100" s="263"/>
-      <c r="H100" s="263"/>
-      <c r="I100" s="261"/>
-      <c r="J100" s="260"/>
-      <c r="K100" s="263"/>
-      <c r="L100" s="263"/>
-      <c r="M100" s="263"/>
-      <c r="N100" s="263"/>
-      <c r="O100" s="263"/>
-      <c r="P100" s="261"/>
-      <c r="Q100" s="260"/>
-      <c r="R100" s="263"/>
-      <c r="S100" s="263"/>
-      <c r="T100" s="261"/>
-      <c r="U100" s="260"/>
-      <c r="V100" s="263"/>
-      <c r="W100" s="261"/>
-      <c r="X100" s="260"/>
-      <c r="Y100" s="263"/>
-      <c r="Z100" s="263"/>
-      <c r="AA100" s="263"/>
-      <c r="AB100" s="263"/>
-      <c r="AC100" s="263"/>
-      <c r="AD100" s="263"/>
-      <c r="AE100" s="263"/>
-      <c r="AF100" s="263"/>
-      <c r="AG100" s="263"/>
-      <c r="AH100" s="263"/>
-      <c r="AI100" s="263"/>
-      <c r="AJ100" s="263"/>
-      <c r="AK100" s="263"/>
-      <c r="AL100" s="263"/>
-      <c r="AM100" s="263"/>
-      <c r="AN100" s="263"/>
-      <c r="AO100" s="263"/>
-      <c r="AP100" s="263"/>
-      <c r="AQ100" s="263"/>
-      <c r="AR100" s="263"/>
-      <c r="AS100" s="263"/>
-      <c r="AT100" s="263"/>
-      <c r="AU100" s="263"/>
-      <c r="AV100" s="263"/>
-      <c r="AW100" s="263"/>
-      <c r="AX100" s="263"/>
-      <c r="AY100" s="263"/>
-      <c r="AZ100" s="263"/>
-      <c r="BA100" s="263"/>
-      <c r="BB100" s="263"/>
-      <c r="BC100" s="263"/>
-      <c r="BD100" s="263"/>
-      <c r="BE100" s="261"/>
+      <c r="B100" s="267"/>
+      <c r="C100" s="269"/>
+      <c r="D100" s="267"/>
+      <c r="E100" s="268"/>
+      <c r="F100" s="268"/>
+      <c r="G100" s="268"/>
+      <c r="H100" s="268"/>
+      <c r="I100" s="269"/>
+      <c r="J100" s="267"/>
+      <c r="K100" s="268"/>
+      <c r="L100" s="268"/>
+      <c r="M100" s="268"/>
+      <c r="N100" s="268"/>
+      <c r="O100" s="268"/>
+      <c r="P100" s="269"/>
+      <c r="Q100" s="267"/>
+      <c r="R100" s="268"/>
+      <c r="S100" s="268"/>
+      <c r="T100" s="269"/>
+      <c r="U100" s="267"/>
+      <c r="V100" s="268"/>
+      <c r="W100" s="269"/>
+      <c r="X100" s="267"/>
+      <c r="Y100" s="268"/>
+      <c r="Z100" s="268"/>
+      <c r="AA100" s="268"/>
+      <c r="AB100" s="268"/>
+      <c r="AC100" s="268"/>
+      <c r="AD100" s="268"/>
+      <c r="AE100" s="268"/>
+      <c r="AF100" s="268"/>
+      <c r="AG100" s="268"/>
+      <c r="AH100" s="268"/>
+      <c r="AI100" s="268"/>
+      <c r="AJ100" s="268"/>
+      <c r="AK100" s="268"/>
+      <c r="AL100" s="268"/>
+      <c r="AM100" s="268"/>
+      <c r="AN100" s="268"/>
+      <c r="AO100" s="268"/>
+      <c r="AP100" s="268"/>
+      <c r="AQ100" s="268"/>
+      <c r="AR100" s="268"/>
+      <c r="AS100" s="268"/>
+      <c r="AT100" s="268"/>
+      <c r="AU100" s="268"/>
+      <c r="AV100" s="268"/>
+      <c r="AW100" s="268"/>
+      <c r="AX100" s="268"/>
+      <c r="AY100" s="268"/>
+      <c r="AZ100" s="268"/>
+      <c r="BA100" s="268"/>
+      <c r="BB100" s="268"/>
+      <c r="BC100" s="268"/>
+      <c r="BD100" s="268"/>
+      <c r="BE100" s="269"/>
     </row>
     <row r="101" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B101" s="251" t="s">
+      <c r="B101" s="248" t="s">
         <v>157</v>
       </c>
-      <c r="C101" s="252"/>
-      <c r="D101" s="252"/>
-      <c r="E101" s="252"/>
-      <c r="F101" s="252"/>
-      <c r="G101" s="252"/>
-      <c r="H101" s="252"/>
-      <c r="I101" s="252"/>
-      <c r="J101" s="252"/>
-      <c r="K101" s="252"/>
-      <c r="L101" s="252"/>
-      <c r="M101" s="252"/>
-      <c r="N101" s="252"/>
-      <c r="O101" s="252"/>
-      <c r="P101" s="252"/>
-      <c r="Q101" s="252"/>
-      <c r="R101" s="252"/>
-      <c r="S101" s="252"/>
-      <c r="T101" s="252"/>
-      <c r="U101" s="252"/>
-      <c r="V101" s="252"/>
-      <c r="W101" s="252"/>
-      <c r="X101" s="252"/>
-      <c r="Y101" s="252"/>
-      <c r="Z101" s="252"/>
-      <c r="AA101" s="252"/>
-      <c r="AB101" s="252"/>
-      <c r="AC101" s="252"/>
-      <c r="AD101" s="252"/>
-      <c r="AE101" s="252"/>
-      <c r="AF101" s="252"/>
-      <c r="AG101" s="252"/>
-      <c r="AH101" s="252"/>
-      <c r="AI101" s="252"/>
-      <c r="AJ101" s="252"/>
-      <c r="AK101" s="252"/>
-      <c r="AL101" s="252"/>
-      <c r="AM101" s="252"/>
-      <c r="AN101" s="252"/>
-      <c r="AO101" s="252"/>
-      <c r="AP101" s="252"/>
-      <c r="AQ101" s="252"/>
-      <c r="AR101" s="252"/>
-      <c r="AS101" s="252"/>
-      <c r="AT101" s="252"/>
-      <c r="AU101" s="252"/>
-      <c r="AV101" s="252"/>
-      <c r="AW101" s="252"/>
-      <c r="AX101" s="252"/>
-      <c r="AY101" s="252"/>
-      <c r="AZ101" s="252"/>
-      <c r="BA101" s="252"/>
-      <c r="BB101" s="252"/>
-      <c r="BC101" s="252"/>
-      <c r="BD101" s="252"/>
-      <c r="BE101" s="253"/>
+      <c r="C101" s="249"/>
+      <c r="D101" s="249"/>
+      <c r="E101" s="249"/>
+      <c r="F101" s="249"/>
+      <c r="G101" s="249"/>
+      <c r="H101" s="249"/>
+      <c r="I101" s="249"/>
+      <c r="J101" s="249"/>
+      <c r="K101" s="249"/>
+      <c r="L101" s="249"/>
+      <c r="M101" s="249"/>
+      <c r="N101" s="249"/>
+      <c r="O101" s="249"/>
+      <c r="P101" s="249"/>
+      <c r="Q101" s="249"/>
+      <c r="R101" s="249"/>
+      <c r="S101" s="249"/>
+      <c r="T101" s="249"/>
+      <c r="U101" s="249"/>
+      <c r="V101" s="249"/>
+      <c r="W101" s="249"/>
+      <c r="X101" s="249"/>
+      <c r="Y101" s="249"/>
+      <c r="Z101" s="249"/>
+      <c r="AA101" s="249"/>
+      <c r="AB101" s="249"/>
+      <c r="AC101" s="249"/>
+      <c r="AD101" s="249"/>
+      <c r="AE101" s="249"/>
+      <c r="AF101" s="249"/>
+      <c r="AG101" s="249"/>
+      <c r="AH101" s="249"/>
+      <c r="AI101" s="249"/>
+      <c r="AJ101" s="249"/>
+      <c r="AK101" s="249"/>
+      <c r="AL101" s="249"/>
+      <c r="AM101" s="249"/>
+      <c r="AN101" s="249"/>
+      <c r="AO101" s="249"/>
+      <c r="AP101" s="249"/>
+      <c r="AQ101" s="249"/>
+      <c r="AR101" s="249"/>
+      <c r="AS101" s="249"/>
+      <c r="AT101" s="249"/>
+      <c r="AU101" s="249"/>
+      <c r="AV101" s="249"/>
+      <c r="AW101" s="249"/>
+      <c r="AX101" s="249"/>
+      <c r="AY101" s="249"/>
+      <c r="AZ101" s="249"/>
+      <c r="BA101" s="249"/>
+      <c r="BB101" s="249"/>
+      <c r="BC101" s="249"/>
+      <c r="BD101" s="249"/>
+      <c r="BE101" s="250"/>
     </row>
     <row r="102" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B102" s="254">
+      <c r="B102" s="251">
         <v>1</v>
       </c>
-      <c r="C102" s="254"/>
+      <c r="C102" s="251"/>
       <c r="D102" s="37" t="s">
         <v>43</v>
       </c>
@@ -11455,70 +11455,70 @@
       <c r="BE102" s="43"/>
     </row>
     <row r="103" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B103" s="251" t="s">
+      <c r="B103" s="248" t="s">
         <v>196</v>
       </c>
-      <c r="C103" s="252"/>
-      <c r="D103" s="252"/>
-      <c r="E103" s="252"/>
-      <c r="F103" s="252"/>
-      <c r="G103" s="252"/>
-      <c r="H103" s="252"/>
-      <c r="I103" s="252"/>
-      <c r="J103" s="252"/>
-      <c r="K103" s="252"/>
-      <c r="L103" s="252"/>
-      <c r="M103" s="252"/>
-      <c r="N103" s="252"/>
-      <c r="O103" s="252"/>
-      <c r="P103" s="252"/>
-      <c r="Q103" s="252"/>
-      <c r="R103" s="252"/>
-      <c r="S103" s="252"/>
-      <c r="T103" s="252"/>
-      <c r="U103" s="252"/>
-      <c r="V103" s="252"/>
-      <c r="W103" s="252"/>
-      <c r="X103" s="252"/>
-      <c r="Y103" s="252"/>
-      <c r="Z103" s="252"/>
-      <c r="AA103" s="252"/>
-      <c r="AB103" s="252"/>
-      <c r="AC103" s="252"/>
-      <c r="AD103" s="252"/>
-      <c r="AE103" s="252"/>
-      <c r="AF103" s="252"/>
-      <c r="AG103" s="252"/>
-      <c r="AH103" s="252"/>
-      <c r="AI103" s="252"/>
-      <c r="AJ103" s="252"/>
-      <c r="AK103" s="252"/>
-      <c r="AL103" s="252"/>
-      <c r="AM103" s="252"/>
-      <c r="AN103" s="252"/>
-      <c r="AO103" s="252"/>
-      <c r="AP103" s="252"/>
-      <c r="AQ103" s="252"/>
-      <c r="AR103" s="252"/>
-      <c r="AS103" s="252"/>
-      <c r="AT103" s="252"/>
-      <c r="AU103" s="252"/>
-      <c r="AV103" s="252"/>
-      <c r="AW103" s="252"/>
-      <c r="AX103" s="252"/>
-      <c r="AY103" s="252"/>
-      <c r="AZ103" s="252"/>
-      <c r="BA103" s="252"/>
-      <c r="BB103" s="252"/>
-      <c r="BC103" s="252"/>
-      <c r="BD103" s="252"/>
-      <c r="BE103" s="253"/>
+      <c r="C103" s="249"/>
+      <c r="D103" s="249"/>
+      <c r="E103" s="249"/>
+      <c r="F103" s="249"/>
+      <c r="G103" s="249"/>
+      <c r="H103" s="249"/>
+      <c r="I103" s="249"/>
+      <c r="J103" s="249"/>
+      <c r="K103" s="249"/>
+      <c r="L103" s="249"/>
+      <c r="M103" s="249"/>
+      <c r="N103" s="249"/>
+      <c r="O103" s="249"/>
+      <c r="P103" s="249"/>
+      <c r="Q103" s="249"/>
+      <c r="R103" s="249"/>
+      <c r="S103" s="249"/>
+      <c r="T103" s="249"/>
+      <c r="U103" s="249"/>
+      <c r="V103" s="249"/>
+      <c r="W103" s="249"/>
+      <c r="X103" s="249"/>
+      <c r="Y103" s="249"/>
+      <c r="Z103" s="249"/>
+      <c r="AA103" s="249"/>
+      <c r="AB103" s="249"/>
+      <c r="AC103" s="249"/>
+      <c r="AD103" s="249"/>
+      <c r="AE103" s="249"/>
+      <c r="AF103" s="249"/>
+      <c r="AG103" s="249"/>
+      <c r="AH103" s="249"/>
+      <c r="AI103" s="249"/>
+      <c r="AJ103" s="249"/>
+      <c r="AK103" s="249"/>
+      <c r="AL103" s="249"/>
+      <c r="AM103" s="249"/>
+      <c r="AN103" s="249"/>
+      <c r="AO103" s="249"/>
+      <c r="AP103" s="249"/>
+      <c r="AQ103" s="249"/>
+      <c r="AR103" s="249"/>
+      <c r="AS103" s="249"/>
+      <c r="AT103" s="249"/>
+      <c r="AU103" s="249"/>
+      <c r="AV103" s="249"/>
+      <c r="AW103" s="249"/>
+      <c r="AX103" s="249"/>
+      <c r="AY103" s="249"/>
+      <c r="AZ103" s="249"/>
+      <c r="BA103" s="249"/>
+      <c r="BB103" s="249"/>
+      <c r="BC103" s="249"/>
+      <c r="BD103" s="249"/>
+      <c r="BE103" s="250"/>
     </row>
     <row r="104" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B104" s="254">
+      <c r="B104" s="251">
         <v>1</v>
       </c>
-      <c r="C104" s="254"/>
+      <c r="C104" s="251"/>
       <c r="D104" s="37" t="s">
         <v>43</v>
       </c>
@@ -11577,70 +11577,70 @@
       <c r="BE104" s="43"/>
     </row>
     <row r="105" spans="2:57">
-      <c r="B105" s="251" t="s">
+      <c r="B105" s="248" t="s">
         <v>39</v>
       </c>
-      <c r="C105" s="252"/>
-      <c r="D105" s="252"/>
-      <c r="E105" s="252"/>
-      <c r="F105" s="252"/>
-      <c r="G105" s="252"/>
-      <c r="H105" s="252"/>
-      <c r="I105" s="252"/>
-      <c r="J105" s="252"/>
-      <c r="K105" s="252"/>
-      <c r="L105" s="252"/>
-      <c r="M105" s="252"/>
-      <c r="N105" s="252"/>
-      <c r="O105" s="252"/>
-      <c r="P105" s="252"/>
-      <c r="Q105" s="252"/>
-      <c r="R105" s="252"/>
-      <c r="S105" s="252"/>
-      <c r="T105" s="252"/>
-      <c r="U105" s="252"/>
-      <c r="V105" s="252"/>
-      <c r="W105" s="252"/>
-      <c r="X105" s="252"/>
-      <c r="Y105" s="252"/>
-      <c r="Z105" s="252"/>
-      <c r="AA105" s="252"/>
-      <c r="AB105" s="252"/>
-      <c r="AC105" s="252"/>
-      <c r="AD105" s="252"/>
-      <c r="AE105" s="252"/>
-      <c r="AF105" s="252"/>
-      <c r="AG105" s="252"/>
-      <c r="AH105" s="252"/>
-      <c r="AI105" s="252"/>
-      <c r="AJ105" s="252"/>
-      <c r="AK105" s="252"/>
-      <c r="AL105" s="252"/>
-      <c r="AM105" s="252"/>
-      <c r="AN105" s="252"/>
-      <c r="AO105" s="252"/>
-      <c r="AP105" s="252"/>
-      <c r="AQ105" s="252"/>
-      <c r="AR105" s="252"/>
-      <c r="AS105" s="252"/>
-      <c r="AT105" s="252"/>
-      <c r="AU105" s="252"/>
-      <c r="AV105" s="252"/>
-      <c r="AW105" s="252"/>
-      <c r="AX105" s="252"/>
-      <c r="AY105" s="252"/>
-      <c r="AZ105" s="252"/>
-      <c r="BA105" s="252"/>
-      <c r="BB105" s="252"/>
-      <c r="BC105" s="252"/>
-      <c r="BD105" s="252"/>
-      <c r="BE105" s="253"/>
+      <c r="C105" s="249"/>
+      <c r="D105" s="249"/>
+      <c r="E105" s="249"/>
+      <c r="F105" s="249"/>
+      <c r="G105" s="249"/>
+      <c r="H105" s="249"/>
+      <c r="I105" s="249"/>
+      <c r="J105" s="249"/>
+      <c r="K105" s="249"/>
+      <c r="L105" s="249"/>
+      <c r="M105" s="249"/>
+      <c r="N105" s="249"/>
+      <c r="O105" s="249"/>
+      <c r="P105" s="249"/>
+      <c r="Q105" s="249"/>
+      <c r="R105" s="249"/>
+      <c r="S105" s="249"/>
+      <c r="T105" s="249"/>
+      <c r="U105" s="249"/>
+      <c r="V105" s="249"/>
+      <c r="W105" s="249"/>
+      <c r="X105" s="249"/>
+      <c r="Y105" s="249"/>
+      <c r="Z105" s="249"/>
+      <c r="AA105" s="249"/>
+      <c r="AB105" s="249"/>
+      <c r="AC105" s="249"/>
+      <c r="AD105" s="249"/>
+      <c r="AE105" s="249"/>
+      <c r="AF105" s="249"/>
+      <c r="AG105" s="249"/>
+      <c r="AH105" s="249"/>
+      <c r="AI105" s="249"/>
+      <c r="AJ105" s="249"/>
+      <c r="AK105" s="249"/>
+      <c r="AL105" s="249"/>
+      <c r="AM105" s="249"/>
+      <c r="AN105" s="249"/>
+      <c r="AO105" s="249"/>
+      <c r="AP105" s="249"/>
+      <c r="AQ105" s="249"/>
+      <c r="AR105" s="249"/>
+      <c r="AS105" s="249"/>
+      <c r="AT105" s="249"/>
+      <c r="AU105" s="249"/>
+      <c r="AV105" s="249"/>
+      <c r="AW105" s="249"/>
+      <c r="AX105" s="249"/>
+      <c r="AY105" s="249"/>
+      <c r="AZ105" s="249"/>
+      <c r="BA105" s="249"/>
+      <c r="BB105" s="249"/>
+      <c r="BC105" s="249"/>
+      <c r="BD105" s="249"/>
+      <c r="BE105" s="250"/>
     </row>
     <row r="106" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B106" s="254">
+      <c r="B106" s="251">
         <v>1</v>
       </c>
-      <c r="C106" s="254"/>
+      <c r="C106" s="251"/>
       <c r="D106" s="37" t="s">
         <v>43</v>
       </c>
@@ -11699,70 +11699,70 @@
       <c r="BE106" s="43"/>
     </row>
     <row r="107" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B107" s="288" t="s">
+      <c r="B107" s="252" t="s">
         <v>158</v>
       </c>
-      <c r="C107" s="289"/>
-      <c r="D107" s="289"/>
-      <c r="E107" s="289"/>
-      <c r="F107" s="289"/>
-      <c r="G107" s="289"/>
-      <c r="H107" s="289"/>
-      <c r="I107" s="289"/>
-      <c r="J107" s="289"/>
-      <c r="K107" s="289"/>
-      <c r="L107" s="289"/>
-      <c r="M107" s="289"/>
-      <c r="N107" s="289"/>
-      <c r="O107" s="289"/>
-      <c r="P107" s="289"/>
-      <c r="Q107" s="289"/>
-      <c r="R107" s="289"/>
-      <c r="S107" s="289"/>
-      <c r="T107" s="289"/>
-      <c r="U107" s="289"/>
-      <c r="V107" s="289"/>
-      <c r="W107" s="289"/>
-      <c r="X107" s="289"/>
-      <c r="Y107" s="289"/>
-      <c r="Z107" s="289"/>
-      <c r="AA107" s="289"/>
-      <c r="AB107" s="289"/>
-      <c r="AC107" s="289"/>
-      <c r="AD107" s="289"/>
-      <c r="AE107" s="289"/>
-      <c r="AF107" s="289"/>
-      <c r="AG107" s="289"/>
-      <c r="AH107" s="289"/>
-      <c r="AI107" s="289"/>
-      <c r="AJ107" s="289"/>
-      <c r="AK107" s="289"/>
-      <c r="AL107" s="289"/>
-      <c r="AM107" s="289"/>
-      <c r="AN107" s="289"/>
-      <c r="AO107" s="289"/>
-      <c r="AP107" s="289"/>
-      <c r="AQ107" s="289"/>
-      <c r="AR107" s="289"/>
-      <c r="AS107" s="289"/>
-      <c r="AT107" s="289"/>
-      <c r="AU107" s="289"/>
-      <c r="AV107" s="289"/>
-      <c r="AW107" s="289"/>
-      <c r="AX107" s="289"/>
-      <c r="AY107" s="289"/>
-      <c r="AZ107" s="289"/>
-      <c r="BA107" s="289"/>
-      <c r="BB107" s="289"/>
-      <c r="BC107" s="289"/>
-      <c r="BD107" s="289"/>
-      <c r="BE107" s="289"/>
+      <c r="C107" s="253"/>
+      <c r="D107" s="253"/>
+      <c r="E107" s="253"/>
+      <c r="F107" s="253"/>
+      <c r="G107" s="253"/>
+      <c r="H107" s="253"/>
+      <c r="I107" s="253"/>
+      <c r="J107" s="253"/>
+      <c r="K107" s="253"/>
+      <c r="L107" s="253"/>
+      <c r="M107" s="253"/>
+      <c r="N107" s="253"/>
+      <c r="O107" s="253"/>
+      <c r="P107" s="253"/>
+      <c r="Q107" s="253"/>
+      <c r="R107" s="253"/>
+      <c r="S107" s="253"/>
+      <c r="T107" s="253"/>
+      <c r="U107" s="253"/>
+      <c r="V107" s="253"/>
+      <c r="W107" s="253"/>
+      <c r="X107" s="253"/>
+      <c r="Y107" s="253"/>
+      <c r="Z107" s="253"/>
+      <c r="AA107" s="253"/>
+      <c r="AB107" s="253"/>
+      <c r="AC107" s="253"/>
+      <c r="AD107" s="253"/>
+      <c r="AE107" s="253"/>
+      <c r="AF107" s="253"/>
+      <c r="AG107" s="253"/>
+      <c r="AH107" s="253"/>
+      <c r="AI107" s="253"/>
+      <c r="AJ107" s="253"/>
+      <c r="AK107" s="253"/>
+      <c r="AL107" s="253"/>
+      <c r="AM107" s="253"/>
+      <c r="AN107" s="253"/>
+      <c r="AO107" s="253"/>
+      <c r="AP107" s="253"/>
+      <c r="AQ107" s="253"/>
+      <c r="AR107" s="253"/>
+      <c r="AS107" s="253"/>
+      <c r="AT107" s="253"/>
+      <c r="AU107" s="253"/>
+      <c r="AV107" s="253"/>
+      <c r="AW107" s="253"/>
+      <c r="AX107" s="253"/>
+      <c r="AY107" s="253"/>
+      <c r="AZ107" s="253"/>
+      <c r="BA107" s="253"/>
+      <c r="BB107" s="253"/>
+      <c r="BC107" s="253"/>
+      <c r="BD107" s="253"/>
+      <c r="BE107" s="253"/>
     </row>
     <row r="108" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B108" s="287">
+      <c r="B108" s="245">
         <v>1</v>
       </c>
-      <c r="C108" s="287"/>
+      <c r="C108" s="245"/>
       <c r="D108" s="40" t="s">
         <v>43</v>
       </c>
@@ -11821,70 +11821,70 @@
       <c r="BE108" s="118"/>
     </row>
     <row r="109" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B109" s="251" t="s">
+      <c r="B109" s="248" t="s">
         <v>257</v>
       </c>
-      <c r="C109" s="252"/>
-      <c r="D109" s="252"/>
-      <c r="E109" s="252"/>
-      <c r="F109" s="252"/>
-      <c r="G109" s="252"/>
-      <c r="H109" s="252"/>
-      <c r="I109" s="252"/>
-      <c r="J109" s="252"/>
-      <c r="K109" s="252"/>
-      <c r="L109" s="252"/>
-      <c r="M109" s="252"/>
-      <c r="N109" s="252"/>
-      <c r="O109" s="252"/>
-      <c r="P109" s="252"/>
-      <c r="Q109" s="252"/>
-      <c r="R109" s="252"/>
-      <c r="S109" s="252"/>
-      <c r="T109" s="252"/>
-      <c r="U109" s="252"/>
-      <c r="V109" s="252"/>
-      <c r="W109" s="252"/>
-      <c r="X109" s="252"/>
-      <c r="Y109" s="252"/>
-      <c r="Z109" s="252"/>
-      <c r="AA109" s="252"/>
-      <c r="AB109" s="252"/>
-      <c r="AC109" s="252"/>
-      <c r="AD109" s="252"/>
-      <c r="AE109" s="252"/>
-      <c r="AF109" s="252"/>
-      <c r="AG109" s="252"/>
-      <c r="AH109" s="252"/>
-      <c r="AI109" s="252"/>
-      <c r="AJ109" s="252"/>
-      <c r="AK109" s="252"/>
-      <c r="AL109" s="252"/>
-      <c r="AM109" s="252"/>
-      <c r="AN109" s="252"/>
-      <c r="AO109" s="252"/>
-      <c r="AP109" s="252"/>
-      <c r="AQ109" s="252"/>
-      <c r="AR109" s="252"/>
-      <c r="AS109" s="252"/>
-      <c r="AT109" s="252"/>
-      <c r="AU109" s="252"/>
-      <c r="AV109" s="252"/>
-      <c r="AW109" s="252"/>
-      <c r="AX109" s="252"/>
-      <c r="AY109" s="252"/>
-      <c r="AZ109" s="252"/>
-      <c r="BA109" s="252"/>
-      <c r="BB109" s="252"/>
-      <c r="BC109" s="252"/>
-      <c r="BD109" s="252"/>
-      <c r="BE109" s="253"/>
+      <c r="C109" s="249"/>
+      <c r="D109" s="249"/>
+      <c r="E109" s="249"/>
+      <c r="F109" s="249"/>
+      <c r="G109" s="249"/>
+      <c r="H109" s="249"/>
+      <c r="I109" s="249"/>
+      <c r="J109" s="249"/>
+      <c r="K109" s="249"/>
+      <c r="L109" s="249"/>
+      <c r="M109" s="249"/>
+      <c r="N109" s="249"/>
+      <c r="O109" s="249"/>
+      <c r="P109" s="249"/>
+      <c r="Q109" s="249"/>
+      <c r="R109" s="249"/>
+      <c r="S109" s="249"/>
+      <c r="T109" s="249"/>
+      <c r="U109" s="249"/>
+      <c r="V109" s="249"/>
+      <c r="W109" s="249"/>
+      <c r="X109" s="249"/>
+      <c r="Y109" s="249"/>
+      <c r="Z109" s="249"/>
+      <c r="AA109" s="249"/>
+      <c r="AB109" s="249"/>
+      <c r="AC109" s="249"/>
+      <c r="AD109" s="249"/>
+      <c r="AE109" s="249"/>
+      <c r="AF109" s="249"/>
+      <c r="AG109" s="249"/>
+      <c r="AH109" s="249"/>
+      <c r="AI109" s="249"/>
+      <c r="AJ109" s="249"/>
+      <c r="AK109" s="249"/>
+      <c r="AL109" s="249"/>
+      <c r="AM109" s="249"/>
+      <c r="AN109" s="249"/>
+      <c r="AO109" s="249"/>
+      <c r="AP109" s="249"/>
+      <c r="AQ109" s="249"/>
+      <c r="AR109" s="249"/>
+      <c r="AS109" s="249"/>
+      <c r="AT109" s="249"/>
+      <c r="AU109" s="249"/>
+      <c r="AV109" s="249"/>
+      <c r="AW109" s="249"/>
+      <c r="AX109" s="249"/>
+      <c r="AY109" s="249"/>
+      <c r="AZ109" s="249"/>
+      <c r="BA109" s="249"/>
+      <c r="BB109" s="249"/>
+      <c r="BC109" s="249"/>
+      <c r="BD109" s="249"/>
+      <c r="BE109" s="250"/>
     </row>
     <row r="110" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B110" s="254">
+      <c r="B110" s="251">
         <v>1</v>
       </c>
-      <c r="C110" s="254"/>
+      <c r="C110" s="251"/>
       <c r="D110" s="37" t="s">
         <v>284</v>
       </c>
@@ -11947,10 +11947,10 @@
       <c r="BE110" s="43"/>
     </row>
     <row r="111" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B111" s="254">
+      <c r="B111" s="251">
         <v>2</v>
       </c>
-      <c r="C111" s="254"/>
+      <c r="C111" s="251"/>
       <c r="D111" s="37" t="s">
         <v>5</v>
       </c>
@@ -12013,10 +12013,10 @@
       <c r="BE111" s="43"/>
     </row>
     <row r="112" spans="2:57">
-      <c r="B112" s="254">
+      <c r="B112" s="251">
         <v>3</v>
       </c>
-      <c r="C112" s="254"/>
+      <c r="C112" s="251"/>
       <c r="D112" s="37" t="s">
         <v>408</v>
       </c>
@@ -12079,10 +12079,10 @@
       <c r="BE112" s="43"/>
     </row>
     <row r="113" spans="2:57">
-      <c r="B113" s="264">
+      <c r="B113" s="246">
         <v>4</v>
       </c>
-      <c r="C113" s="265"/>
+      <c r="C113" s="247"/>
       <c r="D113" s="37" t="s">
         <v>409</v>
       </c>
@@ -12145,10 +12145,10 @@
       <c r="BE113" s="43"/>
     </row>
     <row r="114" spans="2:57">
-      <c r="B114" s="264">
+      <c r="B114" s="246">
         <v>5</v>
       </c>
-      <c r="C114" s="265"/>
+      <c r="C114" s="247"/>
       <c r="D114" s="37" t="s">
         <v>191</v>
       </c>
@@ -12213,10 +12213,10 @@
       <c r="BE114" s="43"/>
     </row>
     <row r="115" spans="2:57">
-      <c r="B115" s="264">
+      <c r="B115" s="246">
         <v>6</v>
       </c>
-      <c r="C115" s="265"/>
+      <c r="C115" s="247"/>
       <c r="D115" s="37" t="s">
         <v>192</v>
       </c>
@@ -12281,70 +12281,70 @@
       <c r="BE115" s="43"/>
     </row>
     <row r="116" spans="2:57">
-      <c r="B116" s="251" t="s">
+      <c r="B116" s="248" t="s">
         <v>258</v>
       </c>
-      <c r="C116" s="252"/>
-      <c r="D116" s="252"/>
-      <c r="E116" s="252"/>
-      <c r="F116" s="252"/>
-      <c r="G116" s="252"/>
-      <c r="H116" s="252"/>
-      <c r="I116" s="252"/>
-      <c r="J116" s="252"/>
-      <c r="K116" s="252"/>
-      <c r="L116" s="252"/>
-      <c r="M116" s="252"/>
-      <c r="N116" s="252"/>
-      <c r="O116" s="252"/>
-      <c r="P116" s="252"/>
-      <c r="Q116" s="252"/>
-      <c r="R116" s="252"/>
-      <c r="S116" s="252"/>
-      <c r="T116" s="252"/>
-      <c r="U116" s="252"/>
-      <c r="V116" s="252"/>
-      <c r="W116" s="252"/>
-      <c r="X116" s="252"/>
-      <c r="Y116" s="252"/>
-      <c r="Z116" s="252"/>
-      <c r="AA116" s="252"/>
-      <c r="AB116" s="252"/>
-      <c r="AC116" s="252"/>
-      <c r="AD116" s="252"/>
-      <c r="AE116" s="252"/>
-      <c r="AF116" s="252"/>
-      <c r="AG116" s="252"/>
-      <c r="AH116" s="252"/>
-      <c r="AI116" s="252"/>
-      <c r="AJ116" s="252"/>
-      <c r="AK116" s="252"/>
-      <c r="AL116" s="252"/>
-      <c r="AM116" s="252"/>
-      <c r="AN116" s="252"/>
-      <c r="AO116" s="252"/>
-      <c r="AP116" s="252"/>
-      <c r="AQ116" s="252"/>
-      <c r="AR116" s="252"/>
-      <c r="AS116" s="252"/>
-      <c r="AT116" s="252"/>
-      <c r="AU116" s="252"/>
-      <c r="AV116" s="252"/>
-      <c r="AW116" s="252"/>
-      <c r="AX116" s="252"/>
-      <c r="AY116" s="252"/>
-      <c r="AZ116" s="252"/>
-      <c r="BA116" s="252"/>
-      <c r="BB116" s="252"/>
-      <c r="BC116" s="252"/>
-      <c r="BD116" s="252"/>
-      <c r="BE116" s="253"/>
+      <c r="C116" s="249"/>
+      <c r="D116" s="249"/>
+      <c r="E116" s="249"/>
+      <c r="F116" s="249"/>
+      <c r="G116" s="249"/>
+      <c r="H116" s="249"/>
+      <c r="I116" s="249"/>
+      <c r="J116" s="249"/>
+      <c r="K116" s="249"/>
+      <c r="L116" s="249"/>
+      <c r="M116" s="249"/>
+      <c r="N116" s="249"/>
+      <c r="O116" s="249"/>
+      <c r="P116" s="249"/>
+      <c r="Q116" s="249"/>
+      <c r="R116" s="249"/>
+      <c r="S116" s="249"/>
+      <c r="T116" s="249"/>
+      <c r="U116" s="249"/>
+      <c r="V116" s="249"/>
+      <c r="W116" s="249"/>
+      <c r="X116" s="249"/>
+      <c r="Y116" s="249"/>
+      <c r="Z116" s="249"/>
+      <c r="AA116" s="249"/>
+      <c r="AB116" s="249"/>
+      <c r="AC116" s="249"/>
+      <c r="AD116" s="249"/>
+      <c r="AE116" s="249"/>
+      <c r="AF116" s="249"/>
+      <c r="AG116" s="249"/>
+      <c r="AH116" s="249"/>
+      <c r="AI116" s="249"/>
+      <c r="AJ116" s="249"/>
+      <c r="AK116" s="249"/>
+      <c r="AL116" s="249"/>
+      <c r="AM116" s="249"/>
+      <c r="AN116" s="249"/>
+      <c r="AO116" s="249"/>
+      <c r="AP116" s="249"/>
+      <c r="AQ116" s="249"/>
+      <c r="AR116" s="249"/>
+      <c r="AS116" s="249"/>
+      <c r="AT116" s="249"/>
+      <c r="AU116" s="249"/>
+      <c r="AV116" s="249"/>
+      <c r="AW116" s="249"/>
+      <c r="AX116" s="249"/>
+      <c r="AY116" s="249"/>
+      <c r="AZ116" s="249"/>
+      <c r="BA116" s="249"/>
+      <c r="BB116" s="249"/>
+      <c r="BC116" s="249"/>
+      <c r="BD116" s="249"/>
+      <c r="BE116" s="250"/>
     </row>
     <row r="117" spans="2:57">
-      <c r="B117" s="287">
+      <c r="B117" s="245">
         <v>1</v>
       </c>
-      <c r="C117" s="287"/>
+      <c r="C117" s="245"/>
       <c r="D117" s="40" t="s">
         <v>43</v>
       </c>
@@ -12404,6 +12404,107 @@
     </row>
   </sheetData>
   <mergeCells count="125">
+    <mergeCell ref="AQ77:BE77"/>
+    <mergeCell ref="AQ78:BE78"/>
+    <mergeCell ref="AQ79:BE79"/>
+    <mergeCell ref="AQ80:BE80"/>
+    <mergeCell ref="AQ81:BE81"/>
+    <mergeCell ref="AQ72:BE72"/>
+    <mergeCell ref="AQ73:BE73"/>
+    <mergeCell ref="AQ74:BE74"/>
+    <mergeCell ref="AQ75:BE75"/>
+    <mergeCell ref="AQ76:BE76"/>
+    <mergeCell ref="B101:BE101"/>
+    <mergeCell ref="B102:C102"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B2:N3"/>
+    <mergeCell ref="J50:O50"/>
+    <mergeCell ref="B49:C50"/>
+    <mergeCell ref="D49:I50"/>
+    <mergeCell ref="W49:X49"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="AQ49:BE50"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="V49:V50"/>
+    <mergeCell ref="P50:U50"/>
+    <mergeCell ref="J49:U49"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="AQ62:BE62"/>
+    <mergeCell ref="AQ63:BE63"/>
+    <mergeCell ref="AQ64:BE64"/>
+    <mergeCell ref="AQ65:BE65"/>
+    <mergeCell ref="AQ66:BE66"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B52:BE52"/>
+    <mergeCell ref="Y49:AC50"/>
+    <mergeCell ref="AF49:AG50"/>
+    <mergeCell ref="AH49:AJ50"/>
+    <mergeCell ref="AK49:AL50"/>
+    <mergeCell ref="AM49:AP50"/>
+    <mergeCell ref="AD49:AE50"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="AD56:AE56"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="AQ51:BE51"/>
+    <mergeCell ref="AQ53:BE53"/>
+    <mergeCell ref="AQ54:BE54"/>
+    <mergeCell ref="AQ55:BE55"/>
+    <mergeCell ref="AQ56:BE56"/>
+    <mergeCell ref="AQ57:BE57"/>
+    <mergeCell ref="AQ58:BE58"/>
+    <mergeCell ref="AQ59:BE59"/>
+    <mergeCell ref="AQ60:BE60"/>
+    <mergeCell ref="AQ61:BE61"/>
+    <mergeCell ref="B99:C100"/>
+    <mergeCell ref="D99:I100"/>
+    <mergeCell ref="AQ82:BE82"/>
+    <mergeCell ref="AQ83:BE83"/>
+    <mergeCell ref="AQ85:BE85"/>
+    <mergeCell ref="AQ86:BE86"/>
+    <mergeCell ref="AQ88:BE88"/>
+    <mergeCell ref="AQ89:BE89"/>
+    <mergeCell ref="AQ90:BE90"/>
+    <mergeCell ref="AQ93:BE93"/>
+    <mergeCell ref="AQ94:BE94"/>
+    <mergeCell ref="AQ96:BE96"/>
+    <mergeCell ref="U99:W100"/>
+    <mergeCell ref="B87:BE87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="B95:BE95"/>
+    <mergeCell ref="AQ92:BE92"/>
+    <mergeCell ref="B84:BE84"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B116:BE116"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B71:BE71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="AQ70:BE70"/>
+    <mergeCell ref="AQ67:BE67"/>
+    <mergeCell ref="AQ68:BE68"/>
+    <mergeCell ref="AQ69:BE69"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="X99:BE100"/>
+    <mergeCell ref="Q99:T100"/>
+    <mergeCell ref="J99:P100"/>
     <mergeCell ref="B117:C117"/>
     <mergeCell ref="B114:C114"/>
     <mergeCell ref="B115:C115"/>
@@ -12428,107 +12529,6 @@
     <mergeCell ref="B81:C81"/>
     <mergeCell ref="B82:C82"/>
     <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B116:BE116"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B71:BE71"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="AQ70:BE70"/>
-    <mergeCell ref="AQ67:BE67"/>
-    <mergeCell ref="AQ68:BE68"/>
-    <mergeCell ref="AQ69:BE69"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="X99:BE100"/>
-    <mergeCell ref="Q99:T100"/>
-    <mergeCell ref="J99:P100"/>
-    <mergeCell ref="B99:C100"/>
-    <mergeCell ref="D99:I100"/>
-    <mergeCell ref="AQ82:BE82"/>
-    <mergeCell ref="AQ83:BE83"/>
-    <mergeCell ref="AQ85:BE85"/>
-    <mergeCell ref="AQ86:BE86"/>
-    <mergeCell ref="AQ88:BE88"/>
-    <mergeCell ref="AQ89:BE89"/>
-    <mergeCell ref="AQ90:BE90"/>
-    <mergeCell ref="AQ93:BE93"/>
-    <mergeCell ref="AQ94:BE94"/>
-    <mergeCell ref="AQ96:BE96"/>
-    <mergeCell ref="U99:W100"/>
-    <mergeCell ref="B87:BE87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="B95:BE95"/>
-    <mergeCell ref="AQ92:BE92"/>
-    <mergeCell ref="B84:BE84"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B52:BE52"/>
-    <mergeCell ref="Y49:AC50"/>
-    <mergeCell ref="AF49:AG50"/>
-    <mergeCell ref="AH49:AJ50"/>
-    <mergeCell ref="AK49:AL50"/>
-    <mergeCell ref="AM49:AP50"/>
-    <mergeCell ref="AD49:AE50"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="AD56:AE56"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="AQ51:BE51"/>
-    <mergeCell ref="AQ53:BE53"/>
-    <mergeCell ref="AQ54:BE54"/>
-    <mergeCell ref="AQ55:BE55"/>
-    <mergeCell ref="AQ56:BE56"/>
-    <mergeCell ref="B101:BE101"/>
-    <mergeCell ref="B102:C102"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B2:N3"/>
-    <mergeCell ref="J50:O50"/>
-    <mergeCell ref="B49:C50"/>
-    <mergeCell ref="D49:I50"/>
-    <mergeCell ref="W49:X49"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="AQ49:BE50"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="V49:V50"/>
-    <mergeCell ref="P50:U50"/>
-    <mergeCell ref="J49:U49"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="AQ62:BE62"/>
-    <mergeCell ref="AQ63:BE63"/>
-    <mergeCell ref="AQ64:BE64"/>
-    <mergeCell ref="AQ65:BE65"/>
-    <mergeCell ref="AQ66:BE66"/>
-    <mergeCell ref="AQ57:BE57"/>
-    <mergeCell ref="AQ58:BE58"/>
-    <mergeCell ref="AQ59:BE59"/>
-    <mergeCell ref="AQ60:BE60"/>
-    <mergeCell ref="AQ61:BE61"/>
-    <mergeCell ref="AQ77:BE77"/>
-    <mergeCell ref="AQ78:BE78"/>
-    <mergeCell ref="AQ79:BE79"/>
-    <mergeCell ref="AQ80:BE80"/>
-    <mergeCell ref="AQ81:BE81"/>
-    <mergeCell ref="AQ72:BE72"/>
-    <mergeCell ref="AQ73:BE73"/>
-    <mergeCell ref="AQ74:BE74"/>
-    <mergeCell ref="AQ75:BE75"/>
-    <mergeCell ref="AQ76:BE76"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="8">
@@ -19244,158 +19244,158 @@
       </c>
     </row>
     <row r="47" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B47" s="258" t="s">
+      <c r="B47" s="264" t="s">
         <v>0</v>
       </c>
-      <c r="C47" s="259"/>
-      <c r="D47" s="258" t="s">
+      <c r="C47" s="266"/>
+      <c r="D47" s="264" t="s">
         <v>12</v>
       </c>
-      <c r="E47" s="262"/>
-      <c r="F47" s="262"/>
-      <c r="G47" s="262"/>
-      <c r="H47" s="262"/>
-      <c r="I47" s="259"/>
-      <c r="J47" s="255" t="s">
+      <c r="E47" s="265"/>
+      <c r="F47" s="265"/>
+      <c r="G47" s="265"/>
+      <c r="H47" s="265"/>
+      <c r="I47" s="266"/>
+      <c r="J47" s="285" t="s">
         <v>13</v>
       </c>
-      <c r="K47" s="256"/>
-      <c r="L47" s="256"/>
-      <c r="M47" s="256"/>
-      <c r="N47" s="256"/>
-      <c r="O47" s="256"/>
-      <c r="P47" s="256"/>
-      <c r="Q47" s="256"/>
-      <c r="R47" s="256"/>
-      <c r="S47" s="256"/>
-      <c r="T47" s="256"/>
-      <c r="U47" s="257"/>
-      <c r="V47" s="266" t="s">
+      <c r="K47" s="286"/>
+      <c r="L47" s="286"/>
+      <c r="M47" s="286"/>
+      <c r="N47" s="286"/>
+      <c r="O47" s="286"/>
+      <c r="P47" s="286"/>
+      <c r="Q47" s="286"/>
+      <c r="R47" s="286"/>
+      <c r="S47" s="286"/>
+      <c r="T47" s="286"/>
+      <c r="U47" s="287"/>
+      <c r="V47" s="288" t="s">
         <v>48</v>
       </c>
-      <c r="W47" s="255" t="s">
+      <c r="W47" s="285" t="s">
         <v>16</v>
       </c>
-      <c r="X47" s="257"/>
-      <c r="Y47" s="258" t="s">
+      <c r="X47" s="287"/>
+      <c r="Y47" s="264" t="s">
         <v>49</v>
       </c>
-      <c r="Z47" s="262"/>
-      <c r="AA47" s="262"/>
-      <c r="AB47" s="262"/>
-      <c r="AC47" s="259"/>
-      <c r="AD47" s="258" t="s">
+      <c r="Z47" s="265"/>
+      <c r="AA47" s="265"/>
+      <c r="AB47" s="265"/>
+      <c r="AC47" s="266"/>
+      <c r="AD47" s="264" t="s">
         <v>50</v>
       </c>
-      <c r="AE47" s="259"/>
-      <c r="AF47" s="258" t="s">
+      <c r="AE47" s="266"/>
+      <c r="AF47" s="264" t="s">
         <v>51</v>
       </c>
-      <c r="AG47" s="259"/>
-      <c r="AH47" s="272" t="s">
+      <c r="AG47" s="266"/>
+      <c r="AH47" s="279" t="s">
         <v>52</v>
       </c>
-      <c r="AI47" s="273"/>
-      <c r="AJ47" s="274"/>
-      <c r="AK47" s="272" t="s">
+      <c r="AI47" s="280"/>
+      <c r="AJ47" s="281"/>
+      <c r="AK47" s="279" t="s">
         <v>53</v>
       </c>
-      <c r="AL47" s="274"/>
-      <c r="AM47" s="272" t="s">
+      <c r="AL47" s="281"/>
+      <c r="AM47" s="279" t="s">
         <v>54</v>
       </c>
-      <c r="AN47" s="273"/>
-      <c r="AO47" s="273"/>
-      <c r="AP47" s="274"/>
-      <c r="AQ47" s="258" t="s">
+      <c r="AN47" s="280"/>
+      <c r="AO47" s="280"/>
+      <c r="AP47" s="281"/>
+      <c r="AQ47" s="264" t="s">
         <v>15</v>
       </c>
-      <c r="AR47" s="262"/>
-      <c r="AS47" s="262"/>
-      <c r="AT47" s="262"/>
-      <c r="AU47" s="262"/>
-      <c r="AV47" s="262"/>
-      <c r="AW47" s="262"/>
-      <c r="AX47" s="262"/>
-      <c r="AY47" s="262"/>
-      <c r="AZ47" s="262"/>
-      <c r="BA47" s="262"/>
-      <c r="BB47" s="262"/>
-      <c r="BC47" s="262"/>
-      <c r="BD47" s="262"/>
-      <c r="BE47" s="259"/>
+      <c r="AR47" s="265"/>
+      <c r="AS47" s="265"/>
+      <c r="AT47" s="265"/>
+      <c r="AU47" s="265"/>
+      <c r="AV47" s="265"/>
+      <c r="AW47" s="265"/>
+      <c r="AX47" s="265"/>
+      <c r="AY47" s="265"/>
+      <c r="AZ47" s="265"/>
+      <c r="BA47" s="265"/>
+      <c r="BB47" s="265"/>
+      <c r="BC47" s="265"/>
+      <c r="BD47" s="265"/>
+      <c r="BE47" s="266"/>
     </row>
     <row r="48" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B48" s="260"/>
-      <c r="C48" s="261"/>
-      <c r="D48" s="260"/>
-      <c r="E48" s="263"/>
-      <c r="F48" s="263"/>
-      <c r="G48" s="263"/>
-      <c r="H48" s="263"/>
-      <c r="I48" s="261"/>
-      <c r="J48" s="255" t="s">
+      <c r="B48" s="267"/>
+      <c r="C48" s="269"/>
+      <c r="D48" s="267"/>
+      <c r="E48" s="268"/>
+      <c r="F48" s="268"/>
+      <c r="G48" s="268"/>
+      <c r="H48" s="268"/>
+      <c r="I48" s="269"/>
+      <c r="J48" s="285" t="s">
         <v>14</v>
       </c>
-      <c r="K48" s="256"/>
-      <c r="L48" s="256"/>
-      <c r="M48" s="256"/>
-      <c r="N48" s="256"/>
-      <c r="O48" s="257"/>
-      <c r="P48" s="255" t="s">
+      <c r="K48" s="286"/>
+      <c r="L48" s="286"/>
+      <c r="M48" s="286"/>
+      <c r="N48" s="286"/>
+      <c r="O48" s="287"/>
+      <c r="P48" s="285" t="s">
         <v>24</v>
       </c>
-      <c r="Q48" s="256"/>
-      <c r="R48" s="256"/>
-      <c r="S48" s="256"/>
-      <c r="T48" s="256"/>
-      <c r="U48" s="257"/>
-      <c r="V48" s="267"/>
+      <c r="Q48" s="286"/>
+      <c r="R48" s="286"/>
+      <c r="S48" s="286"/>
+      <c r="T48" s="286"/>
+      <c r="U48" s="287"/>
+      <c r="V48" s="289"/>
       <c r="W48" s="20" t="s">
         <v>18</v>
       </c>
       <c r="X48" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="Y48" s="260"/>
-      <c r="Z48" s="263"/>
-      <c r="AA48" s="263"/>
-      <c r="AB48" s="263"/>
-      <c r="AC48" s="261"/>
-      <c r="AD48" s="260"/>
-      <c r="AE48" s="261"/>
-      <c r="AF48" s="260"/>
-      <c r="AG48" s="261"/>
-      <c r="AH48" s="275"/>
-      <c r="AI48" s="276"/>
-      <c r="AJ48" s="277"/>
-      <c r="AK48" s="275"/>
-      <c r="AL48" s="277"/>
-      <c r="AM48" s="275"/>
-      <c r="AN48" s="276"/>
-      <c r="AO48" s="276"/>
-      <c r="AP48" s="277"/>
-      <c r="AQ48" s="260"/>
-      <c r="AR48" s="263"/>
-      <c r="AS48" s="263"/>
-      <c r="AT48" s="263"/>
-      <c r="AU48" s="263"/>
-      <c r="AV48" s="263"/>
-      <c r="AW48" s="263"/>
-      <c r="AX48" s="263"/>
-      <c r="AY48" s="263"/>
-      <c r="AZ48" s="263"/>
-      <c r="BA48" s="263"/>
-      <c r="BB48" s="263"/>
-      <c r="BC48" s="263"/>
-      <c r="BD48" s="263"/>
-      <c r="BE48" s="261"/>
+      <c r="Y48" s="267"/>
+      <c r="Z48" s="268"/>
+      <c r="AA48" s="268"/>
+      <c r="AB48" s="268"/>
+      <c r="AC48" s="269"/>
+      <c r="AD48" s="267"/>
+      <c r="AE48" s="269"/>
+      <c r="AF48" s="267"/>
+      <c r="AG48" s="269"/>
+      <c r="AH48" s="282"/>
+      <c r="AI48" s="283"/>
+      <c r="AJ48" s="284"/>
+      <c r="AK48" s="282"/>
+      <c r="AL48" s="284"/>
+      <c r="AM48" s="282"/>
+      <c r="AN48" s="283"/>
+      <c r="AO48" s="283"/>
+      <c r="AP48" s="284"/>
+      <c r="AQ48" s="267"/>
+      <c r="AR48" s="268"/>
+      <c r="AS48" s="268"/>
+      <c r="AT48" s="268"/>
+      <c r="AU48" s="268"/>
+      <c r="AV48" s="268"/>
+      <c r="AW48" s="268"/>
+      <c r="AX48" s="268"/>
+      <c r="AY48" s="268"/>
+      <c r="AZ48" s="268"/>
+      <c r="BA48" s="268"/>
+      <c r="BB48" s="268"/>
+      <c r="BC48" s="268"/>
+      <c r="BD48" s="268"/>
+      <c r="BE48" s="269"/>
     </row>
     <row r="49" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B49" s="268">
+      <c r="B49" s="254">
         <v>1</v>
       </c>
-      <c r="C49" s="269"/>
+      <c r="C49" s="255"/>
       <c r="D49" s="112" t="s">
         <v>106</v>
       </c>
@@ -19462,70 +19462,70 @@
       <c r="BE49" s="111"/>
     </row>
     <row r="50" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B50" s="270" t="s">
+      <c r="B50" s="256" t="s">
         <v>30</v>
       </c>
-      <c r="C50" s="270"/>
-      <c r="D50" s="270"/>
-      <c r="E50" s="270"/>
-      <c r="F50" s="270"/>
-      <c r="G50" s="270"/>
-      <c r="H50" s="270"/>
-      <c r="I50" s="270"/>
-      <c r="J50" s="270"/>
-      <c r="K50" s="270"/>
-      <c r="L50" s="270"/>
-      <c r="M50" s="270"/>
-      <c r="N50" s="270"/>
-      <c r="O50" s="270"/>
-      <c r="P50" s="270"/>
-      <c r="Q50" s="270"/>
-      <c r="R50" s="270"/>
-      <c r="S50" s="270"/>
-      <c r="T50" s="270"/>
-      <c r="U50" s="270"/>
-      <c r="V50" s="270"/>
-      <c r="W50" s="270"/>
-      <c r="X50" s="270"/>
-      <c r="Y50" s="271"/>
-      <c r="Z50" s="271"/>
-      <c r="AA50" s="271"/>
-      <c r="AB50" s="271"/>
-      <c r="AC50" s="271"/>
-      <c r="AD50" s="271"/>
-      <c r="AE50" s="271"/>
-      <c r="AF50" s="270"/>
-      <c r="AG50" s="270"/>
-      <c r="AH50" s="271"/>
-      <c r="AI50" s="271"/>
-      <c r="AJ50" s="271"/>
-      <c r="AK50" s="271"/>
-      <c r="AL50" s="271"/>
-      <c r="AM50" s="271"/>
-      <c r="AN50" s="271"/>
-      <c r="AO50" s="271"/>
-      <c r="AP50" s="271"/>
-      <c r="AQ50" s="270"/>
-      <c r="AR50" s="270"/>
-      <c r="AS50" s="270"/>
-      <c r="AT50" s="270"/>
-      <c r="AU50" s="270"/>
-      <c r="AV50" s="270"/>
-      <c r="AW50" s="270"/>
-      <c r="AX50" s="270"/>
-      <c r="AY50" s="270"/>
-      <c r="AZ50" s="270"/>
-      <c r="BA50" s="270"/>
-      <c r="BB50" s="270"/>
-      <c r="BC50" s="270"/>
-      <c r="BD50" s="270"/>
-      <c r="BE50" s="270"/>
+      <c r="C50" s="256"/>
+      <c r="D50" s="256"/>
+      <c r="E50" s="256"/>
+      <c r="F50" s="256"/>
+      <c r="G50" s="256"/>
+      <c r="H50" s="256"/>
+      <c r="I50" s="256"/>
+      <c r="J50" s="256"/>
+      <c r="K50" s="256"/>
+      <c r="L50" s="256"/>
+      <c r="M50" s="256"/>
+      <c r="N50" s="256"/>
+      <c r="O50" s="256"/>
+      <c r="P50" s="256"/>
+      <c r="Q50" s="256"/>
+      <c r="R50" s="256"/>
+      <c r="S50" s="256"/>
+      <c r="T50" s="256"/>
+      <c r="U50" s="256"/>
+      <c r="V50" s="256"/>
+      <c r="W50" s="256"/>
+      <c r="X50" s="256"/>
+      <c r="Y50" s="257"/>
+      <c r="Z50" s="257"/>
+      <c r="AA50" s="257"/>
+      <c r="AB50" s="257"/>
+      <c r="AC50" s="257"/>
+      <c r="AD50" s="257"/>
+      <c r="AE50" s="257"/>
+      <c r="AF50" s="256"/>
+      <c r="AG50" s="256"/>
+      <c r="AH50" s="257"/>
+      <c r="AI50" s="257"/>
+      <c r="AJ50" s="257"/>
+      <c r="AK50" s="257"/>
+      <c r="AL50" s="257"/>
+      <c r="AM50" s="257"/>
+      <c r="AN50" s="257"/>
+      <c r="AO50" s="257"/>
+      <c r="AP50" s="257"/>
+      <c r="AQ50" s="256"/>
+      <c r="AR50" s="256"/>
+      <c r="AS50" s="256"/>
+      <c r="AT50" s="256"/>
+      <c r="AU50" s="256"/>
+      <c r="AV50" s="256"/>
+      <c r="AW50" s="256"/>
+      <c r="AX50" s="256"/>
+      <c r="AY50" s="256"/>
+      <c r="AZ50" s="256"/>
+      <c r="BA50" s="256"/>
+      <c r="BB50" s="256"/>
+      <c r="BC50" s="256"/>
+      <c r="BD50" s="256"/>
+      <c r="BE50" s="256"/>
     </row>
     <row r="51" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B51" s="264">
+      <c r="B51" s="246">
         <v>2</v>
       </c>
-      <c r="C51" s="265"/>
+      <c r="C51" s="247"/>
       <c r="D51" s="22" t="s">
         <v>107</v>
       </c>
@@ -19601,10 +19601,10 @@
       </c>
     </row>
     <row r="52" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B52" s="264">
+      <c r="B52" s="246">
         <v>3</v>
       </c>
-      <c r="C52" s="265"/>
+      <c r="C52" s="247"/>
       <c r="D52" s="22" t="s">
         <v>108</v>
       </c>
@@ -19679,10 +19679,10 @@
       </c>
     </row>
     <row r="53" spans="1:62" ht="26.4" customHeight="1">
-      <c r="B53" s="264">
+      <c r="B53" s="246">
         <v>4</v>
       </c>
-      <c r="C53" s="265"/>
+      <c r="C53" s="247"/>
       <c r="D53" s="22" t="s">
         <v>149</v>
       </c>
@@ -19753,10 +19753,10 @@
       <c r="BE53" s="302"/>
     </row>
     <row r="54" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B54" s="264">
+      <c r="B54" s="246">
         <v>5</v>
       </c>
-      <c r="C54" s="265"/>
+      <c r="C54" s="247"/>
       <c r="D54" s="22" t="s">
         <v>284</v>
       </c>
@@ -19823,10 +19823,10 @@
       <c r="BE54" s="43"/>
     </row>
     <row r="55" spans="1:62" ht="28.2" customHeight="1">
-      <c r="B55" s="264">
+      <c r="B55" s="246">
         <v>6</v>
       </c>
-      <c r="C55" s="265"/>
+      <c r="C55" s="247"/>
       <c r="D55" s="22" t="s">
         <v>56</v>
       </c>
@@ -19863,10 +19863,10 @@
       <c r="AA55" s="42"/>
       <c r="AB55" s="42"/>
       <c r="AC55" s="43"/>
-      <c r="AD55" s="245">
+      <c r="AD55" s="261">
         <v>100</v>
       </c>
-      <c r="AE55" s="247"/>
+      <c r="AE55" s="263"/>
       <c r="AF55" s="22">
         <v>20</v>
       </c>
@@ -19903,10 +19903,10 @@
       <c r="BE55" s="302"/>
     </row>
     <row r="56" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B56" s="264">
+      <c r="B56" s="246">
         <v>7</v>
       </c>
-      <c r="C56" s="265"/>
+      <c r="C56" s="247"/>
       <c r="D56" s="22" t="s">
         <v>5</v>
       </c>
@@ -19975,10 +19975,10 @@
       </c>
     </row>
     <row r="57" spans="1:62" ht="26.4" customHeight="1">
-      <c r="B57" s="264">
+      <c r="B57" s="246">
         <v>8</v>
       </c>
-      <c r="C57" s="265"/>
+      <c r="C57" s="247"/>
       <c r="D57" s="22" t="s">
         <v>56</v>
       </c>
@@ -20065,10 +20065,10 @@
     </row>
     <row r="58" spans="1:62" ht="13.8" customHeight="1">
       <c r="A58" s="6"/>
-      <c r="B58" s="264">
+      <c r="B58" s="246">
         <v>8</v>
       </c>
-      <c r="C58" s="265"/>
+      <c r="C58" s="247"/>
       <c r="D58" s="22" t="s">
         <v>382</v>
       </c>
@@ -20137,10 +20137,10 @@
     </row>
     <row r="59" spans="1:62" ht="46.2" customHeight="1">
       <c r="A59" s="6"/>
-      <c r="B59" s="264">
+      <c r="B59" s="246">
         <v>9</v>
       </c>
-      <c r="C59" s="265"/>
+      <c r="C59" s="247"/>
       <c r="D59" s="22" t="s">
         <v>56</v>
       </c>
@@ -20225,10 +20225,10 @@
     </row>
     <row r="60" spans="1:62" ht="49.2" customHeight="1">
       <c r="A60" s="6"/>
-      <c r="B60" s="264">
+      <c r="B60" s="246">
         <v>10</v>
       </c>
-      <c r="C60" s="265"/>
+      <c r="C60" s="247"/>
       <c r="D60" s="22" t="s">
         <v>56</v>
       </c>
@@ -20315,10 +20315,10 @@
       </c>
     </row>
     <row r="61" spans="1:62" ht="39" customHeight="1">
-      <c r="B61" s="264">
+      <c r="B61" s="246">
         <v>9</v>
       </c>
-      <c r="C61" s="265"/>
+      <c r="C61" s="247"/>
       <c r="D61" s="22" t="s">
         <v>74</v>
       </c>
@@ -20388,10 +20388,10 @@
       </c>
     </row>
     <row r="62" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B62" s="264">
+      <c r="B62" s="246">
         <v>10</v>
       </c>
-      <c r="C62" s="265"/>
+      <c r="C62" s="247"/>
       <c r="D62" s="22" t="s">
         <v>56</v>
       </c>
@@ -20432,14 +20432,14 @@
       <c r="AA62" s="42"/>
       <c r="AB62" s="42"/>
       <c r="AC62" s="43"/>
-      <c r="AD62" s="245">
+      <c r="AD62" s="261">
         <v>100</v>
       </c>
-      <c r="AE62" s="247"/>
-      <c r="AF62" s="245">
+      <c r="AE62" s="263"/>
+      <c r="AF62" s="261">
         <v>20</v>
       </c>
-      <c r="AG62" s="247"/>
+      <c r="AG62" s="263"/>
       <c r="AH62" s="40" t="s">
         <v>218</v>
       </c>
@@ -20475,10 +20475,10 @@
       </c>
     </row>
     <row r="63" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B63" s="264">
+      <c r="B63" s="246">
         <v>11</v>
       </c>
-      <c r="C63" s="265"/>
+      <c r="C63" s="247"/>
       <c r="D63" s="22" t="s">
         <v>200</v>
       </c>
@@ -20543,10 +20543,10 @@
       <c r="BE63" s="101"/>
     </row>
     <row r="64" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B64" s="264">
+      <c r="B64" s="246">
         <v>12</v>
       </c>
-      <c r="C64" s="265"/>
+      <c r="C64" s="247"/>
       <c r="D64" s="22" t="s">
         <v>109</v>
       </c>
@@ -20615,10 +20615,10 @@
       <c r="BE64" s="101"/>
     </row>
     <row r="65" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B65" s="264">
+      <c r="B65" s="246">
         <v>13</v>
       </c>
-      <c r="C65" s="265"/>
+      <c r="C65" s="247"/>
       <c r="D65" s="22" t="s">
         <v>199</v>
       </c>
@@ -20687,10 +20687,10 @@
       <c r="BE65" s="101"/>
     </row>
     <row r="66" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B66" s="264">
+      <c r="B66" s="246">
         <v>14</v>
       </c>
-      <c r="C66" s="265"/>
+      <c r="C66" s="247"/>
       <c r="D66" s="22" t="s">
         <v>273</v>
       </c>
@@ -20757,70 +20757,70 @@
       <c r="BE66" s="101"/>
     </row>
     <row r="67" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B67" s="251" t="s">
+      <c r="B67" s="248" t="s">
         <v>98</v>
       </c>
-      <c r="C67" s="252"/>
-      <c r="D67" s="252"/>
-      <c r="E67" s="252"/>
-      <c r="F67" s="252"/>
-      <c r="G67" s="252"/>
-      <c r="H67" s="252"/>
-      <c r="I67" s="252"/>
-      <c r="J67" s="252"/>
-      <c r="K67" s="252"/>
-      <c r="L67" s="252"/>
-      <c r="M67" s="252"/>
-      <c r="N67" s="252"/>
-      <c r="O67" s="252"/>
-      <c r="P67" s="252"/>
-      <c r="Q67" s="252"/>
-      <c r="R67" s="252"/>
-      <c r="S67" s="252"/>
-      <c r="T67" s="252"/>
-      <c r="U67" s="252"/>
-      <c r="V67" s="252"/>
-      <c r="W67" s="252"/>
-      <c r="X67" s="252"/>
-      <c r="Y67" s="252"/>
-      <c r="Z67" s="252"/>
-      <c r="AA67" s="252"/>
-      <c r="AB67" s="252"/>
-      <c r="AC67" s="252"/>
-      <c r="AD67" s="252"/>
-      <c r="AE67" s="252"/>
-      <c r="AF67" s="252"/>
-      <c r="AG67" s="252"/>
-      <c r="AH67" s="252"/>
-      <c r="AI67" s="252"/>
-      <c r="AJ67" s="252"/>
-      <c r="AK67" s="252"/>
-      <c r="AL67" s="252"/>
-      <c r="AM67" s="252"/>
-      <c r="AN67" s="252"/>
-      <c r="AO67" s="252"/>
-      <c r="AP67" s="252"/>
-      <c r="AQ67" s="252"/>
-      <c r="AR67" s="252"/>
-      <c r="AS67" s="252"/>
-      <c r="AT67" s="252"/>
-      <c r="AU67" s="252"/>
-      <c r="AV67" s="252"/>
-      <c r="AW67" s="252"/>
-      <c r="AX67" s="252"/>
-      <c r="AY67" s="252"/>
-      <c r="AZ67" s="252"/>
-      <c r="BA67" s="252"/>
-      <c r="BB67" s="252"/>
-      <c r="BC67" s="252"/>
-      <c r="BD67" s="252"/>
-      <c r="BE67" s="252"/>
+      <c r="C67" s="249"/>
+      <c r="D67" s="249"/>
+      <c r="E67" s="249"/>
+      <c r="F67" s="249"/>
+      <c r="G67" s="249"/>
+      <c r="H67" s="249"/>
+      <c r="I67" s="249"/>
+      <c r="J67" s="249"/>
+      <c r="K67" s="249"/>
+      <c r="L67" s="249"/>
+      <c r="M67" s="249"/>
+      <c r="N67" s="249"/>
+      <c r="O67" s="249"/>
+      <c r="P67" s="249"/>
+      <c r="Q67" s="249"/>
+      <c r="R67" s="249"/>
+      <c r="S67" s="249"/>
+      <c r="T67" s="249"/>
+      <c r="U67" s="249"/>
+      <c r="V67" s="249"/>
+      <c r="W67" s="249"/>
+      <c r="X67" s="249"/>
+      <c r="Y67" s="249"/>
+      <c r="Z67" s="249"/>
+      <c r="AA67" s="249"/>
+      <c r="AB67" s="249"/>
+      <c r="AC67" s="249"/>
+      <c r="AD67" s="249"/>
+      <c r="AE67" s="249"/>
+      <c r="AF67" s="249"/>
+      <c r="AG67" s="249"/>
+      <c r="AH67" s="249"/>
+      <c r="AI67" s="249"/>
+      <c r="AJ67" s="249"/>
+      <c r="AK67" s="249"/>
+      <c r="AL67" s="249"/>
+      <c r="AM67" s="249"/>
+      <c r="AN67" s="249"/>
+      <c r="AO67" s="249"/>
+      <c r="AP67" s="249"/>
+      <c r="AQ67" s="249"/>
+      <c r="AR67" s="249"/>
+      <c r="AS67" s="249"/>
+      <c r="AT67" s="249"/>
+      <c r="AU67" s="249"/>
+      <c r="AV67" s="249"/>
+      <c r="AW67" s="249"/>
+      <c r="AX67" s="249"/>
+      <c r="AY67" s="249"/>
+      <c r="AZ67" s="249"/>
+      <c r="BA67" s="249"/>
+      <c r="BB67" s="249"/>
+      <c r="BC67" s="249"/>
+      <c r="BD67" s="249"/>
+      <c r="BE67" s="249"/>
     </row>
     <row r="68" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B68" s="264">
+      <c r="B68" s="246">
         <v>13</v>
       </c>
-      <c r="C68" s="265"/>
+      <c r="C68" s="247"/>
       <c r="D68" s="22" t="s">
         <v>132</v>
       </c>
@@ -20887,10 +20887,10 @@
       <c r="BE68" s="113"/>
     </row>
     <row r="69" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B69" s="264">
+      <c r="B69" s="246">
         <v>14</v>
       </c>
-      <c r="C69" s="265"/>
+      <c r="C69" s="247"/>
       <c r="D69" s="22" t="s">
         <v>134</v>
       </c>
@@ -20957,10 +20957,10 @@
       <c r="BE69" s="113"/>
     </row>
     <row r="70" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B70" s="264">
+      <c r="B70" s="246">
         <v>15</v>
       </c>
-      <c r="C70" s="265"/>
+      <c r="C70" s="247"/>
       <c r="D70" s="22" t="s">
         <v>135</v>
       </c>
@@ -21029,10 +21029,10 @@
       <c r="BE70" s="113"/>
     </row>
     <row r="71" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B71" s="264">
+      <c r="B71" s="246">
         <v>16</v>
       </c>
-      <c r="C71" s="265"/>
+      <c r="C71" s="247"/>
       <c r="D71" s="22" t="s">
         <v>138</v>
       </c>
@@ -21101,10 +21101,10 @@
       <c r="BE71" s="113"/>
     </row>
     <row r="72" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B72" s="264">
+      <c r="B72" s="246">
         <v>17</v>
       </c>
-      <c r="C72" s="265"/>
+      <c r="C72" s="247"/>
       <c r="D72" s="22" t="s">
         <v>141</v>
       </c>
@@ -21173,10 +21173,10 @@
       <c r="BE72" s="113"/>
     </row>
     <row r="73" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B73" s="264">
+      <c r="B73" s="246">
         <v>18</v>
       </c>
-      <c r="C73" s="265"/>
+      <c r="C73" s="247"/>
       <c r="D73" s="22" t="s">
         <v>144</v>
       </c>
@@ -21245,10 +21245,10 @@
       <c r="BE73" s="113"/>
     </row>
     <row r="74" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B74" s="264">
+      <c r="B74" s="246">
         <v>19</v>
       </c>
-      <c r="C74" s="265"/>
+      <c r="C74" s="247"/>
       <c r="D74" s="22" t="s">
         <v>145</v>
       </c>
@@ -21317,10 +21317,10 @@
       <c r="BE74" s="113"/>
     </row>
     <row r="75" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B75" s="264">
+      <c r="B75" s="246">
         <v>20</v>
       </c>
-      <c r="C75" s="265"/>
+      <c r="C75" s="247"/>
       <c r="D75" s="22" t="s">
         <v>146</v>
       </c>
@@ -21385,10 +21385,10 @@
       <c r="BE75" s="113"/>
     </row>
     <row r="76" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B76" s="264">
+      <c r="B76" s="246">
         <v>21</v>
       </c>
-      <c r="C76" s="265"/>
+      <c r="C76" s="247"/>
       <c r="D76" s="22" t="s">
         <v>141</v>
       </c>
@@ -21457,10 +21457,10 @@
       <c r="BE76" s="113"/>
     </row>
     <row r="77" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B77" s="264">
+      <c r="B77" s="246">
         <v>22</v>
       </c>
-      <c r="C77" s="265"/>
+      <c r="C77" s="247"/>
       <c r="D77" s="22" t="s">
         <v>144</v>
       </c>
@@ -21529,10 +21529,10 @@
       <c r="BE77" s="113"/>
     </row>
     <row r="78" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B78" s="264">
+      <c r="B78" s="246">
         <v>23</v>
       </c>
-      <c r="C78" s="265"/>
+      <c r="C78" s="247"/>
       <c r="D78" s="22" t="s">
         <v>145</v>
       </c>
@@ -21601,10 +21601,10 @@
       <c r="BE78" s="113"/>
     </row>
     <row r="79" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B79" s="264">
+      <c r="B79" s="246">
         <v>24</v>
       </c>
-      <c r="C79" s="265"/>
+      <c r="C79" s="247"/>
       <c r="D79" s="22" t="s">
         <v>148</v>
       </c>
@@ -21731,10 +21731,10 @@
       <c r="BE80" s="303"/>
     </row>
     <row r="81" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B81" s="264">
+      <c r="B81" s="246">
         <v>26</v>
       </c>
-      <c r="C81" s="265"/>
+      <c r="C81" s="247"/>
       <c r="D81" s="22" t="s">
         <v>122</v>
       </c>
@@ -21801,10 +21801,10 @@
       <c r="BE81" s="101"/>
     </row>
     <row r="82" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B82" s="264">
+      <c r="B82" s="246">
         <v>27</v>
       </c>
-      <c r="C82" s="265"/>
+      <c r="C82" s="247"/>
       <c r="D82" s="22" t="s">
         <v>124</v>
       </c>
@@ -21871,10 +21871,10 @@
       <c r="BE82" s="101"/>
     </row>
     <row r="83" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B83" s="264">
+      <c r="B83" s="246">
         <v>28</v>
       </c>
-      <c r="C83" s="265"/>
+      <c r="C83" s="247"/>
       <c r="D83" s="22" t="s">
         <v>125</v>
       </c>
@@ -22001,10 +22001,10 @@
       <c r="BE84" s="303"/>
     </row>
     <row r="85" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B85" s="264">
+      <c r="B85" s="246">
         <v>29</v>
       </c>
-      <c r="C85" s="265"/>
+      <c r="C85" s="247"/>
       <c r="D85" s="22" t="s">
         <v>122</v>
       </c>
@@ -22052,29 +22052,29 @@
       <c r="AN85" s="42"/>
       <c r="AO85" s="42"/>
       <c r="AP85" s="43"/>
-      <c r="AQ85" s="278" t="s">
+      <c r="AQ85" s="270" t="s">
         <v>207</v>
       </c>
-      <c r="AR85" s="279"/>
-      <c r="AS85" s="279"/>
-      <c r="AT85" s="279"/>
-      <c r="AU85" s="279"/>
-      <c r="AV85" s="279"/>
-      <c r="AW85" s="279"/>
-      <c r="AX85" s="279"/>
-      <c r="AY85" s="279"/>
-      <c r="AZ85" s="279"/>
-      <c r="BA85" s="279"/>
-      <c r="BB85" s="279"/>
-      <c r="BC85" s="279"/>
-      <c r="BD85" s="279"/>
-      <c r="BE85" s="280"/>
+      <c r="AR85" s="271"/>
+      <c r="AS85" s="271"/>
+      <c r="AT85" s="271"/>
+      <c r="AU85" s="271"/>
+      <c r="AV85" s="271"/>
+      <c r="AW85" s="271"/>
+      <c r="AX85" s="271"/>
+      <c r="AY85" s="271"/>
+      <c r="AZ85" s="271"/>
+      <c r="BA85" s="271"/>
+      <c r="BB85" s="271"/>
+      <c r="BC85" s="271"/>
+      <c r="BD85" s="271"/>
+      <c r="BE85" s="272"/>
     </row>
     <row r="86" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B86" s="264">
+      <c r="B86" s="246">
         <v>30</v>
       </c>
-      <c r="C86" s="265"/>
+      <c r="C86" s="247"/>
       <c r="D86" s="22" t="s">
         <v>124</v>
       </c>
@@ -22141,10 +22141,10 @@
       <c r="BE86" s="101"/>
     </row>
     <row r="87" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B87" s="264">
+      <c r="B87" s="246">
         <v>31</v>
       </c>
-      <c r="C87" s="265"/>
+      <c r="C87" s="247"/>
       <c r="D87" s="22" t="s">
         <v>125</v>
       </c>
@@ -22211,70 +22211,70 @@
       <c r="BE87" s="101"/>
     </row>
     <row r="88" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B88" s="270" t="s">
+      <c r="B88" s="256" t="s">
         <v>126</v>
       </c>
-      <c r="C88" s="270"/>
-      <c r="D88" s="270"/>
-      <c r="E88" s="270"/>
-      <c r="F88" s="270"/>
-      <c r="G88" s="270"/>
-      <c r="H88" s="270"/>
-      <c r="I88" s="270"/>
-      <c r="J88" s="270"/>
-      <c r="K88" s="270"/>
-      <c r="L88" s="270"/>
-      <c r="M88" s="270"/>
-      <c r="N88" s="270"/>
-      <c r="O88" s="270"/>
-      <c r="P88" s="270"/>
-      <c r="Q88" s="270"/>
-      <c r="R88" s="270"/>
-      <c r="S88" s="270"/>
-      <c r="T88" s="270"/>
-      <c r="U88" s="270"/>
-      <c r="V88" s="270"/>
-      <c r="W88" s="270"/>
-      <c r="X88" s="270"/>
-      <c r="Y88" s="271"/>
-      <c r="Z88" s="271"/>
-      <c r="AA88" s="271"/>
-      <c r="AB88" s="271"/>
-      <c r="AC88" s="271"/>
-      <c r="AD88" s="271"/>
-      <c r="AE88" s="271"/>
-      <c r="AF88" s="270"/>
-      <c r="AG88" s="270"/>
-      <c r="AH88" s="271"/>
-      <c r="AI88" s="271"/>
-      <c r="AJ88" s="271"/>
-      <c r="AK88" s="271"/>
-      <c r="AL88" s="271"/>
-      <c r="AM88" s="271"/>
-      <c r="AN88" s="271"/>
-      <c r="AO88" s="271"/>
-      <c r="AP88" s="271"/>
-      <c r="AQ88" s="270"/>
-      <c r="AR88" s="270"/>
-      <c r="AS88" s="270"/>
-      <c r="AT88" s="270"/>
-      <c r="AU88" s="270"/>
-      <c r="AV88" s="270"/>
-      <c r="AW88" s="270"/>
-      <c r="AX88" s="270"/>
-      <c r="AY88" s="270"/>
-      <c r="AZ88" s="270"/>
-      <c r="BA88" s="270"/>
-      <c r="BB88" s="270"/>
-      <c r="BC88" s="270"/>
-      <c r="BD88" s="270"/>
-      <c r="BE88" s="270"/>
+      <c r="C88" s="256"/>
+      <c r="D88" s="256"/>
+      <c r="E88" s="256"/>
+      <c r="F88" s="256"/>
+      <c r="G88" s="256"/>
+      <c r="H88" s="256"/>
+      <c r="I88" s="256"/>
+      <c r="J88" s="256"/>
+      <c r="K88" s="256"/>
+      <c r="L88" s="256"/>
+      <c r="M88" s="256"/>
+      <c r="N88" s="256"/>
+      <c r="O88" s="256"/>
+      <c r="P88" s="256"/>
+      <c r="Q88" s="256"/>
+      <c r="R88" s="256"/>
+      <c r="S88" s="256"/>
+      <c r="T88" s="256"/>
+      <c r="U88" s="256"/>
+      <c r="V88" s="256"/>
+      <c r="W88" s="256"/>
+      <c r="X88" s="256"/>
+      <c r="Y88" s="257"/>
+      <c r="Z88" s="257"/>
+      <c r="AA88" s="257"/>
+      <c r="AB88" s="257"/>
+      <c r="AC88" s="257"/>
+      <c r="AD88" s="257"/>
+      <c r="AE88" s="257"/>
+      <c r="AF88" s="256"/>
+      <c r="AG88" s="256"/>
+      <c r="AH88" s="257"/>
+      <c r="AI88" s="257"/>
+      <c r="AJ88" s="257"/>
+      <c r="AK88" s="257"/>
+      <c r="AL88" s="257"/>
+      <c r="AM88" s="257"/>
+      <c r="AN88" s="257"/>
+      <c r="AO88" s="257"/>
+      <c r="AP88" s="257"/>
+      <c r="AQ88" s="256"/>
+      <c r="AR88" s="256"/>
+      <c r="AS88" s="256"/>
+      <c r="AT88" s="256"/>
+      <c r="AU88" s="256"/>
+      <c r="AV88" s="256"/>
+      <c r="AW88" s="256"/>
+      <c r="AX88" s="256"/>
+      <c r="AY88" s="256"/>
+      <c r="AZ88" s="256"/>
+      <c r="BA88" s="256"/>
+      <c r="BB88" s="256"/>
+      <c r="BC88" s="256"/>
+      <c r="BD88" s="256"/>
+      <c r="BE88" s="256"/>
     </row>
     <row r="89" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B89" s="268">
+      <c r="B89" s="254">
         <v>32</v>
       </c>
-      <c r="C89" s="269"/>
+      <c r="C89" s="255"/>
       <c r="D89" s="99" t="s">
         <v>214</v>
       </c>
@@ -22386,198 +22386,198 @@
       <c r="O91" s="174"/>
     </row>
     <row r="92" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B92" s="258" t="s">
+      <c r="B92" s="264" t="s">
         <v>0</v>
       </c>
-      <c r="C92" s="259"/>
-      <c r="D92" s="258" t="s">
+      <c r="C92" s="266"/>
+      <c r="D92" s="264" t="s">
         <v>12</v>
       </c>
-      <c r="E92" s="262"/>
-      <c r="F92" s="262"/>
-      <c r="G92" s="262"/>
-      <c r="H92" s="262"/>
-      <c r="I92" s="259"/>
-      <c r="J92" s="258" t="s">
+      <c r="E92" s="265"/>
+      <c r="F92" s="265"/>
+      <c r="G92" s="265"/>
+      <c r="H92" s="265"/>
+      <c r="I92" s="266"/>
+      <c r="J92" s="264" t="s">
         <v>1</v>
       </c>
-      <c r="K92" s="262"/>
-      <c r="L92" s="262"/>
-      <c r="M92" s="262"/>
-      <c r="N92" s="262"/>
-      <c r="O92" s="262"/>
-      <c r="P92" s="259"/>
-      <c r="Q92" s="258" t="s">
+      <c r="K92" s="265"/>
+      <c r="L92" s="265"/>
+      <c r="M92" s="265"/>
+      <c r="N92" s="265"/>
+      <c r="O92" s="265"/>
+      <c r="P92" s="266"/>
+      <c r="Q92" s="264" t="s">
         <v>21</v>
       </c>
-      <c r="R92" s="262"/>
-      <c r="S92" s="262"/>
-      <c r="T92" s="259"/>
-      <c r="U92" s="258" t="s">
+      <c r="R92" s="265"/>
+      <c r="S92" s="265"/>
+      <c r="T92" s="266"/>
+      <c r="U92" s="264" t="s">
         <v>22</v>
       </c>
-      <c r="V92" s="262"/>
-      <c r="W92" s="259"/>
-      <c r="X92" s="258" t="s">
+      <c r="V92" s="265"/>
+      <c r="W92" s="266"/>
+      <c r="X92" s="264" t="s">
         <v>15</v>
       </c>
-      <c r="Y92" s="262"/>
-      <c r="Z92" s="262"/>
-      <c r="AA92" s="262"/>
-      <c r="AB92" s="262"/>
-      <c r="AC92" s="262"/>
-      <c r="AD92" s="262"/>
-      <c r="AE92" s="262"/>
-      <c r="AF92" s="262"/>
-      <c r="AG92" s="262"/>
-      <c r="AH92" s="262"/>
-      <c r="AI92" s="262"/>
-      <c r="AJ92" s="262"/>
-      <c r="AK92" s="262"/>
-      <c r="AL92" s="262"/>
-      <c r="AM92" s="262"/>
-      <c r="AN92" s="262"/>
-      <c r="AO92" s="262"/>
-      <c r="AP92" s="262"/>
-      <c r="AQ92" s="262"/>
-      <c r="AR92" s="262"/>
-      <c r="AS92" s="262"/>
-      <c r="AT92" s="262"/>
-      <c r="AU92" s="262"/>
-      <c r="AV92" s="262"/>
-      <c r="AW92" s="262"/>
-      <c r="AX92" s="262"/>
-      <c r="AY92" s="262"/>
-      <c r="AZ92" s="262"/>
-      <c r="BA92" s="262"/>
-      <c r="BB92" s="262"/>
-      <c r="BC92" s="262"/>
-      <c r="BD92" s="262"/>
-      <c r="BE92" s="259"/>
+      <c r="Y92" s="265"/>
+      <c r="Z92" s="265"/>
+      <c r="AA92" s="265"/>
+      <c r="AB92" s="265"/>
+      <c r="AC92" s="265"/>
+      <c r="AD92" s="265"/>
+      <c r="AE92" s="265"/>
+      <c r="AF92" s="265"/>
+      <c r="AG92" s="265"/>
+      <c r="AH92" s="265"/>
+      <c r="AI92" s="265"/>
+      <c r="AJ92" s="265"/>
+      <c r="AK92" s="265"/>
+      <c r="AL92" s="265"/>
+      <c r="AM92" s="265"/>
+      <c r="AN92" s="265"/>
+      <c r="AO92" s="265"/>
+      <c r="AP92" s="265"/>
+      <c r="AQ92" s="265"/>
+      <c r="AR92" s="265"/>
+      <c r="AS92" s="265"/>
+      <c r="AT92" s="265"/>
+      <c r="AU92" s="265"/>
+      <c r="AV92" s="265"/>
+      <c r="AW92" s="265"/>
+      <c r="AX92" s="265"/>
+      <c r="AY92" s="265"/>
+      <c r="AZ92" s="265"/>
+      <c r="BA92" s="265"/>
+      <c r="BB92" s="265"/>
+      <c r="BC92" s="265"/>
+      <c r="BD92" s="265"/>
+      <c r="BE92" s="266"/>
     </row>
     <row r="93" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B93" s="260"/>
-      <c r="C93" s="261"/>
-      <c r="D93" s="260"/>
-      <c r="E93" s="263"/>
-      <c r="F93" s="263"/>
-      <c r="G93" s="263"/>
-      <c r="H93" s="263"/>
-      <c r="I93" s="261"/>
-      <c r="J93" s="260"/>
-      <c r="K93" s="263"/>
-      <c r="L93" s="263"/>
-      <c r="M93" s="263"/>
-      <c r="N93" s="263"/>
-      <c r="O93" s="263"/>
-      <c r="P93" s="261"/>
-      <c r="Q93" s="260"/>
-      <c r="R93" s="263"/>
-      <c r="S93" s="263"/>
-      <c r="T93" s="261"/>
-      <c r="U93" s="260"/>
-      <c r="V93" s="263"/>
-      <c r="W93" s="261"/>
-      <c r="X93" s="260"/>
-      <c r="Y93" s="263"/>
-      <c r="Z93" s="263"/>
-      <c r="AA93" s="263"/>
-      <c r="AB93" s="263"/>
-      <c r="AC93" s="263"/>
-      <c r="AD93" s="263"/>
-      <c r="AE93" s="263"/>
-      <c r="AF93" s="263"/>
-      <c r="AG93" s="263"/>
-      <c r="AH93" s="263"/>
-      <c r="AI93" s="263"/>
-      <c r="AJ93" s="263"/>
-      <c r="AK93" s="263"/>
-      <c r="AL93" s="263"/>
-      <c r="AM93" s="263"/>
-      <c r="AN93" s="263"/>
-      <c r="AO93" s="263"/>
-      <c r="AP93" s="263"/>
-      <c r="AQ93" s="263"/>
-      <c r="AR93" s="263"/>
-      <c r="AS93" s="263"/>
-      <c r="AT93" s="263"/>
-      <c r="AU93" s="263"/>
-      <c r="AV93" s="263"/>
-      <c r="AW93" s="263"/>
-      <c r="AX93" s="263"/>
-      <c r="AY93" s="263"/>
-      <c r="AZ93" s="263"/>
-      <c r="BA93" s="263"/>
-      <c r="BB93" s="263"/>
-      <c r="BC93" s="263"/>
-      <c r="BD93" s="263"/>
-      <c r="BE93" s="261"/>
+      <c r="B93" s="267"/>
+      <c r="C93" s="269"/>
+      <c r="D93" s="267"/>
+      <c r="E93" s="268"/>
+      <c r="F93" s="268"/>
+      <c r="G93" s="268"/>
+      <c r="H93" s="268"/>
+      <c r="I93" s="269"/>
+      <c r="J93" s="267"/>
+      <c r="K93" s="268"/>
+      <c r="L93" s="268"/>
+      <c r="M93" s="268"/>
+      <c r="N93" s="268"/>
+      <c r="O93" s="268"/>
+      <c r="P93" s="269"/>
+      <c r="Q93" s="267"/>
+      <c r="R93" s="268"/>
+      <c r="S93" s="268"/>
+      <c r="T93" s="269"/>
+      <c r="U93" s="267"/>
+      <c r="V93" s="268"/>
+      <c r="W93" s="269"/>
+      <c r="X93" s="267"/>
+      <c r="Y93" s="268"/>
+      <c r="Z93" s="268"/>
+      <c r="AA93" s="268"/>
+      <c r="AB93" s="268"/>
+      <c r="AC93" s="268"/>
+      <c r="AD93" s="268"/>
+      <c r="AE93" s="268"/>
+      <c r="AF93" s="268"/>
+      <c r="AG93" s="268"/>
+      <c r="AH93" s="268"/>
+      <c r="AI93" s="268"/>
+      <c r="AJ93" s="268"/>
+      <c r="AK93" s="268"/>
+      <c r="AL93" s="268"/>
+      <c r="AM93" s="268"/>
+      <c r="AN93" s="268"/>
+      <c r="AO93" s="268"/>
+      <c r="AP93" s="268"/>
+      <c r="AQ93" s="268"/>
+      <c r="AR93" s="268"/>
+      <c r="AS93" s="268"/>
+      <c r="AT93" s="268"/>
+      <c r="AU93" s="268"/>
+      <c r="AV93" s="268"/>
+      <c r="AW93" s="268"/>
+      <c r="AX93" s="268"/>
+      <c r="AY93" s="268"/>
+      <c r="AZ93" s="268"/>
+      <c r="BA93" s="268"/>
+      <c r="BB93" s="268"/>
+      <c r="BC93" s="268"/>
+      <c r="BD93" s="268"/>
+      <c r="BE93" s="269"/>
     </row>
     <row r="94" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B94" s="251" t="s">
+      <c r="B94" s="248" t="s">
         <v>157</v>
       </c>
-      <c r="C94" s="252"/>
-      <c r="D94" s="252"/>
-      <c r="E94" s="252"/>
-      <c r="F94" s="252"/>
-      <c r="G94" s="252"/>
-      <c r="H94" s="252"/>
-      <c r="I94" s="252"/>
-      <c r="J94" s="252"/>
-      <c r="K94" s="252"/>
-      <c r="L94" s="252"/>
-      <c r="M94" s="252"/>
-      <c r="N94" s="252"/>
-      <c r="O94" s="252"/>
-      <c r="P94" s="252"/>
-      <c r="Q94" s="252"/>
-      <c r="R94" s="252"/>
-      <c r="S94" s="252"/>
-      <c r="T94" s="252"/>
-      <c r="U94" s="252"/>
-      <c r="V94" s="252"/>
-      <c r="W94" s="252"/>
-      <c r="X94" s="252"/>
-      <c r="Y94" s="252"/>
-      <c r="Z94" s="252"/>
-      <c r="AA94" s="252"/>
-      <c r="AB94" s="252"/>
-      <c r="AC94" s="252"/>
-      <c r="AD94" s="252"/>
-      <c r="AE94" s="252"/>
-      <c r="AF94" s="252"/>
-      <c r="AG94" s="252"/>
-      <c r="AH94" s="252"/>
-      <c r="AI94" s="252"/>
-      <c r="AJ94" s="252"/>
-      <c r="AK94" s="252"/>
-      <c r="AL94" s="252"/>
-      <c r="AM94" s="252"/>
-      <c r="AN94" s="252"/>
-      <c r="AO94" s="252"/>
-      <c r="AP94" s="252"/>
-      <c r="AQ94" s="252"/>
-      <c r="AR94" s="252"/>
-      <c r="AS94" s="252"/>
-      <c r="AT94" s="252"/>
-      <c r="AU94" s="252"/>
-      <c r="AV94" s="252"/>
-      <c r="AW94" s="252"/>
-      <c r="AX94" s="252"/>
-      <c r="AY94" s="252"/>
-      <c r="AZ94" s="252"/>
-      <c r="BA94" s="252"/>
-      <c r="BB94" s="252"/>
-      <c r="BC94" s="252"/>
-      <c r="BD94" s="252"/>
-      <c r="BE94" s="253"/>
+      <c r="C94" s="249"/>
+      <c r="D94" s="249"/>
+      <c r="E94" s="249"/>
+      <c r="F94" s="249"/>
+      <c r="G94" s="249"/>
+      <c r="H94" s="249"/>
+      <c r="I94" s="249"/>
+      <c r="J94" s="249"/>
+      <c r="K94" s="249"/>
+      <c r="L94" s="249"/>
+      <c r="M94" s="249"/>
+      <c r="N94" s="249"/>
+      <c r="O94" s="249"/>
+      <c r="P94" s="249"/>
+      <c r="Q94" s="249"/>
+      <c r="R94" s="249"/>
+      <c r="S94" s="249"/>
+      <c r="T94" s="249"/>
+      <c r="U94" s="249"/>
+      <c r="V94" s="249"/>
+      <c r="W94" s="249"/>
+      <c r="X94" s="249"/>
+      <c r="Y94" s="249"/>
+      <c r="Z94" s="249"/>
+      <c r="AA94" s="249"/>
+      <c r="AB94" s="249"/>
+      <c r="AC94" s="249"/>
+      <c r="AD94" s="249"/>
+      <c r="AE94" s="249"/>
+      <c r="AF94" s="249"/>
+      <c r="AG94" s="249"/>
+      <c r="AH94" s="249"/>
+      <c r="AI94" s="249"/>
+      <c r="AJ94" s="249"/>
+      <c r="AK94" s="249"/>
+      <c r="AL94" s="249"/>
+      <c r="AM94" s="249"/>
+      <c r="AN94" s="249"/>
+      <c r="AO94" s="249"/>
+      <c r="AP94" s="249"/>
+      <c r="AQ94" s="249"/>
+      <c r="AR94" s="249"/>
+      <c r="AS94" s="249"/>
+      <c r="AT94" s="249"/>
+      <c r="AU94" s="249"/>
+      <c r="AV94" s="249"/>
+      <c r="AW94" s="249"/>
+      <c r="AX94" s="249"/>
+      <c r="AY94" s="249"/>
+      <c r="AZ94" s="249"/>
+      <c r="BA94" s="249"/>
+      <c r="BB94" s="249"/>
+      <c r="BC94" s="249"/>
+      <c r="BD94" s="249"/>
+      <c r="BE94" s="250"/>
     </row>
     <row r="95" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B95" s="254">
+      <c r="B95" s="251">
         <v>1</v>
       </c>
-      <c r="C95" s="254"/>
+      <c r="C95" s="251"/>
       <c r="D95" s="37" t="s">
         <v>43</v>
       </c>
@@ -22636,70 +22636,70 @@
       <c r="BE95" s="43"/>
     </row>
     <row r="96" spans="2:57" ht="14.1" customHeight="1">
-      <c r="B96" s="251" t="s">
+      <c r="B96" s="248" t="s">
         <v>40</v>
       </c>
-      <c r="C96" s="252"/>
-      <c r="D96" s="252"/>
-      <c r="E96" s="252"/>
-      <c r="F96" s="252"/>
-      <c r="G96" s="252"/>
-      <c r="H96" s="252"/>
-      <c r="I96" s="252"/>
-      <c r="J96" s="252"/>
-      <c r="K96" s="252"/>
-      <c r="L96" s="252"/>
-      <c r="M96" s="252"/>
-      <c r="N96" s="252"/>
-      <c r="O96" s="252"/>
-      <c r="P96" s="252"/>
-      <c r="Q96" s="252"/>
-      <c r="R96" s="252"/>
-      <c r="S96" s="252"/>
-      <c r="T96" s="252"/>
-      <c r="U96" s="252"/>
-      <c r="V96" s="252"/>
-      <c r="W96" s="252"/>
-      <c r="X96" s="252"/>
-      <c r="Y96" s="252"/>
-      <c r="Z96" s="252"/>
-      <c r="AA96" s="252"/>
-      <c r="AB96" s="252"/>
-      <c r="AC96" s="252"/>
-      <c r="AD96" s="252"/>
-      <c r="AE96" s="252"/>
-      <c r="AF96" s="252"/>
-      <c r="AG96" s="252"/>
-      <c r="AH96" s="252"/>
-      <c r="AI96" s="252"/>
-      <c r="AJ96" s="252"/>
-      <c r="AK96" s="252"/>
-      <c r="AL96" s="252"/>
-      <c r="AM96" s="252"/>
-      <c r="AN96" s="252"/>
-      <c r="AO96" s="252"/>
-      <c r="AP96" s="252"/>
-      <c r="AQ96" s="252"/>
-      <c r="AR96" s="252"/>
-      <c r="AS96" s="252"/>
-      <c r="AT96" s="252"/>
-      <c r="AU96" s="252"/>
-      <c r="AV96" s="252"/>
-      <c r="AW96" s="252"/>
-      <c r="AX96" s="252"/>
-      <c r="AY96" s="252"/>
-      <c r="AZ96" s="252"/>
-      <c r="BA96" s="252"/>
-      <c r="BB96" s="252"/>
-      <c r="BC96" s="252"/>
-      <c r="BD96" s="252"/>
-      <c r="BE96" s="253"/>
+      <c r="C96" s="249"/>
+      <c r="D96" s="249"/>
+      <c r="E96" s="249"/>
+      <c r="F96" s="249"/>
+      <c r="G96" s="249"/>
+      <c r="H96" s="249"/>
+      <c r="I96" s="249"/>
+      <c r="J96" s="249"/>
+      <c r="K96" s="249"/>
+      <c r="L96" s="249"/>
+      <c r="M96" s="249"/>
+      <c r="N96" s="249"/>
+      <c r="O96" s="249"/>
+      <c r="P96" s="249"/>
+      <c r="Q96" s="249"/>
+      <c r="R96" s="249"/>
+      <c r="S96" s="249"/>
+      <c r="T96" s="249"/>
+      <c r="U96" s="249"/>
+      <c r="V96" s="249"/>
+      <c r="W96" s="249"/>
+      <c r="X96" s="249"/>
+      <c r="Y96" s="249"/>
+      <c r="Z96" s="249"/>
+      <c r="AA96" s="249"/>
+      <c r="AB96" s="249"/>
+      <c r="AC96" s="249"/>
+      <c r="AD96" s="249"/>
+      <c r="AE96" s="249"/>
+      <c r="AF96" s="249"/>
+      <c r="AG96" s="249"/>
+      <c r="AH96" s="249"/>
+      <c r="AI96" s="249"/>
+      <c r="AJ96" s="249"/>
+      <c r="AK96" s="249"/>
+      <c r="AL96" s="249"/>
+      <c r="AM96" s="249"/>
+      <c r="AN96" s="249"/>
+      <c r="AO96" s="249"/>
+      <c r="AP96" s="249"/>
+      <c r="AQ96" s="249"/>
+      <c r="AR96" s="249"/>
+      <c r="AS96" s="249"/>
+      <c r="AT96" s="249"/>
+      <c r="AU96" s="249"/>
+      <c r="AV96" s="249"/>
+      <c r="AW96" s="249"/>
+      <c r="AX96" s="249"/>
+      <c r="AY96" s="249"/>
+      <c r="AZ96" s="249"/>
+      <c r="BA96" s="249"/>
+      <c r="BB96" s="249"/>
+      <c r="BC96" s="249"/>
+      <c r="BD96" s="249"/>
+      <c r="BE96" s="250"/>
     </row>
     <row r="97" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B97" s="254">
+      <c r="B97" s="251">
         <v>1</v>
       </c>
-      <c r="C97" s="254"/>
+      <c r="C97" s="251"/>
       <c r="D97" s="37" t="s">
         <v>43</v>
       </c>
@@ -22758,70 +22758,70 @@
       <c r="BE97" s="43"/>
     </row>
     <row r="98" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B98" s="288" t="s">
+      <c r="B98" s="252" t="s">
         <v>158</v>
       </c>
-      <c r="C98" s="289"/>
-      <c r="D98" s="289"/>
-      <c r="E98" s="289"/>
-      <c r="F98" s="289"/>
-      <c r="G98" s="289"/>
-      <c r="H98" s="289"/>
-      <c r="I98" s="289"/>
-      <c r="J98" s="289"/>
-      <c r="K98" s="289"/>
-      <c r="L98" s="289"/>
-      <c r="M98" s="289"/>
-      <c r="N98" s="289"/>
-      <c r="O98" s="289"/>
-      <c r="P98" s="289"/>
-      <c r="Q98" s="289"/>
-      <c r="R98" s="289"/>
-      <c r="S98" s="289"/>
-      <c r="T98" s="289"/>
-      <c r="U98" s="289"/>
-      <c r="V98" s="289"/>
-      <c r="W98" s="289"/>
-      <c r="X98" s="289"/>
-      <c r="Y98" s="289"/>
-      <c r="Z98" s="289"/>
-      <c r="AA98" s="289"/>
-      <c r="AB98" s="289"/>
-      <c r="AC98" s="289"/>
-      <c r="AD98" s="289"/>
-      <c r="AE98" s="289"/>
-      <c r="AF98" s="289"/>
-      <c r="AG98" s="289"/>
-      <c r="AH98" s="289"/>
-      <c r="AI98" s="289"/>
-      <c r="AJ98" s="289"/>
-      <c r="AK98" s="289"/>
-      <c r="AL98" s="289"/>
-      <c r="AM98" s="289"/>
-      <c r="AN98" s="289"/>
-      <c r="AO98" s="289"/>
-      <c r="AP98" s="289"/>
-      <c r="AQ98" s="289"/>
-      <c r="AR98" s="289"/>
-      <c r="AS98" s="289"/>
-      <c r="AT98" s="289"/>
-      <c r="AU98" s="289"/>
-      <c r="AV98" s="289"/>
-      <c r="AW98" s="289"/>
-      <c r="AX98" s="289"/>
-      <c r="AY98" s="289"/>
-      <c r="AZ98" s="289"/>
-      <c r="BA98" s="289"/>
-      <c r="BB98" s="289"/>
-      <c r="BC98" s="289"/>
-      <c r="BD98" s="289"/>
-      <c r="BE98" s="289"/>
+      <c r="C98" s="253"/>
+      <c r="D98" s="253"/>
+      <c r="E98" s="253"/>
+      <c r="F98" s="253"/>
+      <c r="G98" s="253"/>
+      <c r="H98" s="253"/>
+      <c r="I98" s="253"/>
+      <c r="J98" s="253"/>
+      <c r="K98" s="253"/>
+      <c r="L98" s="253"/>
+      <c r="M98" s="253"/>
+      <c r="N98" s="253"/>
+      <c r="O98" s="253"/>
+      <c r="P98" s="253"/>
+      <c r="Q98" s="253"/>
+      <c r="R98" s="253"/>
+      <c r="S98" s="253"/>
+      <c r="T98" s="253"/>
+      <c r="U98" s="253"/>
+      <c r="V98" s="253"/>
+      <c r="W98" s="253"/>
+      <c r="X98" s="253"/>
+      <c r="Y98" s="253"/>
+      <c r="Z98" s="253"/>
+      <c r="AA98" s="253"/>
+      <c r="AB98" s="253"/>
+      <c r="AC98" s="253"/>
+      <c r="AD98" s="253"/>
+      <c r="AE98" s="253"/>
+      <c r="AF98" s="253"/>
+      <c r="AG98" s="253"/>
+      <c r="AH98" s="253"/>
+      <c r="AI98" s="253"/>
+      <c r="AJ98" s="253"/>
+      <c r="AK98" s="253"/>
+      <c r="AL98" s="253"/>
+      <c r="AM98" s="253"/>
+      <c r="AN98" s="253"/>
+      <c r="AO98" s="253"/>
+      <c r="AP98" s="253"/>
+      <c r="AQ98" s="253"/>
+      <c r="AR98" s="253"/>
+      <c r="AS98" s="253"/>
+      <c r="AT98" s="253"/>
+      <c r="AU98" s="253"/>
+      <c r="AV98" s="253"/>
+      <c r="AW98" s="253"/>
+      <c r="AX98" s="253"/>
+      <c r="AY98" s="253"/>
+      <c r="AZ98" s="253"/>
+      <c r="BA98" s="253"/>
+      <c r="BB98" s="253"/>
+      <c r="BC98" s="253"/>
+      <c r="BD98" s="253"/>
+      <c r="BE98" s="253"/>
     </row>
     <row r="99" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B99" s="287">
+      <c r="B99" s="245">
         <v>1</v>
       </c>
-      <c r="C99" s="287"/>
+      <c r="C99" s="245"/>
       <c r="D99" s="40" t="s">
         <v>43</v>
       </c>
@@ -22880,70 +22880,70 @@
       <c r="BE99" s="43"/>
     </row>
     <row r="100" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B100" s="288" t="s">
+      <c r="B100" s="252" t="s">
         <v>274</v>
       </c>
-      <c r="C100" s="289"/>
-      <c r="D100" s="289"/>
-      <c r="E100" s="289"/>
-      <c r="F100" s="289"/>
-      <c r="G100" s="289"/>
-      <c r="H100" s="289"/>
-      <c r="I100" s="289"/>
-      <c r="J100" s="289"/>
-      <c r="K100" s="289"/>
-      <c r="L100" s="289"/>
-      <c r="M100" s="289"/>
-      <c r="N100" s="289"/>
-      <c r="O100" s="289"/>
-      <c r="P100" s="289"/>
-      <c r="Q100" s="289"/>
-      <c r="R100" s="289"/>
-      <c r="S100" s="289"/>
-      <c r="T100" s="289"/>
-      <c r="U100" s="289"/>
-      <c r="V100" s="289"/>
-      <c r="W100" s="289"/>
-      <c r="X100" s="289"/>
-      <c r="Y100" s="289"/>
-      <c r="Z100" s="289"/>
-      <c r="AA100" s="289"/>
-      <c r="AB100" s="289"/>
-      <c r="AC100" s="289"/>
-      <c r="AD100" s="289"/>
-      <c r="AE100" s="289"/>
-      <c r="AF100" s="289"/>
-      <c r="AG100" s="289"/>
-      <c r="AH100" s="289"/>
-      <c r="AI100" s="289"/>
-      <c r="AJ100" s="289"/>
-      <c r="AK100" s="289"/>
-      <c r="AL100" s="289"/>
-      <c r="AM100" s="289"/>
-      <c r="AN100" s="289"/>
-      <c r="AO100" s="289"/>
-      <c r="AP100" s="289"/>
-      <c r="AQ100" s="289"/>
-      <c r="AR100" s="289"/>
-      <c r="AS100" s="289"/>
-      <c r="AT100" s="289"/>
-      <c r="AU100" s="289"/>
-      <c r="AV100" s="289"/>
-      <c r="AW100" s="289"/>
-      <c r="AX100" s="289"/>
-      <c r="AY100" s="289"/>
-      <c r="AZ100" s="289"/>
-      <c r="BA100" s="289"/>
-      <c r="BB100" s="289"/>
-      <c r="BC100" s="289"/>
-      <c r="BD100" s="289"/>
-      <c r="BE100" s="289"/>
+      <c r="C100" s="253"/>
+      <c r="D100" s="253"/>
+      <c r="E100" s="253"/>
+      <c r="F100" s="253"/>
+      <c r="G100" s="253"/>
+      <c r="H100" s="253"/>
+      <c r="I100" s="253"/>
+      <c r="J100" s="253"/>
+      <c r="K100" s="253"/>
+      <c r="L100" s="253"/>
+      <c r="M100" s="253"/>
+      <c r="N100" s="253"/>
+      <c r="O100" s="253"/>
+      <c r="P100" s="253"/>
+      <c r="Q100" s="253"/>
+      <c r="R100" s="253"/>
+      <c r="S100" s="253"/>
+      <c r="T100" s="253"/>
+      <c r="U100" s="253"/>
+      <c r="V100" s="253"/>
+      <c r="W100" s="253"/>
+      <c r="X100" s="253"/>
+      <c r="Y100" s="253"/>
+      <c r="Z100" s="253"/>
+      <c r="AA100" s="253"/>
+      <c r="AB100" s="253"/>
+      <c r="AC100" s="253"/>
+      <c r="AD100" s="253"/>
+      <c r="AE100" s="253"/>
+      <c r="AF100" s="253"/>
+      <c r="AG100" s="253"/>
+      <c r="AH100" s="253"/>
+      <c r="AI100" s="253"/>
+      <c r="AJ100" s="253"/>
+      <c r="AK100" s="253"/>
+      <c r="AL100" s="253"/>
+      <c r="AM100" s="253"/>
+      <c r="AN100" s="253"/>
+      <c r="AO100" s="253"/>
+      <c r="AP100" s="253"/>
+      <c r="AQ100" s="253"/>
+      <c r="AR100" s="253"/>
+      <c r="AS100" s="253"/>
+      <c r="AT100" s="253"/>
+      <c r="AU100" s="253"/>
+      <c r="AV100" s="253"/>
+      <c r="AW100" s="253"/>
+      <c r="AX100" s="253"/>
+      <c r="AY100" s="253"/>
+      <c r="AZ100" s="253"/>
+      <c r="BA100" s="253"/>
+      <c r="BB100" s="253"/>
+      <c r="BC100" s="253"/>
+      <c r="BD100" s="253"/>
+      <c r="BE100" s="253"/>
     </row>
     <row r="101" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B101" s="287">
+      <c r="B101" s="245">
         <v>1</v>
       </c>
-      <c r="C101" s="287"/>
+      <c r="C101" s="245"/>
       <c r="D101" s="40" t="s">
         <v>43</v>
       </c>
@@ -23002,70 +23002,70 @@
       <c r="BE101" s="43"/>
     </row>
     <row r="102" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B102" s="251" t="s">
+      <c r="B102" s="248" t="s">
         <v>257</v>
       </c>
-      <c r="C102" s="252"/>
-      <c r="D102" s="252"/>
-      <c r="E102" s="252"/>
-      <c r="F102" s="252"/>
-      <c r="G102" s="252"/>
-      <c r="H102" s="252"/>
-      <c r="I102" s="252"/>
-      <c r="J102" s="252"/>
-      <c r="K102" s="252"/>
-      <c r="L102" s="252"/>
-      <c r="M102" s="252"/>
-      <c r="N102" s="252"/>
-      <c r="O102" s="252"/>
-      <c r="P102" s="252"/>
-      <c r="Q102" s="252"/>
-      <c r="R102" s="252"/>
-      <c r="S102" s="252"/>
-      <c r="T102" s="252"/>
-      <c r="U102" s="252"/>
-      <c r="V102" s="252"/>
-      <c r="W102" s="252"/>
-      <c r="X102" s="252"/>
-      <c r="Y102" s="252"/>
-      <c r="Z102" s="252"/>
-      <c r="AA102" s="252"/>
-      <c r="AB102" s="252"/>
-      <c r="AC102" s="252"/>
-      <c r="AD102" s="252"/>
-      <c r="AE102" s="252"/>
-      <c r="AF102" s="252"/>
-      <c r="AG102" s="252"/>
-      <c r="AH102" s="252"/>
-      <c r="AI102" s="252"/>
-      <c r="AJ102" s="252"/>
-      <c r="AK102" s="252"/>
-      <c r="AL102" s="252"/>
-      <c r="AM102" s="252"/>
-      <c r="AN102" s="252"/>
-      <c r="AO102" s="252"/>
-      <c r="AP102" s="252"/>
-      <c r="AQ102" s="252"/>
-      <c r="AR102" s="252"/>
-      <c r="AS102" s="252"/>
-      <c r="AT102" s="252"/>
-      <c r="AU102" s="252"/>
-      <c r="AV102" s="252"/>
-      <c r="AW102" s="252"/>
-      <c r="AX102" s="252"/>
-      <c r="AY102" s="252"/>
-      <c r="AZ102" s="252"/>
-      <c r="BA102" s="252"/>
-      <c r="BB102" s="252"/>
-      <c r="BC102" s="252"/>
-      <c r="BD102" s="252"/>
-      <c r="BE102" s="253"/>
+      <c r="C102" s="249"/>
+      <c r="D102" s="249"/>
+      <c r="E102" s="249"/>
+      <c r="F102" s="249"/>
+      <c r="G102" s="249"/>
+      <c r="H102" s="249"/>
+      <c r="I102" s="249"/>
+      <c r="J102" s="249"/>
+      <c r="K102" s="249"/>
+      <c r="L102" s="249"/>
+      <c r="M102" s="249"/>
+      <c r="N102" s="249"/>
+      <c r="O102" s="249"/>
+      <c r="P102" s="249"/>
+      <c r="Q102" s="249"/>
+      <c r="R102" s="249"/>
+      <c r="S102" s="249"/>
+      <c r="T102" s="249"/>
+      <c r="U102" s="249"/>
+      <c r="V102" s="249"/>
+      <c r="W102" s="249"/>
+      <c r="X102" s="249"/>
+      <c r="Y102" s="249"/>
+      <c r="Z102" s="249"/>
+      <c r="AA102" s="249"/>
+      <c r="AB102" s="249"/>
+      <c r="AC102" s="249"/>
+      <c r="AD102" s="249"/>
+      <c r="AE102" s="249"/>
+      <c r="AF102" s="249"/>
+      <c r="AG102" s="249"/>
+      <c r="AH102" s="249"/>
+      <c r="AI102" s="249"/>
+      <c r="AJ102" s="249"/>
+      <c r="AK102" s="249"/>
+      <c r="AL102" s="249"/>
+      <c r="AM102" s="249"/>
+      <c r="AN102" s="249"/>
+      <c r="AO102" s="249"/>
+      <c r="AP102" s="249"/>
+      <c r="AQ102" s="249"/>
+      <c r="AR102" s="249"/>
+      <c r="AS102" s="249"/>
+      <c r="AT102" s="249"/>
+      <c r="AU102" s="249"/>
+      <c r="AV102" s="249"/>
+      <c r="AW102" s="249"/>
+      <c r="AX102" s="249"/>
+      <c r="AY102" s="249"/>
+      <c r="AZ102" s="249"/>
+      <c r="BA102" s="249"/>
+      <c r="BB102" s="249"/>
+      <c r="BC102" s="249"/>
+      <c r="BD102" s="249"/>
+      <c r="BE102" s="250"/>
     </row>
     <row r="103" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B103" s="254">
+      <c r="B103" s="251">
         <v>1</v>
       </c>
-      <c r="C103" s="254"/>
+      <c r="C103" s="251"/>
       <c r="D103" s="37" t="s">
         <v>268</v>
       </c>
@@ -23130,10 +23130,10 @@
       <c r="BE103" s="43"/>
     </row>
     <row r="104" spans="1:62" s="23" customFormat="1" ht="14.1" customHeight="1">
-      <c r="B104" s="254">
+      <c r="B104" s="251">
         <v>2</v>
       </c>
-      <c r="C104" s="254"/>
+      <c r="C104" s="251"/>
       <c r="D104" s="37" t="s">
         <v>284</v>
       </c>
@@ -23201,10 +23201,10 @@
       <c r="BJ104" s="21"/>
     </row>
     <row r="105" spans="1:62" s="23" customFormat="1" ht="14.1" customHeight="1">
-      <c r="B105" s="254">
+      <c r="B105" s="251">
         <v>3</v>
       </c>
-      <c r="C105" s="254"/>
+      <c r="C105" s="251"/>
       <c r="D105" s="37" t="s">
         <v>5</v>
       </c>
@@ -23273,10 +23273,10 @@
     </row>
     <row r="106" spans="1:62" s="23" customFormat="1" ht="14.1" customHeight="1">
       <c r="A106" s="6"/>
-      <c r="B106" s="254">
+      <c r="B106" s="251">
         <v>4</v>
       </c>
-      <c r="C106" s="254"/>
+      <c r="C106" s="251"/>
       <c r="D106" s="37" t="s">
         <v>408</v>
       </c>
@@ -23345,10 +23345,10 @@
     </row>
     <row r="107" spans="1:62" s="23" customFormat="1" ht="14.1" customHeight="1">
       <c r="A107" s="6"/>
-      <c r="B107" s="254">
+      <c r="B107" s="251">
         <v>5</v>
       </c>
-      <c r="C107" s="254"/>
+      <c r="C107" s="251"/>
       <c r="D107" s="37" t="s">
         <v>409</v>
       </c>
@@ -23416,10 +23416,10 @@
       <c r="BJ107" s="21"/>
     </row>
     <row r="108" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B108" s="254">
+      <c r="B108" s="251">
         <v>6</v>
       </c>
-      <c r="C108" s="254"/>
+      <c r="C108" s="251"/>
       <c r="D108" s="37" t="s">
         <v>215</v>
       </c>
@@ -23484,10 +23484,10 @@
       <c r="BE108" s="43"/>
     </row>
     <row r="109" spans="1:62" ht="14.1" customHeight="1">
-      <c r="B109" s="254">
+      <c r="B109" s="251">
         <v>7</v>
       </c>
-      <c r="C109" s="254"/>
+      <c r="C109" s="251"/>
       <c r="D109" s="37" t="s">
         <v>192</v>
       </c>
@@ -23552,10 +23552,10 @@
       <c r="BE109" s="43"/>
     </row>
     <row r="110" spans="1:62">
-      <c r="B110" s="254">
+      <c r="B110" s="251">
         <v>8</v>
       </c>
-      <c r="C110" s="254"/>
+      <c r="C110" s="251"/>
       <c r="D110" s="37" t="s">
         <v>9</v>
       </c>
@@ -23620,70 +23620,70 @@
       <c r="BE110" s="43"/>
     </row>
     <row r="111" spans="1:62">
-      <c r="B111" s="251" t="s">
+      <c r="B111" s="248" t="s">
         <v>258</v>
       </c>
-      <c r="C111" s="252"/>
-      <c r="D111" s="252"/>
-      <c r="E111" s="252"/>
-      <c r="F111" s="252"/>
-      <c r="G111" s="252"/>
-      <c r="H111" s="252"/>
-      <c r="I111" s="252"/>
-      <c r="J111" s="252"/>
-      <c r="K111" s="252"/>
-      <c r="L111" s="252"/>
-      <c r="M111" s="252"/>
-      <c r="N111" s="252"/>
-      <c r="O111" s="252"/>
-      <c r="P111" s="252"/>
-      <c r="Q111" s="252"/>
-      <c r="R111" s="252"/>
-      <c r="S111" s="252"/>
-      <c r="T111" s="252"/>
-      <c r="U111" s="252"/>
-      <c r="V111" s="252"/>
-      <c r="W111" s="252"/>
-      <c r="X111" s="252"/>
-      <c r="Y111" s="252"/>
-      <c r="Z111" s="252"/>
-      <c r="AA111" s="252"/>
-      <c r="AB111" s="252"/>
-      <c r="AC111" s="252"/>
-      <c r="AD111" s="252"/>
-      <c r="AE111" s="252"/>
-      <c r="AF111" s="252"/>
-      <c r="AG111" s="252"/>
-      <c r="AH111" s="252"/>
-      <c r="AI111" s="252"/>
-      <c r="AJ111" s="252"/>
-      <c r="AK111" s="252"/>
-      <c r="AL111" s="252"/>
-      <c r="AM111" s="252"/>
-      <c r="AN111" s="252"/>
-      <c r="AO111" s="252"/>
-      <c r="AP111" s="252"/>
-      <c r="AQ111" s="252"/>
-      <c r="AR111" s="252"/>
-      <c r="AS111" s="252"/>
-      <c r="AT111" s="252"/>
-      <c r="AU111" s="252"/>
-      <c r="AV111" s="252"/>
-      <c r="AW111" s="252"/>
-      <c r="AX111" s="252"/>
-      <c r="AY111" s="252"/>
-      <c r="AZ111" s="252"/>
-      <c r="BA111" s="252"/>
-      <c r="BB111" s="252"/>
-      <c r="BC111" s="252"/>
-      <c r="BD111" s="252"/>
-      <c r="BE111" s="253"/>
+      <c r="C111" s="249"/>
+      <c r="D111" s="249"/>
+      <c r="E111" s="249"/>
+      <c r="F111" s="249"/>
+      <c r="G111" s="249"/>
+      <c r="H111" s="249"/>
+      <c r="I111" s="249"/>
+      <c r="J111" s="249"/>
+      <c r="K111" s="249"/>
+      <c r="L111" s="249"/>
+      <c r="M111" s="249"/>
+      <c r="N111" s="249"/>
+      <c r="O111" s="249"/>
+      <c r="P111" s="249"/>
+      <c r="Q111" s="249"/>
+      <c r="R111" s="249"/>
+      <c r="S111" s="249"/>
+      <c r="T111" s="249"/>
+      <c r="U111" s="249"/>
+      <c r="V111" s="249"/>
+      <c r="W111" s="249"/>
+      <c r="X111" s="249"/>
+      <c r="Y111" s="249"/>
+      <c r="Z111" s="249"/>
+      <c r="AA111" s="249"/>
+      <c r="AB111" s="249"/>
+      <c r="AC111" s="249"/>
+      <c r="AD111" s="249"/>
+      <c r="AE111" s="249"/>
+      <c r="AF111" s="249"/>
+      <c r="AG111" s="249"/>
+      <c r="AH111" s="249"/>
+      <c r="AI111" s="249"/>
+      <c r="AJ111" s="249"/>
+      <c r="AK111" s="249"/>
+      <c r="AL111" s="249"/>
+      <c r="AM111" s="249"/>
+      <c r="AN111" s="249"/>
+      <c r="AO111" s="249"/>
+      <c r="AP111" s="249"/>
+      <c r="AQ111" s="249"/>
+      <c r="AR111" s="249"/>
+      <c r="AS111" s="249"/>
+      <c r="AT111" s="249"/>
+      <c r="AU111" s="249"/>
+      <c r="AV111" s="249"/>
+      <c r="AW111" s="249"/>
+      <c r="AX111" s="249"/>
+      <c r="AY111" s="249"/>
+      <c r="AZ111" s="249"/>
+      <c r="BA111" s="249"/>
+      <c r="BB111" s="249"/>
+      <c r="BC111" s="249"/>
+      <c r="BD111" s="249"/>
+      <c r="BE111" s="250"/>
     </row>
     <row r="112" spans="1:62">
-      <c r="B112" s="287">
+      <c r="B112" s="245">
         <v>1</v>
       </c>
-      <c r="C112" s="287"/>
+      <c r="C112" s="245"/>
       <c r="D112" s="40" t="s">
         <v>43</v>
       </c>
@@ -23743,6 +23743,81 @@
     </row>
   </sheetData>
   <mergeCells count="91">
+    <mergeCell ref="B2:N3"/>
+    <mergeCell ref="B47:C48"/>
+    <mergeCell ref="D47:I48"/>
+    <mergeCell ref="J47:U47"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="Y47:AC48"/>
+    <mergeCell ref="AD47:AE48"/>
+    <mergeCell ref="AF47:AG48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:BE50"/>
+    <mergeCell ref="AH47:AJ48"/>
+    <mergeCell ref="W47:X47"/>
+    <mergeCell ref="AQ47:BE48"/>
+    <mergeCell ref="J48:O48"/>
+    <mergeCell ref="P48:U48"/>
+    <mergeCell ref="AK47:AL48"/>
+    <mergeCell ref="AM47:AP48"/>
+    <mergeCell ref="V47:V48"/>
+    <mergeCell ref="AQ53:BE53"/>
+    <mergeCell ref="AQ57:BE57"/>
+    <mergeCell ref="AQ62:BE62"/>
+    <mergeCell ref="AQ85:BE85"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B80:BE80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:BE84"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="AQ55:BE55"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B98:BE98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B102:BE102"/>
+    <mergeCell ref="B105:C105"/>
+    <mergeCell ref="B104:C104"/>
+    <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B100:BE100"/>
+    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="B111:BE111"/>
+    <mergeCell ref="B107:C107"/>
+    <mergeCell ref="B96:BE96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="AD55:AE55"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="AF62:AG62"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B88:BE88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B92:C93"/>
+    <mergeCell ref="D92:I93"/>
+    <mergeCell ref="J92:P93"/>
+    <mergeCell ref="Q92:T93"/>
+    <mergeCell ref="B74:C74"/>
     <mergeCell ref="B59:C59"/>
     <mergeCell ref="B60:C60"/>
     <mergeCell ref="AQ59:BE59"/>
@@ -23759,81 +23834,6 @@
     <mergeCell ref="B69:C69"/>
     <mergeCell ref="B70:C70"/>
     <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B96:BE96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="AD55:AE55"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="AF62:AG62"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B88:BE88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B92:C93"/>
-    <mergeCell ref="D92:I93"/>
-    <mergeCell ref="J92:P93"/>
-    <mergeCell ref="Q92:T93"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B98:BE98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B108:C108"/>
-    <mergeCell ref="B109:C109"/>
-    <mergeCell ref="B102:BE102"/>
-    <mergeCell ref="B105:C105"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B103:C103"/>
-    <mergeCell ref="B110:C110"/>
-    <mergeCell ref="B100:BE100"/>
-    <mergeCell ref="B101:C101"/>
-    <mergeCell ref="B111:BE111"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="AQ53:BE53"/>
-    <mergeCell ref="AQ57:BE57"/>
-    <mergeCell ref="AQ62:BE62"/>
-    <mergeCell ref="AQ85:BE85"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B80:BE80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:BE84"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="AQ55:BE55"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="Y47:AC48"/>
-    <mergeCell ref="AD47:AE48"/>
-    <mergeCell ref="AF47:AG48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B50:BE50"/>
-    <mergeCell ref="AH47:AJ48"/>
-    <mergeCell ref="W47:X47"/>
-    <mergeCell ref="AQ47:BE48"/>
-    <mergeCell ref="J48:O48"/>
-    <mergeCell ref="P48:U48"/>
-    <mergeCell ref="AK47:AL48"/>
-    <mergeCell ref="AM47:AP48"/>
-    <mergeCell ref="V47:V48"/>
-    <mergeCell ref="B2:N3"/>
-    <mergeCell ref="B47:C48"/>
-    <mergeCell ref="D47:I48"/>
-    <mergeCell ref="J47:U47"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B58:C58"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="9">
@@ -32908,6 +32908,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="B2:J3"/>
+    <mergeCell ref="M56:R56"/>
+    <mergeCell ref="M8:R9"/>
+    <mergeCell ref="M11:R11"/>
+    <mergeCell ref="M53:R54"/>
+    <mergeCell ref="M41:R42"/>
+    <mergeCell ref="M44:R44"/>
     <mergeCell ref="M61:R62"/>
     <mergeCell ref="S61:AO62"/>
     <mergeCell ref="M64:R64"/>
@@ -32924,13 +32931,6 @@
     <mergeCell ref="M19:R19"/>
     <mergeCell ref="AA28:AO29"/>
     <mergeCell ref="S41:AO42"/>
-    <mergeCell ref="B2:J3"/>
-    <mergeCell ref="M56:R56"/>
-    <mergeCell ref="M8:R9"/>
-    <mergeCell ref="M11:R11"/>
-    <mergeCell ref="M53:R54"/>
-    <mergeCell ref="M41:R42"/>
-    <mergeCell ref="M44:R44"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
